--- a/data/MyPortfolio.xlsx
+++ b/data/MyPortfolio.xlsx
@@ -638,41 +638,41 @@
         <v>1741.62</v>
       </c>
       <c r="J2" s="11" t="n">
-        <v>16588000</v>
+        <v>17668000</v>
       </c>
       <c r="K2" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="11" t="n">
-        <v>16751000</v>
+        <v>17868500</v>
       </c>
       <c r="M2" s="11" t="n">
         <v>0</v>
       </c>
       <c r="N2" s="12" t="n">
-        <v>-0.009730762342546714</v>
+        <v>-0.01122086353079441</v>
       </c>
       <c r="O2" s="12" t="n">
         <v>-0.007968740209955527</v>
       </c>
       <c r="P2" s="12" t="n">
-        <v>-0.294626767050114</v>
+        <v>-0.24870181578499</v>
       </c>
       <c r="Q2" s="12" t="n">
-        <v>-0.3898209364556551</v>
+        <v>-0.3500938211537562</v>
       </c>
       <c r="R2" s="12" t="n">
-        <v>-0.7587678226781063</v>
+        <v>-0.7430618453747753</v>
       </c>
       <c r="S2" s="12" t="n">
         <v>-0.02402367062858168</v>
       </c>
       <c r="T2" s="6">
-        <f>(-0.7587678226781063 - 0.04) / (STDEVP(N2:N205) * SQRT(252))</f>
+        <f>(-0.7430618453747753 - 0.04) / (STDEVP(N2:N205) * SQRT(252))</f>
         <v/>
       </c>
       <c r="U2" s="12" t="n">
-        <v>-0.7844521941143038</v>
+        <v>-0.7704184570539858</v>
       </c>
     </row>
     <row r="3">
@@ -706,25 +706,25 @@
         <v>1755.61</v>
       </c>
       <c r="J3" s="11" t="n">
-        <v>16751000</v>
+        <v>17868500</v>
       </c>
       <c r="K3" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L3" s="11" t="n">
-        <v>18240000</v>
+        <v>19915000</v>
       </c>
       <c r="M3" s="11" t="n">
         <v>0</v>
       </c>
       <c r="N3" s="12" t="n">
-        <v>-0.08163377192982456</v>
+        <v>-0.1027617373838815</v>
       </c>
       <c r="O3" s="12" t="n">
         <v>-0.006249115557694029</v>
       </c>
       <c r="P3" s="12" t="n">
-        <v>-0.2876955012573222</v>
+        <v>-0.2401759336288257</v>
       </c>
       <c r="Q3" s="13" t="n"/>
       <c r="R3" s="13" t="n"/>
@@ -763,25 +763,25 @@
         <v>1766.65</v>
       </c>
       <c r="J4" s="11" t="n">
-        <v>18240000</v>
+        <v>19915000</v>
       </c>
       <c r="K4" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L4" s="11" t="n">
-        <v>18971000</v>
+        <v>20648500</v>
       </c>
       <c r="M4" s="11" t="n">
         <v>0</v>
       </c>
       <c r="N4" s="12" t="n">
-        <v>-0.03853249696905803</v>
+        <v>-0.03552316148872799</v>
       </c>
       <c r="O4" s="12" t="n">
         <v>0.002713026500252624</v>
       </c>
       <c r="P4" s="12" t="n">
-        <v>-0.2243786008556837</v>
+        <v>-0.1531524032917181</v>
       </c>
       <c r="Q4" s="13" t="n"/>
       <c r="R4" s="13" t="n"/>
@@ -820,25 +820,25 @@
         <v>1761.87</v>
       </c>
       <c r="J5" s="11" t="n">
-        <v>18971000</v>
+        <v>20648500</v>
       </c>
       <c r="K5" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L5" s="11" t="n">
-        <v>19216000</v>
+        <v>20906000</v>
       </c>
       <c r="M5" s="11" t="n">
         <v>0</v>
       </c>
       <c r="N5" s="12" t="n">
-        <v>-0.01274979184013322</v>
+        <v>-0.01231703817086004</v>
       </c>
       <c r="O5" s="12" t="n">
         <v>-0.0009526239686995508</v>
       </c>
       <c r="P5" s="12" t="n">
-        <v>-0.1932942125456785</v>
+        <v>-0.1219617072241547</v>
       </c>
       <c r="Q5" s="13" t="n"/>
       <c r="R5" s="13" t="n"/>
@@ -877,25 +877,25 @@
         <v>1763.55</v>
       </c>
       <c r="J6" s="11" t="n">
-        <v>19216000</v>
+        <v>20906000</v>
       </c>
       <c r="K6" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L6" s="11" t="n">
-        <v>19718000</v>
+        <v>21428000</v>
       </c>
       <c r="M6" s="11" t="n">
         <v>0</v>
       </c>
       <c r="N6" s="12" t="n">
-        <v>-0.02545897149812354</v>
+        <v>-0.02436064961732313</v>
       </c>
       <c r="O6" s="12" t="n">
         <v>-0.005974692106079038</v>
       </c>
       <c r="P6" s="12" t="n">
-        <v>-0.1828760523049791</v>
+        <v>-0.1110120081956645</v>
       </c>
       <c r="Q6" s="13" t="n"/>
       <c r="R6" s="13" t="n"/>
@@ -934,25 +934,25 @@
         <v>1774.15</v>
       </c>
       <c r="J7" s="11" t="n">
-        <v>19718000</v>
+        <v>21428000</v>
       </c>
       <c r="K7" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="11" t="n">
-        <v>20021000</v>
+        <v>21728500</v>
       </c>
       <c r="M7" s="11" t="n">
         <v>0</v>
       </c>
       <c r="N7" s="12" t="n">
-        <v>-0.01513410918535538</v>
+        <v>-0.0138297627539867</v>
       </c>
       <c r="O7" s="12" t="n">
         <v>0.007679069424012974</v>
       </c>
       <c r="P7" s="12" t="n">
-        <v>-0.1615294545873011</v>
+        <v>-0.08881494841752124</v>
       </c>
       <c r="Q7" s="13" t="n"/>
       <c r="R7" s="13" t="n"/>
@@ -991,25 +991,25 @@
         <v>1760.63</v>
       </c>
       <c r="J8" s="11" t="n">
-        <v>20021000</v>
+        <v>21728500</v>
       </c>
       <c r="K8" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="11" t="n">
-        <v>20002000</v>
+        <v>21722000</v>
       </c>
       <c r="M8" s="11" t="n">
         <v>0</v>
       </c>
       <c r="N8" s="12" t="n">
-        <v>0.0009499050094990501</v>
+        <v>0.0002992357978086733</v>
       </c>
       <c r="O8" s="12" t="n">
         <v>0.01263034388354312</v>
       </c>
       <c r="P8" s="12" t="n">
-        <v>-0.1486449543712524</v>
+        <v>-0.0760367559590307</v>
       </c>
       <c r="Q8" s="13" t="n"/>
       <c r="R8" s="13" t="n"/>
@@ -1048,25 +1048,25 @@
         <v>1738.67</v>
       </c>
       <c r="J9" s="11" t="n">
-        <v>20002000</v>
+        <v>21722000</v>
       </c>
       <c r="K9" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="11" t="n">
-        <v>19935000</v>
+        <v>21632500</v>
       </c>
       <c r="M9" s="11" t="n">
         <v>0</v>
       </c>
       <c r="N9" s="12" t="n">
-        <v>0.003360922999749185</v>
+        <v>0.004137293424245926</v>
       </c>
       <c r="O9" s="12" t="n">
         <v>0.02760096219200103</v>
       </c>
       <c r="P9" s="12" t="n">
-        <v>-0.1494528933286943</v>
+        <v>-0.07631315612868195</v>
       </c>
       <c r="Q9" s="13" t="n"/>
       <c r="R9" s="13" t="n"/>
@@ -1105,25 +1105,25 @@
         <v>1691.97</v>
       </c>
       <c r="J10" s="11" t="n">
-        <v>19935000</v>
+        <v>21632500</v>
       </c>
       <c r="K10" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="11" t="n">
-        <v>19491000</v>
+        <v>21153500</v>
       </c>
       <c r="M10" s="11" t="n">
         <v>0</v>
       </c>
       <c r="N10" s="12" t="n">
-        <v>0.02277974449746037</v>
+        <v>0.02264400690193112</v>
       </c>
       <c r="O10" s="12" t="n">
         <v>0.001260474364436881</v>
       </c>
       <c r="P10" s="12" t="n">
-        <v>-0.1523019412312528</v>
+        <v>-0.08011897384926392</v>
       </c>
       <c r="Q10" s="13" t="n"/>
       <c r="R10" s="13" t="n"/>
@@ -1162,7 +1162,7 @@
         <v>1689.84</v>
       </c>
       <c r="J11" s="11" t="n">
-        <v>19491000</v>
+        <v>21153500</v>
       </c>
       <c r="K11" s="11" t="n">
         <v>0</v>
@@ -1174,13 +1174,13 @@
         <v>0</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>-0.03145497912939774</v>
+        <v>0.05115782150665871</v>
       </c>
       <c r="O11" s="12" t="n">
         <v>-0.00942019215550649</v>
       </c>
       <c r="P11" s="12" t="n">
-        <v>-0.1711821989735817</v>
+        <v>-0.1004875401974069</v>
       </c>
       <c r="Q11" s="13" t="n"/>
       <c r="R11" s="13" t="n"/>

--- a/data/MyPortfolio.xlsx
+++ b/data/MyPortfolio.xlsx
@@ -521,7 +521,7 @@
           <t>FPT</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>PNJ</t>
         </is>
@@ -622,7 +622,7 @@
       <c r="D2" s="8" t="n">
         <v>52700</v>
       </c>
-      <c r="E2" s="8" t="n">
+      <c r="E2" s="9" t="n">
         <v>15500</v>
       </c>
       <c r="F2" s="9" t="n">
@@ -656,23 +656,23 @@
         <v>-0.007968740209955527</v>
       </c>
       <c r="P2" s="12" t="n">
-        <v>-0.24870181578499</v>
+        <v>-0.2487018157849902</v>
       </c>
       <c r="Q2" s="12" t="n">
-        <v>-0.3500938211537562</v>
+        <v>-0.3500938211537564</v>
       </c>
       <c r="R2" s="12" t="n">
-        <v>-0.7430618453747753</v>
+        <v>-0.7430618453747757</v>
       </c>
       <c r="S2" s="12" t="n">
         <v>-0.02402367062858168</v>
       </c>
       <c r="T2" s="6">
-        <f>(-0.7430618453747753 - 0.04) / (STDEVP(N2:N205) * SQRT(252))</f>
+        <f>(-0.7430618453747757 - 0.04) / (STDEVP(N2:N205) * SQRT(252))</f>
         <v/>
       </c>
       <c r="U2" s="12" t="n">
-        <v>-0.7704184570539858</v>
+        <v>-0.7704184570539859</v>
       </c>
     </row>
     <row r="3">
@@ -690,7 +690,7 @@
       <c r="D3" s="8" t="n">
         <v>52700</v>
       </c>
-      <c r="E3" s="8" t="n">
+      <c r="E3" s="9" t="n">
         <v>16050</v>
       </c>
       <c r="F3" s="9" t="n">
@@ -712,19 +712,19 @@
         <v>0</v>
       </c>
       <c r="L3" s="11" t="n">
-        <v>19915000</v>
+        <v>18240000</v>
       </c>
       <c r="M3" s="11" t="n">
         <v>0</v>
       </c>
       <c r="N3" s="12" t="n">
-        <v>-0.1027617373838815</v>
+        <v>-0.02036732456140351</v>
       </c>
       <c r="O3" s="12" t="n">
         <v>-0.006249115557694029</v>
       </c>
       <c r="P3" s="12" t="n">
-        <v>-0.2401759336288257</v>
+        <v>-0.2401759336288259</v>
       </c>
       <c r="Q3" s="13" t="n"/>
       <c r="R3" s="13" t="n"/>
@@ -747,7 +747,7 @@
       <c r="D4" s="8" t="n">
         <v>54000</v>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="E4" s="9" t="n">
         <v>17150</v>
       </c>
       <c r="F4" s="9" t="n">
@@ -763,25 +763,25 @@
         <v>1766.65</v>
       </c>
       <c r="J4" s="11" t="n">
-        <v>19915000</v>
+        <v>18240000</v>
       </c>
       <c r="K4" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L4" s="11" t="n">
-        <v>20648500</v>
+        <v>18971000</v>
       </c>
       <c r="M4" s="11" t="n">
         <v>0</v>
       </c>
       <c r="N4" s="12" t="n">
-        <v>-0.03552316148872799</v>
+        <v>-0.03853249696905803</v>
       </c>
       <c r="O4" s="12" t="n">
         <v>0.002713026500252624</v>
       </c>
       <c r="P4" s="12" t="n">
-        <v>-0.1531524032917181</v>
+        <v>-0.2243786008556837</v>
       </c>
       <c r="Q4" s="13" t="n"/>
       <c r="R4" s="13" t="n"/>
@@ -804,7 +804,7 @@
       <c r="D5" s="8" t="n">
         <v>55400</v>
       </c>
-      <c r="E5" s="8" t="n">
+      <c r="E5" s="9" t="n">
         <v>17050</v>
       </c>
       <c r="F5" s="9" t="n">
@@ -820,25 +820,25 @@
         <v>1761.87</v>
       </c>
       <c r="J5" s="11" t="n">
-        <v>20648500</v>
+        <v>18971000</v>
       </c>
       <c r="K5" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L5" s="11" t="n">
-        <v>20906000</v>
+        <v>19216000</v>
       </c>
       <c r="M5" s="11" t="n">
         <v>0</v>
       </c>
       <c r="N5" s="12" t="n">
-        <v>-0.01231703817086004</v>
+        <v>-0.01274979184013322</v>
       </c>
       <c r="O5" s="12" t="n">
         <v>-0.0009526239686995508</v>
       </c>
       <c r="P5" s="12" t="n">
-        <v>-0.1219617072241547</v>
+        <v>-0.1932942125456785</v>
       </c>
       <c r="Q5" s="13" t="n"/>
       <c r="R5" s="13" t="n"/>
@@ -861,7 +861,7 @@
       <c r="D6" s="8" t="n">
         <v>56000</v>
       </c>
-      <c r="E6" s="8" t="n">
+      <c r="E6" s="9" t="n">
         <v>17450</v>
       </c>
       <c r="F6" s="9" t="n">
@@ -877,25 +877,25 @@
         <v>1763.55</v>
       </c>
       <c r="J6" s="11" t="n">
-        <v>20906000</v>
+        <v>19216000</v>
       </c>
       <c r="K6" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L6" s="11" t="n">
-        <v>21428000</v>
+        <v>19718000</v>
       </c>
       <c r="M6" s="11" t="n">
         <v>0</v>
       </c>
       <c r="N6" s="12" t="n">
-        <v>-0.02436064961732313</v>
+        <v>-0.02545897149812354</v>
       </c>
       <c r="O6" s="12" t="n">
         <v>-0.005974692106079038</v>
       </c>
       <c r="P6" s="12" t="n">
-        <v>-0.1110120081956645</v>
+        <v>-0.1828760523049791</v>
       </c>
       <c r="Q6" s="13" t="n"/>
       <c r="R6" s="13" t="n"/>
@@ -918,7 +918,7 @@
       <c r="D7" s="8" t="n">
         <v>57000</v>
       </c>
-      <c r="E7" s="8" t="n">
+      <c r="E7" s="9" t="n">
         <v>17450</v>
       </c>
       <c r="F7" s="9" t="n">
@@ -934,25 +934,25 @@
         <v>1774.15</v>
       </c>
       <c r="J7" s="11" t="n">
-        <v>21428000</v>
+        <v>19718000</v>
       </c>
       <c r="K7" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="11" t="n">
-        <v>21728500</v>
+        <v>20021000</v>
       </c>
       <c r="M7" s="11" t="n">
         <v>0</v>
       </c>
       <c r="N7" s="12" t="n">
-        <v>-0.0138297627539867</v>
+        <v>-0.01513410918535538</v>
       </c>
       <c r="O7" s="12" t="n">
         <v>0.007679069424012974</v>
       </c>
       <c r="P7" s="12" t="n">
-        <v>-0.08881494841752124</v>
+        <v>-0.1615294545873011</v>
       </c>
       <c r="Q7" s="13" t="n"/>
       <c r="R7" s="13" t="n"/>
@@ -975,7 +975,7 @@
       <c r="D8" s="8" t="n">
         <v>57400</v>
       </c>
-      <c r="E8" s="8" t="n">
+      <c r="E8" s="9" t="n">
         <v>18600</v>
       </c>
       <c r="F8" s="9" t="n">
@@ -991,25 +991,25 @@
         <v>1760.63</v>
       </c>
       <c r="J8" s="11" t="n">
-        <v>21728500</v>
+        <v>20021000</v>
       </c>
       <c r="K8" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="11" t="n">
-        <v>21722000</v>
+        <v>20002000</v>
       </c>
       <c r="M8" s="11" t="n">
         <v>0</v>
       </c>
       <c r="N8" s="12" t="n">
-        <v>0.0002992357978086733</v>
+        <v>0.0009499050094990501</v>
       </c>
       <c r="O8" s="12" t="n">
         <v>0.01263034388354312</v>
       </c>
       <c r="P8" s="12" t="n">
-        <v>-0.0760367559590307</v>
+        <v>-0.1486449543712524</v>
       </c>
       <c r="Q8" s="13" t="n"/>
       <c r="R8" s="13" t="n"/>
@@ -1032,7 +1032,7 @@
       <c r="D9" s="8" t="n">
         <v>57400</v>
       </c>
-      <c r="E9" s="8" t="n">
+      <c r="E9" s="9" t="n">
         <v>19200</v>
       </c>
       <c r="F9" s="9" t="n">
@@ -1048,25 +1048,25 @@
         <v>1738.67</v>
       </c>
       <c r="J9" s="11" t="n">
-        <v>21722000</v>
+        <v>20002000</v>
       </c>
       <c r="K9" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="11" t="n">
-        <v>21632500</v>
+        <v>19935000</v>
       </c>
       <c r="M9" s="11" t="n">
         <v>0</v>
       </c>
       <c r="N9" s="12" t="n">
-        <v>0.004137293424245926</v>
+        <v>0.003360922999749185</v>
       </c>
       <c r="O9" s="12" t="n">
         <v>0.02760096219200103</v>
       </c>
       <c r="P9" s="12" t="n">
-        <v>-0.07631315612868195</v>
+        <v>-0.1494528933286943</v>
       </c>
       <c r="Q9" s="13" t="n"/>
       <c r="R9" s="13" t="n"/>
@@ -1089,7 +1089,7 @@
       <c r="D10" s="8" t="n">
         <v>57400</v>
       </c>
-      <c r="E10" s="8" t="n">
+      <c r="E10" s="9" t="n">
         <v>19750</v>
       </c>
       <c r="F10" s="9" t="n">
@@ -1105,25 +1105,25 @@
         <v>1691.97</v>
       </c>
       <c r="J10" s="11" t="n">
-        <v>21632500</v>
+        <v>19935000</v>
       </c>
       <c r="K10" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="11" t="n">
-        <v>21153500</v>
+        <v>19491000</v>
       </c>
       <c r="M10" s="11" t="n">
         <v>0</v>
       </c>
       <c r="N10" s="12" t="n">
-        <v>0.02264400690193112</v>
+        <v>0.02277974449746037</v>
       </c>
       <c r="O10" s="12" t="n">
         <v>0.001260474364436881</v>
       </c>
       <c r="P10" s="12" t="n">
-        <v>-0.08011897384926392</v>
+        <v>-0.1523019412312528</v>
       </c>
       <c r="Q10" s="13" t="n"/>
       <c r="R10" s="13" t="n"/>
@@ -1146,7 +1146,7 @@
       <c r="D11" s="8" t="n">
         <v>57100</v>
       </c>
-      <c r="E11" s="8" t="n">
+      <c r="E11" s="9" t="n">
         <v>18500</v>
       </c>
       <c r="F11" s="9" t="n">
@@ -1162,7 +1162,7 @@
         <v>1689.84</v>
       </c>
       <c r="J11" s="11" t="n">
-        <v>21153500</v>
+        <v>19491000</v>
       </c>
       <c r="K11" s="11" t="n">
         <v>0</v>
@@ -1174,13 +1174,13 @@
         <v>0</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>0.05115782150665871</v>
+        <v>-0.03145497912939774</v>
       </c>
       <c r="O11" s="12" t="n">
         <v>-0.00942019215550649</v>
       </c>
       <c r="P11" s="12" t="n">
-        <v>-0.1004875401974069</v>
+        <v>-0.1711821989735817</v>
       </c>
       <c r="Q11" s="13" t="n"/>
       <c r="R11" s="13" t="n"/>
@@ -1203,7 +1203,7 @@
       <c r="D12" s="8" t="n">
         <v>58200</v>
       </c>
-      <c r="E12" s="8" t="n">
+      <c r="E12" s="9" t="n">
         <v>18800</v>
       </c>
       <c r="F12" s="9" t="n">
@@ -1260,7 +1260,7 @@
       <c r="D13" s="8" t="n">
         <v>58000</v>
       </c>
-      <c r="E13" s="8" t="n">
+      <c r="E13" s="9" t="n">
         <v>18200</v>
       </c>
       <c r="F13" s="9" t="n">
@@ -1317,7 +1317,7 @@
       <c r="D14" s="8" t="n">
         <v>57100</v>
       </c>
-      <c r="E14" s="8" t="n">
+      <c r="E14" s="9" t="n">
         <v>18650</v>
       </c>
       <c r="F14" s="9" t="n">
@@ -1374,7 +1374,7 @@
       <c r="D15" s="8" t="n">
         <v>56300</v>
       </c>
-      <c r="E15" s="8" t="n">
+      <c r="E15" s="9" t="n">
         <v>19200</v>
       </c>
       <c r="F15" s="9" t="n">
@@ -1431,7 +1431,7 @@
       <c r="D16" s="8" t="n">
         <v>57100</v>
       </c>
-      <c r="E16" s="8" t="n">
+      <c r="E16" s="9" t="n">
         <v>18150</v>
       </c>
       <c r="F16" s="9" t="n">
@@ -1488,7 +1488,7 @@
       <c r="D17" s="8" t="n">
         <v>57900</v>
       </c>
-      <c r="E17" s="8" t="n">
+      <c r="E17" s="9" t="n">
         <v>19500</v>
       </c>
       <c r="F17" s="9" t="n">
@@ -1545,7 +1545,7 @@
       <c r="D18" s="8" t="n">
         <v>59700</v>
       </c>
-      <c r="E18" s="8" t="n">
+      <c r="E18" s="9" t="n">
         <v>18250</v>
       </c>
       <c r="F18" s="9" t="n">
@@ -1602,7 +1602,7 @@
       <c r="D19" s="8" t="n">
         <v>59700</v>
       </c>
-      <c r="E19" s="8" t="n">
+      <c r="E19" s="9" t="n">
         <v>18900</v>
       </c>
       <c r="F19" s="9" t="n">
@@ -1659,7 +1659,7 @@
       <c r="D20" s="8" t="n">
         <v>60400</v>
       </c>
-      <c r="E20" s="8" t="n">
+      <c r="E20" s="9" t="n">
         <v>20150</v>
       </c>
       <c r="F20" s="9" t="n">
@@ -1716,7 +1716,7 @@
       <c r="D21" s="8" t="n">
         <v>61900</v>
       </c>
-      <c r="E21" s="8" t="n">
+      <c r="E21" s="9" t="n">
         <v>21650</v>
       </c>
       <c r="F21" s="9" t="n">
@@ -1773,7 +1773,7 @@
       <c r="D22" s="8" t="n">
         <v>62100</v>
       </c>
-      <c r="E22" s="8" t="n">
+      <c r="E22" s="9" t="n">
         <v>23050</v>
       </c>
       <c r="F22" s="9" t="n">
@@ -1830,7 +1830,7 @@
       <c r="D23" s="8" t="n">
         <v>62700</v>
       </c>
-      <c r="E23" s="8" t="n">
+      <c r="E23" s="9" t="n">
         <v>24750</v>
       </c>
       <c r="F23" s="9" t="n">
@@ -1887,7 +1887,7 @@
       <c r="D24" s="8" t="n">
         <v>63000</v>
       </c>
-      <c r="E24" s="8" t="n">
+      <c r="E24" s="9" t="n">
         <v>26600</v>
       </c>
       <c r="F24" s="9" t="n">
@@ -1946,7 +1946,7 @@
       <c r="D25" s="8" t="n">
         <v>63200</v>
       </c>
-      <c r="E25" s="8" t="n">
+      <c r="E25" s="9" t="n">
         <v>28600</v>
       </c>
       <c r="F25" s="9" t="n">
@@ -2003,7 +2003,7 @@
       <c r="D26" s="8" t="n">
         <v>63700</v>
       </c>
-      <c r="E26" s="8" t="n">
+      <c r="E26" s="9" t="n">
         <v>30700</v>
       </c>
       <c r="F26" s="9" t="n">
@@ -2060,7 +2060,7 @@
       <c r="D27" s="8" t="n">
         <v>64700</v>
       </c>
-      <c r="E27" s="8" t="n">
+      <c r="E27" s="9" t="n">
         <v>33000</v>
       </c>
       <c r="F27" s="9" t="n">
@@ -2117,7 +2117,7 @@
       <c r="D28" s="8" t="n">
         <v>65300</v>
       </c>
-      <c r="E28" s="8" t="n">
+      <c r="E28" s="9" t="n">
         <v>33300</v>
       </c>
       <c r="F28" s="9" t="n">
@@ -2174,7 +2174,7 @@
       <c r="D29" s="8" t="n">
         <v>66100</v>
       </c>
-      <c r="E29" s="8" t="n">
+      <c r="E29" s="9" t="n">
         <v>35300</v>
       </c>
       <c r="F29" s="9" t="n">
@@ -2231,7 +2231,7 @@
       <c r="D30" s="8" t="n">
         <v>66600</v>
       </c>
-      <c r="E30" s="8" t="n">
+      <c r="E30" s="9" t="n">
         <v>35800</v>
       </c>
       <c r="F30" s="9" t="n">
@@ -2288,7 +2288,7 @@
       <c r="D31" s="8" t="n">
         <v>66400</v>
       </c>
-      <c r="E31" s="8" t="n">
+      <c r="E31" s="9" t="n">
         <v>36900</v>
       </c>
       <c r="F31" s="9" t="n">
@@ -2345,7 +2345,7 @@
       <c r="D32" s="8" t="n">
         <v>71700</v>
       </c>
-      <c r="E32" s="8" t="n">
+      <c r="E32" s="9" t="n">
         <v>36750</v>
       </c>
       <c r="F32" s="9" t="n">
@@ -2402,7 +2402,7 @@
       <c r="D33" s="8" t="n">
         <v>74300</v>
       </c>
-      <c r="E33" s="8" t="n">
+      <c r="E33" s="9" t="n">
         <v>36750</v>
       </c>
       <c r="F33" s="9" t="n">
@@ -2459,7 +2459,7 @@
       <c r="D34" s="8" t="n">
         <v>73800</v>
       </c>
-      <c r="E34" s="8" t="n">
+      <c r="E34" s="9" t="n">
         <v>36750</v>
       </c>
       <c r="F34" s="9" t="n">
@@ -2516,7 +2516,7 @@
       <c r="D35" s="8" t="n">
         <v>72700</v>
       </c>
-      <c r="E35" s="8" t="n">
+      <c r="E35" s="9" t="n">
         <v>37200</v>
       </c>
       <c r="F35" s="9" t="n">
@@ -2573,7 +2573,7 @@
       <c r="D36" s="8" t="n">
         <v>72400</v>
       </c>
-      <c r="E36" s="8" t="n">
+      <c r="E36" s="9" t="n">
         <v>35900</v>
       </c>
       <c r="F36" s="9" t="n">
@@ -2630,7 +2630,7 @@
       <c r="D37" s="8" t="n">
         <v>72700</v>
       </c>
-      <c r="E37" s="8" t="n">
+      <c r="E37" s="9" t="n">
         <v>37300</v>
       </c>
       <c r="F37" s="9" t="n">
@@ -2687,7 +2687,7 @@
       <c r="D38" s="8" t="n">
         <v>74500</v>
       </c>
-      <c r="E38" s="8" t="n">
+      <c r="E38" s="9" t="n">
         <v>38200</v>
       </c>
       <c r="F38" s="9" t="n">
@@ -2744,7 +2744,7 @@
       <c r="D39" s="8" t="n">
         <v>72400</v>
       </c>
-      <c r="E39" s="8" t="n">
+      <c r="E39" s="9" t="n">
         <v>37950</v>
       </c>
       <c r="F39" s="9" t="n">
@@ -2801,7 +2801,7 @@
       <c r="D40" s="8" t="n">
         <v>72200</v>
       </c>
-      <c r="E40" s="8" t="n">
+      <c r="E40" s="9" t="n">
         <v>38400</v>
       </c>
       <c r="F40" s="9" t="n">
@@ -2858,7 +2858,7 @@
       <c r="D41" s="8" t="n">
         <v>72400</v>
       </c>
-      <c r="E41" s="8" t="n">
+      <c r="E41" s="9" t="n">
         <v>38400</v>
       </c>
       <c r="F41" s="9" t="n">
@@ -2915,7 +2915,7 @@
       <c r="D42" s="8" t="n">
         <v>72800</v>
       </c>
-      <c r="E42" s="8" t="n">
+      <c r="E42" s="9" t="n">
         <v>40050</v>
       </c>
       <c r="F42" s="9" t="n">
@@ -2972,7 +2972,7 @@
       <c r="D43" s="8" t="n">
         <v>72200</v>
       </c>
-      <c r="E43" s="8" t="n">
+      <c r="E43" s="9" t="n">
         <v>39800</v>
       </c>
       <c r="F43" s="9" t="n">
@@ -3029,7 +3029,7 @@
       <c r="D44" s="8" t="n">
         <v>73200</v>
       </c>
-      <c r="E44" s="8" t="n">
+      <c r="E44" s="9" t="n">
         <v>42100</v>
       </c>
       <c r="F44" s="9" t="n">
@@ -3088,7 +3088,7 @@
       <c r="D45" s="8" t="n">
         <v>72200</v>
       </c>
-      <c r="E45" s="8" t="n">
+      <c r="E45" s="9" t="n">
         <v>41900</v>
       </c>
       <c r="F45" s="9" t="n">
@@ -3145,7 +3145,7 @@
       <c r="D46" s="8" t="n">
         <v>72600</v>
       </c>
-      <c r="E46" s="8" t="n">
+      <c r="E46" s="9" t="n">
         <v>43100</v>
       </c>
       <c r="F46" s="9" t="n">
@@ -3202,7 +3202,7 @@
       <c r="D47" s="8" t="n">
         <v>70700</v>
       </c>
-      <c r="E47" s="8" t="n">
+      <c r="E47" s="9" t="n">
         <v>42650</v>
       </c>
       <c r="F47" s="9" t="n">
@@ -3259,7 +3259,7 @@
       <c r="D48" s="8" t="n">
         <v>71400</v>
       </c>
-      <c r="E48" s="8" t="n">
+      <c r="E48" s="9" t="n">
         <v>42650</v>
       </c>
       <c r="F48" s="9" t="n">
@@ -3316,7 +3316,7 @@
       <c r="D49" s="8" t="n">
         <v>72000</v>
       </c>
-      <c r="E49" s="8" t="n">
+      <c r="E49" s="9" t="n">
         <v>39900</v>
       </c>
       <c r="F49" s="9" t="n">
@@ -3373,7 +3373,7 @@
       <c r="D50" s="8" t="n">
         <v>69800</v>
       </c>
-      <c r="E50" s="8" t="n">
+      <c r="E50" s="9" t="n">
         <v>37300</v>
       </c>
       <c r="F50" s="9" t="n">
@@ -3430,7 +3430,7 @@
       <c r="D51" s="8" t="n">
         <v>68900</v>
       </c>
-      <c r="E51" s="8" t="n">
+      <c r="E51" s="9" t="n">
         <v>35700</v>
       </c>
       <c r="F51" s="9" t="n">
@@ -3487,7 +3487,7 @@
       <c r="D52" s="8" t="n">
         <v>69000</v>
       </c>
-      <c r="E52" s="8" t="n">
+      <c r="E52" s="9" t="n">
         <v>35050</v>
       </c>
       <c r="F52" s="9" t="n">
@@ -3544,7 +3544,7 @@
       <c r="D53" s="8" t="n">
         <v>68800</v>
       </c>
-      <c r="E53" s="8" t="n">
+      <c r="E53" s="9" t="n">
         <v>36200</v>
       </c>
       <c r="F53" s="9" t="n">
@@ -3601,7 +3601,7 @@
       <c r="D54" s="8" t="n">
         <v>68300</v>
       </c>
-      <c r="E54" s="8" t="n">
+      <c r="E54" s="9" t="n">
         <v>36500</v>
       </c>
       <c r="F54" s="9" t="n">
@@ -3658,7 +3658,7 @@
       <c r="D55" s="8" t="n">
         <v>69200</v>
       </c>
-      <c r="E55" s="8" t="n">
+      <c r="E55" s="9" t="n">
         <v>35300</v>
       </c>
       <c r="F55" s="9" t="n">
@@ -3715,7 +3715,7 @@
       <c r="D56" s="8" t="n">
         <v>70800</v>
       </c>
-      <c r="E56" s="8" t="n">
+      <c r="E56" s="9" t="n">
         <v>35050</v>
       </c>
       <c r="F56" s="9" t="n">
@@ -3772,7 +3772,7 @@
       <c r="D57" s="8" t="n">
         <v>71200</v>
       </c>
-      <c r="E57" s="8" t="n">
+      <c r="E57" s="9" t="n">
         <v>34850</v>
       </c>
       <c r="F57" s="9" t="n">
@@ -3829,7 +3829,7 @@
       <c r="D58" s="8" t="n">
         <v>71800</v>
       </c>
-      <c r="E58" s="8" t="n">
+      <c r="E58" s="9" t="n">
         <v>35950</v>
       </c>
       <c r="F58" s="9" t="n">
@@ -3886,7 +3886,7 @@
       <c r="D59" s="8" t="n">
         <v>70800</v>
       </c>
-      <c r="E59" s="8" t="n">
+      <c r="E59" s="9" t="n">
         <v>36000</v>
       </c>
       <c r="F59" s="9" t="n">
@@ -3943,7 +3943,7 @@
       <c r="D60" s="8" t="n">
         <v>70700</v>
       </c>
-      <c r="E60" s="8" t="n">
+      <c r="E60" s="9" t="n">
         <v>36450</v>
       </c>
       <c r="F60" s="9" t="n">
@@ -4000,7 +4000,7 @@
       <c r="D61" s="8" t="n">
         <v>70300</v>
       </c>
-      <c r="E61" s="8" t="n">
+      <c r="E61" s="9" t="n">
         <v>37900</v>
       </c>
       <c r="F61" s="9" t="n">
@@ -4057,7 +4057,7 @@
       <c r="D62" s="8" t="n">
         <v>71500</v>
       </c>
-      <c r="E62" s="8" t="n">
+      <c r="E62" s="9" t="n">
         <v>35450</v>
       </c>
       <c r="F62" s="9" t="n">
@@ -4114,7 +4114,7 @@
       <c r="D63" s="8" t="n">
         <v>71700</v>
       </c>
-      <c r="E63" s="8" t="n">
+      <c r="E63" s="9" t="n">
         <v>33150</v>
       </c>
       <c r="F63" s="9" t="n">
@@ -4171,7 +4171,7 @@
       <c r="D64" s="8" t="n">
         <v>67100</v>
       </c>
-      <c r="E64" s="8" t="n">
+      <c r="E64" s="9" t="n">
         <v>31000</v>
       </c>
       <c r="F64" s="9" t="n">
@@ -4230,7 +4230,7 @@
       <c r="D65" s="8" t="n">
         <v>67000</v>
       </c>
-      <c r="E65" s="8" t="n">
+      <c r="E65" s="9" t="n">
         <v>32500</v>
       </c>
       <c r="F65" s="9" t="n">
@@ -4287,7 +4287,7 @@
       <c r="D66" s="8" t="n">
         <v>65100</v>
       </c>
-      <c r="E66" s="8" t="n">
+      <c r="E66" s="9" t="n">
         <v>32750</v>
       </c>
       <c r="F66" s="9" t="n">
@@ -4344,7 +4344,7 @@
       <c r="D67" s="8" t="n">
         <v>63000</v>
       </c>
-      <c r="E67" s="8" t="n">
+      <c r="E67" s="9" t="n">
         <v>32650</v>
       </c>
       <c r="F67" s="9" t="n">
@@ -4401,7 +4401,7 @@
       <c r="D68" s="8" t="n">
         <v>62200</v>
       </c>
-      <c r="E68" s="8" t="n">
+      <c r="E68" s="9" t="n">
         <v>32900</v>
       </c>
       <c r="F68" s="9" t="n">
@@ -4458,7 +4458,7 @@
       <c r="D69" s="8" t="n">
         <v>62900</v>
       </c>
-      <c r="E69" s="8" t="n">
+      <c r="E69" s="9" t="n">
         <v>30750</v>
       </c>
       <c r="F69" s="9" t="n">
@@ -4515,7 +4515,7 @@
       <c r="D70" s="8" t="n">
         <v>64700</v>
       </c>
-      <c r="E70" s="8" t="n">
+      <c r="E70" s="9" t="n">
         <v>33050</v>
       </c>
       <c r="F70" s="9" t="n">
@@ -4572,7 +4572,7 @@
       <c r="D71" s="8" t="n">
         <v>64600</v>
       </c>
-      <c r="E71" s="8" t="n">
+      <c r="E71" s="9" t="n">
         <v>35500</v>
       </c>
       <c r="F71" s="9" t="n">
@@ -4629,7 +4629,7 @@
       <c r="D72" s="8" t="n">
         <v>64800</v>
       </c>
-      <c r="E72" s="8" t="n">
+      <c r="E72" s="9" t="n">
         <v>38150</v>
       </c>
       <c r="F72" s="9" t="n">
@@ -4686,7 +4686,7 @@
       <c r="D73" s="8" t="n">
         <v>67100</v>
       </c>
-      <c r="E73" s="8" t="n">
+      <c r="E73" s="9" t="n">
         <v>41000</v>
       </c>
       <c r="F73" s="9" t="n">
@@ -4743,7 +4743,7 @@
       <c r="D74" s="8" t="n">
         <v>67000</v>
       </c>
-      <c r="E74" s="8" t="n">
+      <c r="E74" s="9" t="n">
         <v>43000</v>
       </c>
       <c r="F74" s="9" t="n">
@@ -4800,7 +4800,7 @@
       <c r="D75" s="8" t="n">
         <v>68000</v>
       </c>
-      <c r="E75" s="8" t="n">
+      <c r="E75" s="9" t="n">
         <v>40900</v>
       </c>
       <c r="F75" s="9" t="n">
@@ -4857,7 +4857,7 @@
       <c r="D76" s="8" t="n">
         <v>66800</v>
       </c>
-      <c r="E76" s="8" t="n">
+      <c r="E76" s="9" t="n">
         <v>43650</v>
       </c>
       <c r="F76" s="9" t="n">
@@ -4914,7 +4914,7 @@
       <c r="D77" s="8" t="n">
         <v>70300</v>
       </c>
-      <c r="E77" s="8" t="n">
+      <c r="E77" s="9" t="n">
         <v>46900</v>
       </c>
       <c r="F77" s="9" t="n">
@@ -4971,7 +4971,7 @@
       <c r="D78" s="8" t="n">
         <v>70500</v>
       </c>
-      <c r="E78" s="8" t="n">
+      <c r="E78" s="9" t="n">
         <v>43850</v>
       </c>
       <c r="F78" s="9" t="n">
@@ -5028,7 +5028,7 @@
       <c r="D79" s="8" t="n">
         <v>70600</v>
       </c>
-      <c r="E79" s="8" t="n">
+      <c r="E79" s="9" t="n">
         <v>46600</v>
       </c>
       <c r="F79" s="9" t="n">
@@ -5085,7 +5085,7 @@
       <c r="D80" s="8" t="n">
         <v>72100</v>
       </c>
-      <c r="E80" s="8" t="n">
+      <c r="E80" s="9" t="n">
         <v>50000</v>
       </c>
       <c r="F80" s="9" t="n">
@@ -5142,7 +5142,7 @@
       <c r="D81" s="8" t="n">
         <v>72100</v>
       </c>
-      <c r="E81" s="8" t="n">
+      <c r="E81" s="9" t="n">
         <v>52000</v>
       </c>
       <c r="F81" s="9" t="n">
@@ -5199,7 +5199,7 @@
       <c r="D82" s="8" t="n">
         <v>73200</v>
       </c>
-      <c r="E82" s="8" t="n">
+      <c r="E82" s="9" t="n">
         <v>50800</v>
       </c>
       <c r="F82" s="9" t="n">
@@ -5256,7 +5256,7 @@
       <c r="D83" s="8" t="n">
         <v>73000</v>
       </c>
-      <c r="E83" s="8" t="n">
+      <c r="E83" s="9" t="n">
         <v>54600</v>
       </c>
       <c r="F83" s="9" t="n">
@@ -5313,7 +5313,7 @@
       <c r="D84" s="8" t="n">
         <v>72300</v>
       </c>
-      <c r="E84" s="8" t="n">
+      <c r="E84" s="9" t="n">
         <v>58700</v>
       </c>
       <c r="F84" s="9" t="n">
@@ -5370,7 +5370,7 @@
       <c r="D85" s="8" t="n">
         <v>72500</v>
       </c>
-      <c r="E85" s="8" t="n">
+      <c r="E85" s="9" t="n">
         <v>63100</v>
       </c>
       <c r="F85" s="9" t="n">
@@ -5427,7 +5427,7 @@
       <c r="D86" s="8" t="n">
         <v>72900</v>
       </c>
-      <c r="E86" s="8" t="n">
+      <c r="E86" s="9" t="n">
         <v>62700</v>
       </c>
       <c r="F86" s="9" t="n">
@@ -5484,7 +5484,7 @@
       <c r="D87" s="8" t="n">
         <v>70200</v>
       </c>
-      <c r="E87" s="8" t="n">
+      <c r="E87" s="9" t="n">
         <v>63000</v>
       </c>
       <c r="F87" s="9" t="n">
@@ -5543,7 +5543,7 @@
       <c r="D88" s="8" t="n">
         <v>70400</v>
       </c>
-      <c r="E88" s="8" t="n">
+      <c r="E88" s="9" t="n">
         <v>63200</v>
       </c>
       <c r="F88" s="9" t="n">
@@ -5600,7 +5600,7 @@
       <c r="D89" s="8" t="n">
         <v>70800</v>
       </c>
-      <c r="E89" s="8" t="n">
+      <c r="E89" s="9" t="n">
         <v>63500</v>
       </c>
       <c r="F89" s="9" t="n">
@@ -5657,7 +5657,7 @@
       <c r="D90" s="8" t="n">
         <v>71000</v>
       </c>
-      <c r="E90" s="8" t="n">
+      <c r="E90" s="9" t="n">
         <v>64100</v>
       </c>
       <c r="F90" s="9" t="n">
@@ -5714,7 +5714,7 @@
       <c r="D91" s="8" t="n">
         <v>70800</v>
       </c>
-      <c r="E91" s="8" t="n">
+      <c r="E91" s="9" t="n">
         <v>65500</v>
       </c>
       <c r="F91" s="9" t="n">
@@ -5771,7 +5771,7 @@
       <c r="D92" s="8" t="n">
         <v>70800</v>
       </c>
-      <c r="E92" s="8" t="n">
+      <c r="E92" s="9" t="n">
         <v>65200</v>
       </c>
       <c r="F92" s="9" t="n">
@@ -5828,7 +5828,7 @@
       <c r="D93" s="8" t="n">
         <v>70600</v>
       </c>
-      <c r="E93" s="8" t="n">
+      <c r="E93" s="9" t="n">
         <v>66000</v>
       </c>
       <c r="F93" s="9" t="n">
@@ -5885,7 +5885,7 @@
       <c r="D94" s="8" t="n">
         <v>71500</v>
       </c>
-      <c r="E94" s="8" t="n">
+      <c r="E94" s="9" t="n">
         <v>67100</v>
       </c>
       <c r="F94" s="9" t="n">
@@ -5942,7 +5942,7 @@
       <c r="D95" s="8" t="n">
         <v>71600</v>
       </c>
-      <c r="E95" s="8" t="n">
+      <c r="E95" s="9" t="n">
         <v>68000</v>
       </c>
       <c r="F95" s="9" t="n">
@@ -5999,7 +5999,7 @@
       <c r="D96" s="8" t="n">
         <v>72300</v>
       </c>
-      <c r="E96" s="8" t="n">
+      <c r="E96" s="9" t="n">
         <v>68000</v>
       </c>
       <c r="F96" s="9" t="n">
@@ -6056,7 +6056,7 @@
       <c r="D97" s="8" t="n">
         <v>73200</v>
       </c>
-      <c r="E97" s="8" t="n">
+      <c r="E97" s="9" t="n">
         <v>68200</v>
       </c>
       <c r="F97" s="9" t="n">
@@ -6113,7 +6113,7 @@
       <c r="D98" s="8" t="n">
         <v>73600</v>
       </c>
-      <c r="E98" s="8" t="n">
+      <c r="E98" s="9" t="n">
         <v>65000</v>
       </c>
       <c r="F98" s="9" t="n">
@@ -6170,7 +6170,7 @@
       <c r="D99" s="8" t="n">
         <v>73500</v>
       </c>
-      <c r="E99" s="8" t="n">
+      <c r="E99" s="9" t="n">
         <v>62000</v>
       </c>
       <c r="F99" s="9" t="n">
@@ -6227,7 +6227,7 @@
       <c r="D100" s="8" t="n">
         <v>73100</v>
       </c>
-      <c r="E100" s="8" t="n">
+      <c r="E100" s="9" t="n">
         <v>62000</v>
       </c>
       <c r="F100" s="9" t="n">
@@ -6284,7 +6284,7 @@
       <c r="D101" s="8" t="n">
         <v>74200</v>
       </c>
-      <c r="E101" s="8" t="n">
+      <c r="E101" s="9" t="n">
         <v>64000</v>
       </c>
       <c r="F101" s="9" t="n">
@@ -6341,7 +6341,7 @@
       <c r="D102" s="8" t="n">
         <v>73700</v>
       </c>
-      <c r="E102" s="8" t="n">
+      <c r="E102" s="9" t="n">
         <v>64800</v>
       </c>
       <c r="F102" s="9" t="n">
@@ -6398,7 +6398,7 @@
       <c r="D103" s="8" t="n">
         <v>72900</v>
       </c>
-      <c r="E103" s="8" t="n">
+      <c r="E103" s="9" t="n">
         <v>65100</v>
       </c>
       <c r="F103" s="9" t="n">
@@ -6455,7 +6455,7 @@
       <c r="D104" s="8" t="n">
         <v>75000</v>
       </c>
-      <c r="E104" s="8" t="n">
+      <c r="E104" s="9" t="n">
         <v>65700</v>
       </c>
       <c r="F104" s="9" t="n">
@@ -6512,7 +6512,7 @@
       <c r="D105" s="8" t="n">
         <v>76100</v>
       </c>
-      <c r="E105" s="8" t="n">
+      <c r="E105" s="9" t="n">
         <v>65000</v>
       </c>
       <c r="F105" s="9" t="n">
@@ -6569,7 +6569,7 @@
       <c r="D106" s="8" t="n">
         <v>76500</v>
       </c>
-      <c r="E106" s="8" t="n">
+      <c r="E106" s="9" t="n">
         <v>65400</v>
       </c>
       <c r="F106" s="9" t="n">
@@ -6626,7 +6626,7 @@
       <c r="D107" s="8" t="n">
         <v>74800</v>
       </c>
-      <c r="E107" s="8" t="n">
+      <c r="E107" s="9" t="n">
         <v>65000</v>
       </c>
       <c r="F107" s="9" t="n">
@@ -6683,7 +6683,7 @@
       <c r="D108" s="8" t="n">
         <v>72900</v>
       </c>
-      <c r="E108" s="8" t="n">
+      <c r="E108" s="9" t="n">
         <v>65800</v>
       </c>
       <c r="F108" s="9" t="n">
@@ -6740,7 +6740,7 @@
       <c r="D109" s="8" t="n">
         <v>71600</v>
       </c>
-      <c r="E109" s="8" t="n">
+      <c r="E109" s="9" t="n">
         <v>65800</v>
       </c>
       <c r="F109" s="9" t="n">
@@ -6799,7 +6799,7 @@
       <c r="D110" s="8" t="n">
         <v>71200</v>
       </c>
-      <c r="E110" s="8" t="n">
+      <c r="E110" s="9" t="n">
         <v>65900</v>
       </c>
       <c r="F110" s="9" t="n">
@@ -6856,7 +6856,7 @@
       <c r="D111" s="8" t="n">
         <v>72599.99999879659</v>
       </c>
-      <c r="E111" s="8" t="n">
+      <c r="E111" s="9" t="n">
         <v>65300</v>
       </c>
       <c r="F111" s="9" t="n">
@@ -6913,7 +6913,7 @@
       <c r="D112" s="8" t="n">
         <v>74500</v>
       </c>
-      <c r="E112" s="8" t="n">
+      <c r="E112" s="9" t="n">
         <v>65200</v>
       </c>
       <c r="F112" s="9" t="n">
@@ -6970,7 +6970,7 @@
       <c r="D113" s="8" t="n">
         <v>73500</v>
       </c>
-      <c r="E113" s="8" t="n">
+      <c r="E113" s="9" t="n">
         <v>64300</v>
       </c>
       <c r="F113" s="9" t="n">
@@ -7027,7 +7027,7 @@
       <c r="D114" s="8" t="n">
         <v>75100</v>
       </c>
-      <c r="E114" s="8" t="n">
+      <c r="E114" s="9" t="n">
         <v>65500</v>
       </c>
       <c r="F114" s="9" t="n">
@@ -7084,7 +7084,7 @@
       <c r="D115" s="8" t="n">
         <v>76500</v>
       </c>
-      <c r="E115" s="8" t="n">
+      <c r="E115" s="9" t="n">
         <v>65300</v>
       </c>
       <c r="F115" s="9" t="n">
@@ -7141,7 +7141,7 @@
       <c r="D116" s="8" t="n">
         <v>77700</v>
       </c>
-      <c r="E116" s="8" t="n">
+      <c r="E116" s="9" t="n">
         <v>65800</v>
       </c>
       <c r="F116" s="9" t="n">
@@ -7198,7 +7198,7 @@
       <c r="D117" s="8" t="n">
         <v>74500</v>
       </c>
-      <c r="E117" s="8" t="n">
+      <c r="E117" s="9" t="n">
         <v>65000</v>
       </c>
       <c r="F117" s="9" t="n">
@@ -7255,7 +7255,7 @@
       <c r="D118" s="8" t="n">
         <v>74900</v>
       </c>
-      <c r="E118" s="8" t="n">
+      <c r="E118" s="9" t="n">
         <v>64700</v>
       </c>
       <c r="F118" s="9" t="n">
@@ -7312,7 +7312,7 @@
       <c r="D119" s="8" t="n">
         <v>72900</v>
       </c>
-      <c r="E119" s="8" t="n">
+      <c r="E119" s="9" t="n">
         <v>67300</v>
       </c>
       <c r="F119" s="9" t="n">
@@ -7369,7 +7369,7 @@
       <c r="D120" s="8" t="n">
         <v>73900</v>
       </c>
-      <c r="E120" s="8" t="n">
+      <c r="E120" s="9" t="n">
         <v>69500</v>
       </c>
       <c r="F120" s="9" t="n">
@@ -7426,7 +7426,7 @@
       <c r="D121" s="8" t="n">
         <v>70700</v>
       </c>
-      <c r="E121" s="8" t="n">
+      <c r="E121" s="9" t="n">
         <v>69600</v>
       </c>
       <c r="F121" s="9" t="n">
@@ -7483,7 +7483,7 @@
       <c r="D122" s="8" t="n">
         <v>70600</v>
       </c>
-      <c r="E122" s="8" t="n">
+      <c r="E122" s="9" t="n">
         <v>69500</v>
       </c>
       <c r="F122" s="9" t="n">
@@ -7540,7 +7540,7 @@
       <c r="D123" s="8" t="n">
         <v>70000</v>
       </c>
-      <c r="E123" s="8" t="n">
+      <c r="E123" s="9" t="n">
         <v>69100</v>
       </c>
       <c r="F123" s="9" t="n">
@@ -7597,7 +7597,7 @@
       <c r="D124" s="8" t="n">
         <v>71900</v>
       </c>
-      <c r="E124" s="8" t="n">
+      <c r="E124" s="9" t="n">
         <v>70100</v>
       </c>
       <c r="F124" s="9" t="n">
@@ -7654,7 +7654,7 @@
       <c r="D125" s="8" t="n">
         <v>73000</v>
       </c>
-      <c r="E125" s="8" t="n">
+      <c r="E125" s="9" t="n">
         <v>69100</v>
       </c>
       <c r="F125" s="9" t="n">
@@ -7711,7 +7711,7 @@
       <c r="D126" s="8" t="n">
         <v>73300</v>
       </c>
-      <c r="E126" s="8" t="n">
+      <c r="E126" s="9" t="n">
         <v>68000</v>
       </c>
       <c r="F126" s="9" t="n">
@@ -7768,7 +7768,7 @@
       <c r="D127" s="8" t="n">
         <v>74300</v>
       </c>
-      <c r="E127" s="8" t="n">
+      <c r="E127" s="9" t="n">
         <v>67400</v>
       </c>
       <c r="F127" s="9" t="n">
@@ -7825,7 +7825,7 @@
       <c r="D128" s="8" t="n">
         <v>73700</v>
       </c>
-      <c r="E128" s="8" t="n">
+      <c r="E128" s="9" t="n">
         <v>68300</v>
       </c>
       <c r="F128" s="9" t="n">
@@ -7882,7 +7882,7 @@
       <c r="D129" s="8" t="n">
         <v>75500</v>
       </c>
-      <c r="E129" s="8" t="n">
+      <c r="E129" s="9" t="n">
         <v>67300</v>
       </c>
       <c r="F129" s="9" t="n">
@@ -7941,7 +7941,7 @@
       <c r="D130" s="8" t="n">
         <v>74400</v>
       </c>
-      <c r="E130" s="8" t="n">
+      <c r="E130" s="9" t="n">
         <v>67000</v>
       </c>
       <c r="F130" s="9" t="n">
@@ -7998,7 +7998,7 @@
       <c r="D131" s="8" t="n">
         <v>73400</v>
       </c>
-      <c r="E131" s="8" t="n">
+      <c r="E131" s="9" t="n">
         <v>70000</v>
       </c>
       <c r="F131" s="9" t="n">
@@ -8055,7 +8055,7 @@
       <c r="D132" s="8" t="n">
         <v>74300</v>
       </c>
-      <c r="E132" s="8" t="n">
+      <c r="E132" s="9" t="n">
         <v>71700</v>
       </c>
       <c r="F132" s="9" t="n">
@@ -8112,7 +8112,7 @@
       <c r="D133" s="8" t="n">
         <v>74600</v>
       </c>
-      <c r="E133" s="8" t="n">
+      <c r="E133" s="9" t="n">
         <v>73333.33333333333</v>
       </c>
       <c r="F133" s="9" t="n">
@@ -8169,7 +8169,7 @@
       <c r="D134" s="8" t="n">
         <v>75100</v>
       </c>
-      <c r="E134" s="8" t="n">
+      <c r="E134" s="9" t="n">
         <v>111900</v>
       </c>
       <c r="F134" s="9" t="n">
@@ -8226,7 +8226,7 @@
       <c r="D135" s="8" t="n">
         <v>76900</v>
       </c>
-      <c r="E135" s="8" t="n">
+      <c r="E135" s="9" t="n">
         <v>115000</v>
       </c>
       <c r="F135" s="9" t="n">
@@ -8283,7 +8283,7 @@
       <c r="D136" s="8" t="n">
         <v>76000</v>
       </c>
-      <c r="E136" s="8" t="n">
+      <c r="E136" s="9" t="n">
         <v>111000</v>
       </c>
       <c r="F136" s="9" t="n">
@@ -8340,7 +8340,7 @@
       <c r="D137" s="8" t="n">
         <v>74100</v>
       </c>
-      <c r="E137" s="8" t="n">
+      <c r="E137" s="9" t="n">
         <v>108900</v>
       </c>
       <c r="F137" s="9" t="n">
@@ -8397,7 +8397,7 @@
       <c r="D138" s="8" t="n">
         <v>75100</v>
       </c>
-      <c r="E138" s="8" t="n">
+      <c r="E138" s="9" t="n">
         <v>109200</v>
       </c>
       <c r="F138" s="9" t="n">
@@ -8454,7 +8454,7 @@
       <c r="D139" s="8" t="n">
         <v>76200</v>
       </c>
-      <c r="E139" s="8" t="n">
+      <c r="E139" s="9" t="n">
         <v>109500</v>
       </c>
       <c r="F139" s="9" t="n">
@@ -8511,7 +8511,7 @@
       <c r="D140" s="8" t="n">
         <v>76000</v>
       </c>
-      <c r="E140" s="8" t="n">
+      <c r="E140" s="9" t="n">
         <v>110000</v>
       </c>
       <c r="F140" s="9" t="n">
@@ -8568,7 +8568,7 @@
       <c r="D141" s="8" t="n">
         <v>77700</v>
       </c>
-      <c r="E141" s="8" t="n">
+      <c r="E141" s="9" t="n">
         <v>109000</v>
       </c>
       <c r="F141" s="9" t="n">
@@ -8625,7 +8625,7 @@
       <c r="D142" s="8" t="n">
         <v>78300</v>
       </c>
-      <c r="E142" s="8" t="n">
+      <c r="E142" s="9" t="n">
         <v>110000</v>
       </c>
       <c r="F142" s="9" t="n">
@@ -8682,7 +8682,7 @@
       <c r="D143" s="8" t="n">
         <v>79100</v>
       </c>
-      <c r="E143" s="8" t="n">
+      <c r="E143" s="9" t="n">
         <v>107000</v>
       </c>
       <c r="F143" s="9" t="n">
@@ -8739,7 +8739,7 @@
       <c r="D144" s="8" t="n">
         <v>74000</v>
       </c>
-      <c r="E144" s="8" t="n">
+      <c r="E144" s="9" t="n">
         <v>100000</v>
       </c>
       <c r="F144" s="9" t="n">
@@ -8796,7 +8796,7 @@
       <c r="D145" s="8" t="n">
         <v>73900</v>
       </c>
-      <c r="E145" s="8" t="n">
+      <c r="E145" s="9" t="n">
         <v>104600</v>
       </c>
       <c r="F145" s="9" t="n">
@@ -8853,7 +8853,7 @@
       <c r="D146" s="8" t="n">
         <v>74000</v>
       </c>
-      <c r="E146" s="8" t="n">
+      <c r="E146" s="9" t="n">
         <v>108800</v>
       </c>
       <c r="F146" s="9" t="n">
@@ -8910,7 +8910,7 @@
       <c r="D147" s="8" t="n">
         <v>74700</v>
       </c>
-      <c r="E147" s="8" t="n">
+      <c r="E147" s="9" t="n">
         <v>108900</v>
       </c>
       <c r="F147" s="9" t="n">
@@ -8967,7 +8967,7 @@
       <c r="D148" s="8" t="n">
         <v>75300</v>
       </c>
-      <c r="E148" s="8" t="n">
+      <c r="E148" s="9" t="n">
         <v>109300</v>
       </c>
       <c r="F148" s="9" t="n">
@@ -9024,7 +9024,7 @@
       <c r="D149" s="8" t="n">
         <v>74700</v>
       </c>
-      <c r="E149" s="8" t="n">
+      <c r="E149" s="9" t="n">
         <v>108000</v>
       </c>
       <c r="F149" s="9" t="n">
@@ -9083,7 +9083,7 @@
       <c r="D150" s="8" t="n">
         <v>74000</v>
       </c>
-      <c r="E150" s="8" t="n">
+      <c r="E150" s="9" t="n">
         <v>108000</v>
       </c>
       <c r="F150" s="9" t="n">
@@ -9140,7 +9140,7 @@
       <c r="D151" s="8" t="n">
         <v>76100</v>
       </c>
-      <c r="E151" s="8" t="n">
+      <c r="E151" s="9" t="n">
         <v>109900</v>
       </c>
       <c r="F151" s="9" t="n">
@@ -9197,7 +9197,7 @@
       <c r="D152" s="8" t="n">
         <v>74200</v>
       </c>
-      <c r="E152" s="8" t="n">
+      <c r="E152" s="9" t="n">
         <v>106000</v>
       </c>
       <c r="F152" s="9" t="n">
@@ -9254,7 +9254,7 @@
       <c r="D153" s="8" t="n">
         <v>77000</v>
       </c>
-      <c r="E153" s="8" t="n">
+      <c r="E153" s="9" t="n">
         <v>111000</v>
       </c>
       <c r="F153" s="9" t="n">
@@ -9311,7 +9311,7 @@
       <c r="D154" s="8" t="n">
         <v>75400</v>
       </c>
-      <c r="E154" s="8" t="n">
+      <c r="E154" s="9" t="n">
         <v>108500</v>
       </c>
       <c r="F154" s="9" t="n">
@@ -9368,7 +9368,7 @@
       <c r="D155" s="8" t="n">
         <v>73100</v>
       </c>
-      <c r="E155" s="8" t="n">
+      <c r="E155" s="9" t="n">
         <v>106300</v>
       </c>
       <c r="F155" s="9" t="n">
@@ -9425,7 +9425,7 @@
       <c r="D156" s="8" t="n">
         <v>74600</v>
       </c>
-      <c r="E156" s="8" t="n">
+      <c r="E156" s="9" t="n">
         <v>114200</v>
       </c>
       <c r="F156" s="9" t="n">
@@ -9482,7 +9482,7 @@
       <c r="D157" s="8" t="n">
         <v>76800</v>
       </c>
-      <c r="E157" s="8" t="n">
+      <c r="E157" s="9" t="n">
         <v>114900</v>
       </c>
       <c r="F157" s="9" t="n">
@@ -9539,7 +9539,7 @@
       <c r="D158" s="8" t="n">
         <v>78600</v>
       </c>
-      <c r="E158" s="8" t="n">
+      <c r="E158" s="9" t="n">
         <v>115000</v>
       </c>
       <c r="F158" s="9" t="n">
@@ -9596,7 +9596,7 @@
       <c r="D159" s="8" t="n">
         <v>79400</v>
       </c>
-      <c r="E159" s="8" t="n">
+      <c r="E159" s="9" t="n">
         <v>117700</v>
       </c>
       <c r="F159" s="9" t="n">
@@ -9653,7 +9653,7 @@
       <c r="D160" s="8" t="n">
         <v>78200</v>
       </c>
-      <c r="E160" s="8" t="n">
+      <c r="E160" s="9" t="n">
         <v>118000</v>
       </c>
       <c r="F160" s="9" t="n">
@@ -9710,7 +9710,7 @@
       <c r="D161" s="8" t="n">
         <v>77000</v>
       </c>
-      <c r="E161" s="8" t="n">
+      <c r="E161" s="9" t="n">
         <v>116900</v>
       </c>
       <c r="F161" s="9" t="n">
@@ -9767,7 +9767,7 @@
       <c r="D162" s="8" t="n">
         <v>77700</v>
       </c>
-      <c r="E162" s="8" t="n">
+      <c r="E162" s="9" t="n">
         <v>117900</v>
       </c>
       <c r="F162" s="9" t="n">
@@ -9824,7 +9824,7 @@
       <c r="D163" s="8" t="n">
         <v>80200</v>
       </c>
-      <c r="E163" s="8" t="n">
+      <c r="E163" s="9" t="n">
         <v>119000</v>
       </c>
       <c r="F163" s="9" t="n">
@@ -9881,7 +9881,7 @@
       <c r="D164" s="8" t="n">
         <v>79500</v>
       </c>
-      <c r="E164" s="8" t="n">
+      <c r="E164" s="9" t="n">
         <v>113500</v>
       </c>
       <c r="F164" s="9" t="n">
@@ -9938,7 +9938,7 @@
       <c r="D165" s="8" t="n">
         <v>75900</v>
       </c>
-      <c r="E165" s="8" t="n">
+      <c r="E165" s="9" t="n">
         <v>106500</v>
       </c>
       <c r="F165" s="9" t="n">
@@ -9995,7 +9995,7 @@
       <c r="D166" s="8" t="n">
         <v>81600</v>
       </c>
-      <c r="E166" s="8" t="n">
+      <c r="E166" s="9" t="n">
         <v>114500</v>
       </c>
       <c r="F166" s="9" t="n">
@@ -10052,7 +10052,7 @@
       <c r="D167" s="8" t="n">
         <v>84400</v>
       </c>
-      <c r="E167" s="8" t="n">
+      <c r="E167" s="9" t="n">
         <v>116000</v>
       </c>
       <c r="F167" s="9" t="n">
@@ -10109,7 +10109,7 @@
       <c r="D168" s="8" t="n">
         <v>85100</v>
       </c>
-      <c r="E168" s="8" t="n">
+      <c r="E168" s="9" t="n">
         <v>120900</v>
       </c>
       <c r="F168" s="9" t="n">
@@ -10166,7 +10166,7 @@
       <c r="D169" s="8" t="n">
         <v>87000</v>
       </c>
-      <c r="E169" s="8" t="n">
+      <c r="E169" s="9" t="n">
         <v>122000</v>
       </c>
       <c r="F169" s="9" t="n">
@@ -10223,7 +10223,7 @@
       <c r="D170" s="8" t="n">
         <v>89600</v>
       </c>
-      <c r="E170" s="8" t="n">
+      <c r="E170" s="9" t="n">
         <v>124500</v>
       </c>
       <c r="F170" s="9" t="n">
@@ -10280,7 +10280,7 @@
       <c r="D171" s="8" t="n">
         <v>92900</v>
       </c>
-      <c r="E171" s="8" t="n">
+      <c r="E171" s="9" t="n">
         <v>121900</v>
       </c>
       <c r="F171" s="9" t="n">
@@ -10339,7 +10339,7 @@
       <c r="D172" s="8" t="n">
         <v>90500</v>
       </c>
-      <c r="E172" s="8" t="n">
+      <c r="E172" s="9" t="n">
         <v>120000</v>
       </c>
       <c r="F172" s="9" t="n">
@@ -10396,7 +10396,7 @@
       <c r="D173" s="8" t="n">
         <v>89100</v>
       </c>
-      <c r="E173" s="8" t="n">
+      <c r="E173" s="9" t="n">
         <v>119500</v>
       </c>
       <c r="F173" s="9" t="n">
@@ -10453,7 +10453,7 @@
       <c r="D174" s="8" t="n">
         <v>92500</v>
       </c>
-      <c r="E174" s="8" t="n">
+      <c r="E174" s="9" t="n">
         <v>120500</v>
       </c>
       <c r="F174" s="9" t="n">
@@ -10510,7 +10510,7 @@
       <c r="D175" s="8" t="n">
         <v>94500</v>
       </c>
-      <c r="E175" s="8" t="n">
+      <c r="E175" s="9" t="n">
         <v>120200</v>
       </c>
       <c r="F175" s="9" t="n">
@@ -10567,7 +10567,7 @@
       <c r="D176" s="8" t="n">
         <v>96300</v>
       </c>
-      <c r="E176" s="8" t="n">
+      <c r="E176" s="9" t="n">
         <v>120000</v>
       </c>
       <c r="F176" s="9" t="n">
@@ -10624,7 +10624,7 @@
       <c r="D177" s="8" t="n">
         <v>98800</v>
       </c>
-      <c r="E177" s="8" t="n">
+      <c r="E177" s="9" t="n">
         <v>118500</v>
       </c>
       <c r="F177" s="9" t="n">
@@ -10681,7 +10681,7 @@
       <c r="D178" s="8" t="n">
         <v>98600</v>
       </c>
-      <c r="E178" s="8" t="n">
+      <c r="E178" s="9" t="n">
         <v>115900</v>
       </c>
       <c r="F178" s="9" t="n">
@@ -10738,7 +10738,7 @@
       <c r="D179" s="8" t="n">
         <v>97800</v>
       </c>
-      <c r="E179" s="8" t="n">
+      <c r="E179" s="9" t="n">
         <v>112900</v>
       </c>
       <c r="F179" s="9" t="n">
@@ -10795,7 +10795,7 @@
       <c r="D180" s="8" t="n">
         <v>99000</v>
       </c>
-      <c r="E180" s="8" t="n">
+      <c r="E180" s="9" t="n">
         <v>112900</v>
       </c>
       <c r="F180" s="9" t="n">
@@ -10852,7 +10852,7 @@
       <c r="D181" s="8" t="n">
         <v>97600</v>
       </c>
-      <c r="E181" s="8" t="n">
+      <c r="E181" s="9" t="n">
         <v>108900</v>
       </c>
       <c r="F181" s="9" t="n">
@@ -10909,7 +10909,7 @@
       <c r="D182" s="8" t="n">
         <v>99000</v>
       </c>
-      <c r="E182" s="8" t="n">
+      <c r="E182" s="9" t="n">
         <v>116200</v>
       </c>
       <c r="F182" s="9" t="n">
@@ -10966,7 +10966,7 @@
       <c r="D183" s="8" t="n">
         <v>101900</v>
       </c>
-      <c r="E183" s="8" t="n">
+      <c r="E183" s="9" t="n">
         <v>119700</v>
       </c>
       <c r="F183" s="9" t="n">
@@ -11023,7 +11023,7 @@
       <c r="D184" s="8" t="n">
         <v>103900</v>
       </c>
-      <c r="E184" s="8" t="n">
+      <c r="E184" s="9" t="n">
         <v>120000</v>
       </c>
       <c r="F184" s="9" t="n">
@@ -11080,7 +11080,7 @@
       <c r="D185" s="8" t="n">
         <v>104300</v>
       </c>
-      <c r="E185" s="8" t="n">
+      <c r="E185" s="9" t="n">
         <v>118200</v>
       </c>
       <c r="F185" s="9" t="n">
@@ -11137,7 +11137,7 @@
       <c r="D186" s="8" t="n">
         <v>104500</v>
       </c>
-      <c r="E186" s="8" t="n">
+      <c r="E186" s="9" t="n">
         <v>127000</v>
       </c>
       <c r="F186" s="9" t="n">
@@ -11196,7 +11196,7 @@
       <c r="D187" s="8" t="n">
         <v>106100</v>
       </c>
-      <c r="E187" s="8" t="n">
+      <c r="E187" s="9" t="n">
         <v>126500</v>
       </c>
       <c r="F187" s="9" t="n">
@@ -11253,7 +11253,7 @@
       <c r="D188" s="8" t="n">
         <v>104500</v>
       </c>
-      <c r="E188" s="8" t="n">
+      <c r="E188" s="9" t="n">
         <v>118500</v>
       </c>
       <c r="F188" s="9" t="n">
@@ -11310,7 +11310,7 @@
       <c r="D189" s="8" t="n">
         <v>102100</v>
       </c>
-      <c r="E189" s="8" t="n">
+      <c r="E189" s="9" t="n">
         <v>116000</v>
       </c>
       <c r="F189" s="9" t="n">
@@ -11367,7 +11367,7 @@
       <c r="D190" s="8" t="n">
         <v>98500</v>
       </c>
-      <c r="E190" s="8" t="n">
+      <c r="E190" s="9" t="n">
         <v>116800</v>
       </c>
       <c r="F190" s="9" t="n">
@@ -11424,7 +11424,7 @@
       <c r="D191" s="8" t="n">
         <v>101000</v>
       </c>
-      <c r="E191" s="8" t="n">
+      <c r="E191" s="9" t="n">
         <v>112400</v>
       </c>
       <c r="F191" s="9" t="n">
@@ -11481,7 +11481,7 @@
       <c r="D192" s="8" t="n">
         <v>103500</v>
       </c>
-      <c r="E192" s="8" t="n">
+      <c r="E192" s="9" t="n">
         <v>110400</v>
       </c>
       <c r="F192" s="9" t="n">
@@ -11538,7 +11538,7 @@
       <c r="D193" s="8" t="n">
         <v>105000</v>
       </c>
-      <c r="E193" s="8" t="n">
+      <c r="E193" s="9" t="n">
         <v>109900</v>
       </c>
       <c r="F193" s="9" t="n">
@@ -11595,7 +11595,7 @@
       <c r="D194" s="8" t="n">
         <v>104100</v>
       </c>
-      <c r="E194" s="8" t="n">
+      <c r="E194" s="9" t="n">
         <v>111900</v>
       </c>
       <c r="F194" s="9" t="n">
@@ -11652,7 +11652,7 @@
       <c r="D195" s="8" t="n">
         <v>105800</v>
       </c>
-      <c r="E195" s="8" t="n">
+      <c r="E195" s="9" t="n">
         <v>114200</v>
       </c>
       <c r="F195" s="9" t="n">
@@ -11709,7 +11709,7 @@
       <c r="D196" s="8" t="n">
         <v>105300</v>
       </c>
-      <c r="E196" s="8" t="n">
+      <c r="E196" s="9" t="n">
         <v>107700</v>
       </c>
       <c r="F196" s="9" t="n">
@@ -11766,7 +11766,7 @@
       <c r="D197" s="8" t="n">
         <v>98500</v>
       </c>
-      <c r="E197" s="8" t="n">
+      <c r="E197" s="9" t="n">
         <v>101500</v>
       </c>
       <c r="F197" s="9" t="n">
@@ -11823,7 +11823,7 @@
       <c r="D198" s="8" t="n">
         <v>99800</v>
       </c>
-      <c r="E198" s="8" t="n">
+      <c r="E198" s="9" t="n">
         <v>101500</v>
       </c>
       <c r="F198" s="9" t="n">
@@ -11880,7 +11880,7 @@
       <c r="D199" s="8" t="n">
         <v>98900</v>
       </c>
-      <c r="E199" s="8" t="n">
+      <c r="E199" s="9" t="n">
         <v>102900</v>
       </c>
       <c r="F199" s="9" t="n">
@@ -11937,7 +11937,7 @@
       <c r="D200" s="8" t="n">
         <v>99500</v>
       </c>
-      <c r="E200" s="8" t="n">
+      <c r="E200" s="9" t="n">
         <v>103200</v>
       </c>
       <c r="F200" s="9" t="n">
@@ -11994,7 +11994,7 @@
       <c r="D201" s="8" t="n">
         <v>97400</v>
       </c>
-      <c r="E201" s="8" t="n">
+      <c r="E201" s="9" t="n">
         <v>103000</v>
       </c>
       <c r="F201" s="9" t="n">
@@ -12051,7 +12051,7 @@
       <c r="D202" s="8" t="n">
         <v>96500</v>
       </c>
-      <c r="E202" s="8" t="n">
+      <c r="E202" s="9" t="n">
         <v>102999.9999963356</v>
       </c>
       <c r="F202" s="9" t="n">
@@ -12108,7 +12108,7 @@
       <c r="D203" s="8" t="n">
         <v>97500</v>
       </c>
-      <c r="E203" s="8" t="n">
+      <c r="E203" s="9" t="n">
         <v>102600</v>
       </c>
       <c r="F203" s="9" t="n">
@@ -12165,7 +12165,7 @@
       <c r="D204" s="8" t="n">
         <v>94000</v>
       </c>
-      <c r="E204" s="8" t="n">
+      <c r="E204" s="9" t="n">
         <v>98700</v>
       </c>
       <c r="F204" s="9" t="n">
@@ -12222,7 +12222,7 @@
       <c r="D205" s="8" t="n">
         <v>95000</v>
       </c>
-      <c r="E205" s="8" t="n">
+      <c r="E205" s="9" t="n">
         <v>98500</v>
       </c>
       <c r="F205" s="9" t="n">
@@ -12279,7 +12279,7 @@
       <c r="D206" s="8" t="n">
         <v>95800</v>
       </c>
-      <c r="E206" s="8" t="n">
+      <c r="E206" s="9" t="n">
         <v>97000</v>
       </c>
       <c r="F206" s="9" t="n">
@@ -12347,7 +12347,7 @@
       <c r="D207" s="8" t="n">
         <v>96500</v>
       </c>
-      <c r="E207" s="8" t="n">
+      <c r="E207" s="9" t="n">
         <v>96800</v>
       </c>
       <c r="F207" s="9" t="n">
@@ -12404,7 +12404,7 @@
       <c r="D208" s="8" t="n">
         <v>94300</v>
       </c>
-      <c r="E208" s="8" t="n">
+      <c r="E208" s="9" t="n">
         <v>96000</v>
       </c>
       <c r="F208" s="9" t="n">
@@ -12461,7 +12461,7 @@
       <c r="D209" s="8" t="n">
         <v>92500</v>
       </c>
-      <c r="E209" s="8" t="n">
+      <c r="E209" s="9" t="n">
         <v>95900</v>
       </c>
       <c r="F209" s="9" t="n">
@@ -12518,7 +12518,7 @@
       <c r="D210" s="8" t="n">
         <v>93000</v>
       </c>
-      <c r="E210" s="8" t="n">
+      <c r="E210" s="9" t="n">
         <v>95400</v>
       </c>
       <c r="F210" s="9" t="n">
@@ -12575,7 +12575,7 @@
       <c r="D211" s="8" t="n">
         <v>93600</v>
       </c>
-      <c r="E211" s="8" t="n">
+      <c r="E211" s="9" t="n">
         <v>95800</v>
       </c>
       <c r="F211" s="9" t="n">
@@ -12632,7 +12632,7 @@
       <c r="D212" s="8" t="n">
         <v>94000</v>
       </c>
-      <c r="E212" s="8" t="n">
+      <c r="E212" s="9" t="n">
         <v>93400</v>
       </c>
       <c r="F212" s="9" t="n">
@@ -12689,7 +12689,7 @@
       <c r="D213" s="8" t="n">
         <v>93700</v>
       </c>
-      <c r="E213" s="8" t="n">
+      <c r="E213" s="9" t="n">
         <v>93900</v>
       </c>
       <c r="F213" s="9" t="n">
@@ -12746,7 +12746,7 @@
       <c r="D214" s="8" t="n">
         <v>93900</v>
       </c>
-      <c r="E214" s="8" t="n">
+      <c r="E214" s="9" t="n">
         <v>92500</v>
       </c>
       <c r="F214" s="9" t="n">
@@ -12803,7 +12803,7 @@
       <c r="D215" s="8" t="n">
         <v>94400</v>
       </c>
-      <c r="E215" s="8" t="n">
+      <c r="E215" s="9" t="n">
         <v>91900</v>
       </c>
       <c r="F215" s="9" t="n">
@@ -12860,7 +12860,7 @@
       <c r="D216" s="8" t="n">
         <v>95900</v>
       </c>
-      <c r="E216" s="8" t="n">
+      <c r="E216" s="9" t="n">
         <v>92400</v>
       </c>
       <c r="F216" s="9" t="n">
@@ -12917,7 +12917,7 @@
       <c r="D217" s="8" t="n">
         <v>94900</v>
       </c>
-      <c r="E217" s="8" t="n">
+      <c r="E217" s="9" t="n">
         <v>92400</v>
       </c>
       <c r="F217" s="9" t="n">
@@ -12974,7 +12974,7 @@
       <c r="D218" s="8" t="n">
         <v>93800</v>
       </c>
-      <c r="E218" s="8" t="n">
+      <c r="E218" s="9" t="n">
         <v>90900</v>
       </c>
       <c r="F218" s="9" t="n">
@@ -13031,7 +13031,7 @@
       <c r="D219" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E219" s="8" t="n">
+      <c r="E219" s="9" t="n">
         <v>89800</v>
       </c>
       <c r="F219" s="9" t="n">
@@ -13088,7 +13088,7 @@
       <c r="D220" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E220" s="8" t="n">
+      <c r="E220" s="9" t="n">
         <v>88000</v>
       </c>
       <c r="F220" s="9" t="n">
@@ -13145,7 +13145,7 @@
       <c r="D221" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E221" s="8" t="n">
+      <c r="E221" s="9" t="n">
         <v>88100</v>
       </c>
       <c r="F221" s="9" t="n">
@@ -13202,7 +13202,7 @@
       <c r="D222" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E222" s="8" t="n">
+      <c r="E222" s="9" t="n">
         <v>88500</v>
       </c>
       <c r="F222" s="9" t="n">
@@ -13259,7 +13259,7 @@
       <c r="D223" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E223" s="8" t="n">
+      <c r="E223" s="9" t="n">
         <v>89400</v>
       </c>
       <c r="F223" s="9" t="n">
@@ -13316,7 +13316,7 @@
       <c r="D224" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E224" s="8" t="n">
+      <c r="E224" s="9" t="n">
         <v>91600</v>
       </c>
       <c r="F224" s="9" t="n">
@@ -13373,7 +13373,7 @@
       <c r="D225" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E225" s="8" t="n">
+      <c r="E225" s="9" t="n">
         <v>90300</v>
       </c>
       <c r="F225" s="9" t="n">
@@ -13430,7 +13430,7 @@
       <c r="D226" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E226" s="8" t="n">
+      <c r="E226" s="9" t="n">
         <v>91400</v>
       </c>
       <c r="F226" s="9" t="n">
@@ -13487,7 +13487,7 @@
       <c r="D227" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E227" s="8" t="n">
+      <c r="E227" s="9" t="n">
         <v>91600</v>
       </c>
       <c r="F227" s="9" t="n">
@@ -13544,7 +13544,7 @@
       <c r="D228" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E228" s="8" t="n">
+      <c r="E228" s="9" t="n">
         <v>91600</v>
       </c>
       <c r="F228" s="9" t="n">
@@ -13601,7 +13601,7 @@
       <c r="D229" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E229" s="8" t="n">
+      <c r="E229" s="9" t="n">
         <v>91000</v>
       </c>
       <c r="F229" s="9" t="n">
@@ -13660,7 +13660,7 @@
       <c r="D230" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E230" s="8" t="n">
+      <c r="E230" s="9" t="n">
         <v>90200</v>
       </c>
       <c r="F230" s="9" t="n">
@@ -13717,7 +13717,7 @@
       <c r="D231" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E231" s="8" t="n">
+      <c r="E231" s="9" t="n">
         <v>87200</v>
       </c>
       <c r="F231" s="9" t="n">
@@ -13774,7 +13774,7 @@
       <c r="D232" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E232" s="8" t="n">
+      <c r="E232" s="9" t="n">
         <v>87000</v>
       </c>
       <c r="F232" s="9" t="n">
@@ -13831,7 +13831,7 @@
       <c r="D233" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E233" s="8" t="n">
+      <c r="E233" s="9" t="n">
         <v>87500</v>
       </c>
       <c r="F233" s="9" t="n">
@@ -13888,7 +13888,7 @@
       <c r="D234" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E234" s="8" t="n">
+      <c r="E234" s="9" t="n">
         <v>87100</v>
       </c>
       <c r="F234" s="9" t="n">
@@ -13945,7 +13945,7 @@
       <c r="D235" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E235" s="8" t="n">
+      <c r="E235" s="9" t="n">
         <v>87800</v>
       </c>
       <c r="F235" s="9" t="n">
@@ -14002,7 +14002,7 @@
       <c r="D236" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E236" s="8" t="n">
+      <c r="E236" s="9" t="n">
         <v>89300</v>
       </c>
       <c r="F236" s="9" t="n">
@@ -14059,7 +14059,7 @@
       <c r="D237" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E237" s="8" t="n">
+      <c r="E237" s="9" t="n">
         <v>89400</v>
       </c>
       <c r="F237" s="9" t="n">
@@ -14116,7 +14116,7 @@
       <c r="D238" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E238" s="8" t="n">
+      <c r="E238" s="9" t="n">
         <v>89800</v>
       </c>
       <c r="F238" s="9" t="n">
@@ -14173,7 +14173,7 @@
       <c r="D239" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E239" s="8" t="n">
+      <c r="E239" s="9" t="n">
         <v>90000</v>
       </c>
       <c r="F239" s="9" t="n">
@@ -14230,7 +14230,7 @@
       <c r="D240" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E240" s="8" t="n">
+      <c r="E240" s="9" t="n">
         <v>90300</v>
       </c>
       <c r="F240" s="9" t="n">
@@ -14287,7 +14287,7 @@
       <c r="D241" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E241" s="8" t="n">
+      <c r="E241" s="9" t="n">
         <v>89400</v>
       </c>
       <c r="F241" s="9" t="n">
@@ -14344,7 +14344,7 @@
       <c r="D242" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E242" s="8" t="n">
+      <c r="E242" s="9" t="n">
         <v>89100</v>
       </c>
       <c r="F242" s="9" t="n">
@@ -14401,7 +14401,7 @@
       <c r="D243" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E243" s="8" t="n">
+      <c r="E243" s="9" t="n">
         <v>87000</v>
       </c>
       <c r="F243" s="9" t="n">
@@ -14458,7 +14458,7 @@
       <c r="D244" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E244" s="8" t="n">
+      <c r="E244" s="9" t="n">
         <v>87500</v>
       </c>
       <c r="F244" s="9" t="n">
@@ -14515,7 +14515,7 @@
       <c r="D245" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E245" s="8" t="n">
+      <c r="E245" s="9" t="n">
         <v>90000</v>
       </c>
       <c r="F245" s="9" t="n">
@@ -14572,7 +14572,7 @@
       <c r="D246" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E246" s="8" t="n">
+      <c r="E246" s="9" t="n">
         <v>91400</v>
       </c>
       <c r="F246" s="9" t="n">
@@ -14629,7 +14629,7 @@
       <c r="D247" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E247" s="8" t="n">
+      <c r="E247" s="9" t="n">
         <v>90000</v>
       </c>
       <c r="F247" s="9" t="n">
@@ -14686,7 +14686,7 @@
       <c r="D248" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E248" s="8" t="n">
+      <c r="E248" s="9" t="n">
         <v>92900</v>
       </c>
       <c r="F248" s="9" t="n">
@@ -14743,7 +14743,7 @@
       <c r="D249" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E249" s="8" t="n">
+      <c r="E249" s="9" t="n">
         <v>94600</v>
       </c>
       <c r="F249" s="9" t="n">
@@ -14802,7 +14802,7 @@
       <c r="D250" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E250" s="8" t="n">
+      <c r="E250" s="9" t="n">
         <v>94600</v>
       </c>
       <c r="F250" s="9" t="n">
@@ -14859,7 +14859,7 @@
       <c r="D251" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E251" s="8" t="n">
+      <c r="E251" s="9" t="n">
         <v>95500</v>
       </c>
       <c r="F251" s="9" t="n">
@@ -14916,7 +14916,7 @@
       <c r="D252" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E252" s="8" t="n">
+      <c r="E252" s="9" t="n">
         <v>94900</v>
       </c>
       <c r="F252" s="9" t="n">
@@ -14973,7 +14973,7 @@
       <c r="D253" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E253" s="8" t="n">
+      <c r="E253" s="9" t="n">
         <v>93500</v>
       </c>
       <c r="F253" s="9" t="n">
@@ -15030,7 +15030,7 @@
       <c r="D254" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E254" s="8" t="n">
+      <c r="E254" s="9" t="n">
         <v>95000</v>
       </c>
       <c r="F254" s="9" t="n">
@@ -15087,7 +15087,7 @@
       <c r="D255" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E255" s="8" t="n">
+      <c r="E255" s="9" t="n">
         <v>92300</v>
       </c>
       <c r="F255" s="9" t="n">
@@ -15144,7 +15144,7 @@
       <c r="D256" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E256" s="8" t="n">
+      <c r="E256" s="9" t="n">
         <v>87700</v>
       </c>
       <c r="F256" s="9" t="n">
@@ -15201,7 +15201,7 @@
       <c r="D257" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E257" s="8" t="n">
+      <c r="E257" s="9" t="n">
         <v>86900</v>
       </c>
       <c r="F257" s="9" t="n">
@@ -15258,7 +15258,7 @@
       <c r="D258" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E258" s="8" t="n">
+      <c r="E258" s="9" t="n">
         <v>83900</v>
       </c>
       <c r="F258" s="9" t="n">
@@ -15315,7 +15315,7 @@
       <c r="D259" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E259" s="8" t="n">
+      <c r="E259" s="9" t="n">
         <v>90100</v>
       </c>
       <c r="F259" s="9" t="n">
@@ -15372,7 +15372,7 @@
       <c r="D260" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E260" s="8" t="n">
+      <c r="E260" s="9" t="n">
         <v>92100</v>
       </c>
       <c r="F260" s="9" t="n">
@@ -15429,7 +15429,7 @@
       <c r="D261" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E261" s="8" t="n">
+      <c r="E261" s="9" t="n">
         <v>86100</v>
       </c>
       <c r="F261" s="9" t="n">
@@ -15486,7 +15486,7 @@
       <c r="D262" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E262" s="8" t="n">
+      <c r="E262" s="9" t="n">
         <v>84700</v>
       </c>
       <c r="F262" s="9" t="n">
@@ -15543,7 +15543,7 @@
       <c r="D263" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E263" s="8" t="n">
+      <c r="E263" s="9" t="n">
         <v>84900</v>
       </c>
       <c r="F263" s="9" t="n">
@@ -15600,7 +15600,7 @@
       <c r="D264" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E264" s="8" t="n">
+      <c r="E264" s="9" t="n">
         <v>85000</v>
       </c>
       <c r="F264" s="9" t="n">
@@ -15657,7 +15657,7 @@
       <c r="D265" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E265" s="8" t="n">
+      <c r="E265" s="9" t="n">
         <v>85000</v>
       </c>
       <c r="F265" s="9" t="n">
@@ -15714,7 +15714,7 @@
       <c r="D266" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E266" s="8" t="n">
+      <c r="E266" s="9" t="n">
         <v>84000</v>
       </c>
       <c r="F266" s="9" t="n">
@@ -15771,7 +15771,7 @@
       <c r="D267" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E267" s="8" t="n">
+      <c r="E267" s="9" t="n">
         <v>84900</v>
       </c>
       <c r="F267" s="9" t="n">
@@ -15828,7 +15828,7 @@
       <c r="D268" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E268" s="8" t="n">
+      <c r="E268" s="9" t="n">
         <v>84200</v>
       </c>
       <c r="F268" s="9" t="n">
@@ -15885,7 +15885,7 @@
       <c r="D269" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E269" s="8" t="n">
+      <c r="E269" s="9" t="n">
         <v>83000</v>
       </c>
       <c r="F269" s="9" t="n">
@@ -15942,7 +15942,7 @@
       <c r="D270" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E270" s="8" t="n">
+      <c r="E270" s="9" t="n">
         <v>83100</v>
       </c>
       <c r="F270" s="9" t="n">
@@ -15999,7 +15999,7 @@
       <c r="D271" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E271" s="8" t="n">
+      <c r="E271" s="9" t="n">
         <v>83400</v>
       </c>
       <c r="F271" s="9" t="n">
@@ -16056,7 +16056,7 @@
       <c r="D272" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E272" s="8" t="n">
+      <c r="E272" s="9" t="n">
         <v>83100</v>
       </c>
       <c r="F272" s="9" t="n">
@@ -16115,7 +16115,7 @@
       <c r="D273" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E273" s="8" t="n">
+      <c r="E273" s="9" t="n">
         <v>83500</v>
       </c>
       <c r="F273" s="9" t="n">
@@ -16172,7 +16172,7 @@
       <c r="D274" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E274" s="8" t="n">
+      <c r="E274" s="9" t="n">
         <v>84700</v>
       </c>
       <c r="F274" s="9" t="n">
@@ -16229,7 +16229,7 @@
       <c r="D275" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E275" s="8" t="n">
+      <c r="E275" s="9" t="n">
         <v>86200</v>
       </c>
       <c r="F275" s="9" t="n">
@@ -16286,7 +16286,7 @@
       <c r="D276" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E276" s="8" t="n">
+      <c r="E276" s="9" t="n">
         <v>87600</v>
       </c>
       <c r="F276" s="9" t="n">
@@ -16343,7 +16343,7 @@
       <c r="D277" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E277" s="8" t="n">
+      <c r="E277" s="9" t="n">
         <v>87900</v>
       </c>
       <c r="F277" s="9" t="n">
@@ -16400,7 +16400,7 @@
       <c r="D278" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E278" s="8" t="n">
+      <c r="E278" s="9" t="n">
         <v>87900</v>
       </c>
       <c r="F278" s="9" t="n">
@@ -16457,7 +16457,7 @@
       <c r="D279" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E279" s="8" t="n">
+      <c r="E279" s="9" t="n">
         <v>88500</v>
       </c>
       <c r="F279" s="9" t="n">
@@ -16514,7 +16514,7 @@
       <c r="D280" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E280" s="8" t="n">
+      <c r="E280" s="9" t="n">
         <v>88100</v>
       </c>
       <c r="F280" s="9" t="n">
@@ -16571,7 +16571,7 @@
       <c r="D281" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E281" s="8" t="n">
+      <c r="E281" s="9" t="n">
         <v>87100</v>
       </c>
       <c r="F281" s="9" t="n">
@@ -16628,7 +16628,7 @@
       <c r="D282" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E282" s="8" t="n">
+      <c r="E282" s="9" t="n">
         <v>88700</v>
       </c>
       <c r="F282" s="9" t="n">
@@ -16685,7 +16685,7 @@
       <c r="D283" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E283" s="8" t="n">
+      <c r="E283" s="9" t="n">
         <v>88200</v>
       </c>
       <c r="F283" s="9" t="n">
@@ -16742,7 +16742,7 @@
       <c r="D284" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E284" s="8" t="n">
+      <c r="E284" s="9" t="n">
         <v>88000</v>
       </c>
       <c r="F284" s="9" t="n">
@@ -16799,7 +16799,7 @@
       <c r="D285" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E285" s="8" t="n">
+      <c r="E285" s="9" t="n">
         <v>86200</v>
       </c>
       <c r="F285" s="9" t="n">
@@ -16856,7 +16856,7 @@
       <c r="D286" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E286" s="8" t="n">
+      <c r="E286" s="9" t="n">
         <v>86200</v>
       </c>
       <c r="F286" s="9" t="n">
@@ -16913,7 +16913,7 @@
       <c r="D287" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E287" s="8" t="n">
+      <c r="E287" s="9" t="n">
         <v>85700</v>
       </c>
       <c r="F287" s="9" t="n">
@@ -16970,7 +16970,7 @@
       <c r="D288" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E288" s="8" t="n">
+      <c r="E288" s="9" t="n">
         <v>84800</v>
       </c>
       <c r="F288" s="9" t="n">
@@ -17027,7 +17027,7 @@
       <c r="D289" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E289" s="8" t="n">
+      <c r="E289" s="9" t="n">
         <v>87200</v>
       </c>
       <c r="F289" s="9" t="n">
@@ -17084,7 +17084,7 @@
       <c r="D290" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E290" s="8" t="n">
+      <c r="E290" s="9" t="n">
         <v>88400</v>
       </c>
       <c r="F290" s="9" t="n">
@@ -17141,7 +17141,7 @@
       <c r="D291" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E291" s="8" t="n">
+      <c r="E291" s="9" t="n">
         <v>86300</v>
       </c>
       <c r="F291" s="9" t="n">
@@ -17198,7 +17198,7 @@
       <c r="D292" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E292" s="8" t="n">
+      <c r="E292" s="9" t="n">
         <v>85600</v>
       </c>
       <c r="F292" s="9" t="n">
@@ -17257,7 +17257,7 @@
       <c r="D293" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E293" s="8" t="n">
+      <c r="E293" s="9" t="n">
         <v>85600</v>
       </c>
       <c r="F293" s="9" t="n">
@@ -17314,7 +17314,7 @@
       <c r="D294" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E294" s="8" t="n">
+      <c r="E294" s="9" t="n">
         <v>85300</v>
       </c>
       <c r="F294" s="9" t="n">
@@ -17371,7 +17371,7 @@
       <c r="D295" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E295" s="8" t="n">
+      <c r="E295" s="9" t="n">
         <v>84200</v>
       </c>
       <c r="F295" s="9" t="n">
@@ -17428,7 +17428,7 @@
       <c r="D296" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E296" s="8" t="n">
+      <c r="E296" s="9" t="n">
         <v>83500</v>
       </c>
       <c r="F296" s="9" t="n">
@@ -17485,7 +17485,7 @@
       <c r="D297" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E297" s="8" t="n">
+      <c r="E297" s="9" t="n">
         <v>84800</v>
       </c>
       <c r="F297" s="9" t="n">
@@ -17542,7 +17542,7 @@
       <c r="D298" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E298" s="8" t="n">
+      <c r="E298" s="9" t="n">
         <v>85600</v>
       </c>
       <c r="F298" s="9" t="n">
@@ -17599,7 +17599,7 @@
       <c r="D299" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E299" s="8" t="n">
+      <c r="E299" s="9" t="n">
         <v>85300</v>
       </c>
       <c r="F299" s="9" t="n">
@@ -17656,7 +17656,7 @@
       <c r="D300" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E300" s="8" t="n">
+      <c r="E300" s="9" t="n">
         <v>84900</v>
       </c>
       <c r="F300" s="9" t="n">
@@ -17713,7 +17713,7 @@
       <c r="D301" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E301" s="8" t="n">
+      <c r="E301" s="9" t="n">
         <v>85000</v>
       </c>
       <c r="F301" s="9" t="n">
@@ -17770,7 +17770,7 @@
       <c r="D302" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E302" s="8" t="n">
+      <c r="E302" s="9" t="n">
         <v>86200</v>
       </c>
       <c r="F302" s="9" t="n">
@@ -17827,7 +17827,7 @@
       <c r="D303" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E303" s="8" t="n">
+      <c r="E303" s="9" t="n">
         <v>88000</v>
       </c>
       <c r="F303" s="9" t="n">
@@ -17884,7 +17884,7 @@
       <c r="D304" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E304" s="8" t="n">
+      <c r="E304" s="9" t="n">
         <v>88000</v>
       </c>
       <c r="F304" s="9" t="n">
@@ -17941,7 +17941,7 @@
       <c r="D305" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E305" s="8" t="n">
+      <c r="E305" s="9" t="n">
         <v>87500</v>
       </c>
       <c r="F305" s="9" t="n">
@@ -17998,7 +17998,7 @@
       <c r="D306" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E306" s="8" t="n">
+      <c r="E306" s="9" t="n">
         <v>86500</v>
       </c>
       <c r="F306" s="9" t="n">
@@ -18055,7 +18055,7 @@
       <c r="D307" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E307" s="8" t="n">
+      <c r="E307" s="9" t="n">
         <v>85800</v>
       </c>
       <c r="F307" s="9" t="n">
@@ -18112,7 +18112,7 @@
       <c r="D308" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E308" s="8" t="n">
+      <c r="E308" s="9" t="n">
         <v>86400</v>
       </c>
       <c r="F308" s="9" t="n">
@@ -18169,7 +18169,7 @@
       <c r="D309" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E309" s="8" t="n">
+      <c r="E309" s="9" t="n">
         <v>86300</v>
       </c>
       <c r="F309" s="9" t="n">
@@ -18226,7 +18226,7 @@
       <c r="D310" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E310" s="8" t="n">
+      <c r="E310" s="9" t="n">
         <v>85500</v>
       </c>
       <c r="F310" s="9" t="n">
@@ -18283,7 +18283,7 @@
       <c r="D311" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E311" s="8" t="n">
+      <c r="E311" s="9" t="n">
         <v>86500</v>
       </c>
       <c r="F311" s="9" t="n">
@@ -18340,7 +18340,7 @@
       <c r="D312" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E312" s="8" t="n">
+      <c r="E312" s="9" t="n">
         <v>90300</v>
       </c>
       <c r="F312" s="9" t="n">
@@ -18397,7 +18397,7 @@
       <c r="D313" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E313" s="8" t="n">
+      <c r="E313" s="9" t="n">
         <v>84400</v>
       </c>
       <c r="F313" s="9" t="n">
@@ -18456,7 +18456,7 @@
       <c r="D314" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E314" s="8" t="n">
+      <c r="E314" s="9" t="n">
         <v>85500</v>
       </c>
       <c r="F314" s="9" t="n">
@@ -18513,7 +18513,7 @@
       <c r="D315" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E315" s="8" t="n">
+      <c r="E315" s="9" t="n">
         <v>84300</v>
       </c>
       <c r="F315" s="9" t="n">
@@ -18570,7 +18570,7 @@
       <c r="D316" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E316" s="8" t="n">
+      <c r="E316" s="9" t="n">
         <v>86000</v>
       </c>
       <c r="F316" s="9" t="n">
@@ -18627,7 +18627,7 @@
       <c r="D317" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E317" s="8" t="n">
+      <c r="E317" s="9" t="n">
         <v>86400</v>
       </c>
       <c r="F317" s="9" t="n">
@@ -18684,7 +18684,7 @@
       <c r="D318" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E318" s="8" t="n">
+      <c r="E318" s="9" t="n">
         <v>86000</v>
       </c>
       <c r="F318" s="9" t="n">
@@ -18741,7 +18741,7 @@
       <c r="D319" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E319" s="8" t="n">
+      <c r="E319" s="9" t="n">
         <v>86000</v>
       </c>
       <c r="F319" s="9" t="n">
@@ -18798,7 +18798,7 @@
       <c r="D320" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E320" s="8" t="n">
+      <c r="E320" s="9" t="n">
         <v>85900</v>
       </c>
       <c r="F320" s="9" t="n">
@@ -18855,7 +18855,7 @@
       <c r="D321" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E321" s="8" t="n">
+      <c r="E321" s="9" t="n">
         <v>85000</v>
       </c>
       <c r="F321" s="9" t="n">
@@ -18912,7 +18912,7 @@
       <c r="D322" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E322" s="8" t="n">
+      <c r="E322" s="9" t="n">
         <v>86200</v>
       </c>
       <c r="F322" s="9" t="n">
@@ -18969,7 +18969,7 @@
       <c r="D323" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E323" s="8" t="n">
+      <c r="E323" s="9" t="n">
         <v>86300</v>
       </c>
       <c r="F323" s="9" t="n">
@@ -19026,7 +19026,7 @@
       <c r="D324" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E324" s="8" t="n">
+      <c r="E324" s="9" t="n">
         <v>88000</v>
       </c>
       <c r="F324" s="9" t="n">
@@ -19083,7 +19083,7 @@
       <c r="D325" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E325" s="8" t="n">
+      <c r="E325" s="9" t="n">
         <v>86700</v>
       </c>
       <c r="F325" s="9" t="n">
@@ -19140,7 +19140,7 @@
       <c r="D326" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E326" s="8" t="n">
+      <c r="E326" s="9" t="n">
         <v>87600</v>
       </c>
       <c r="F326" s="9" t="n">
@@ -19197,7 +19197,7 @@
       <c r="D327" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E327" s="8" t="n">
+      <c r="E327" s="9" t="n">
         <v>83200</v>
       </c>
       <c r="F327" s="9" t="n">
@@ -19254,7 +19254,7 @@
       <c r="D328" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E328" s="8" t="n">
+      <c r="E328" s="9" t="n">
         <v>82300</v>
       </c>
       <c r="F328" s="9" t="n">
@@ -19311,7 +19311,7 @@
       <c r="D329" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E329" s="8" t="n">
+      <c r="E329" s="9" t="n">
         <v>82800</v>
       </c>
       <c r="F329" s="9" t="n">
@@ -19368,7 +19368,7 @@
       <c r="D330" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E330" s="8" t="n">
+      <c r="E330" s="9" t="n">
         <v>82300</v>
       </c>
       <c r="F330" s="9" t="n">
@@ -19425,7 +19425,7 @@
       <c r="D331" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E331" s="8" t="n">
+      <c r="E331" s="9" t="n">
         <v>82500</v>
       </c>
       <c r="F331" s="9" t="n">
@@ -19482,7 +19482,7 @@
       <c r="D332" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E332" s="8" t="n">
+      <c r="E332" s="9" t="n">
         <v>82700</v>
       </c>
       <c r="F332" s="9" t="n">
@@ -19539,7 +19539,7 @@
       <c r="D333" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E333" s="8" t="n">
+      <c r="E333" s="9" t="n">
         <v>82500</v>
       </c>
       <c r="F333" s="9" t="n">
@@ -19596,7 +19596,7 @@
       <c r="D334" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E334" s="8" t="n">
+      <c r="E334" s="9" t="n">
         <v>82900</v>
       </c>
       <c r="F334" s="9" t="n">
@@ -19653,7 +19653,7 @@
       <c r="D335" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E335" s="8" t="n">
+      <c r="E335" s="9" t="n">
         <v>83400</v>
       </c>
       <c r="F335" s="9" t="n">
@@ -19710,7 +19710,7 @@
       <c r="D336" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E336" s="8" t="n">
+      <c r="E336" s="9" t="n">
         <v>83100</v>
       </c>
       <c r="F336" s="9" t="n">
@@ -19769,7 +19769,7 @@
       <c r="D337" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E337" s="8" t="n">
+      <c r="E337" s="9" t="n">
         <v>81900</v>
       </c>
       <c r="F337" s="9" t="n">
@@ -19826,7 +19826,7 @@
       <c r="D338" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E338" s="8" t="n">
+      <c r="E338" s="9" t="n">
         <v>80900</v>
       </c>
       <c r="F338" s="9" t="n">
@@ -19883,7 +19883,7 @@
       <c r="D339" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E339" s="8" t="n">
+      <c r="E339" s="9" t="n">
         <v>79600</v>
       </c>
       <c r="F339" s="9" t="n">
@@ -19940,7 +19940,7 @@
       <c r="D340" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E340" s="8" t="n">
+      <c r="E340" s="9" t="n">
         <v>80200</v>
       </c>
       <c r="F340" s="9" t="n">
@@ -19997,7 +19997,7 @@
       <c r="D341" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E341" s="8" t="n">
+      <c r="E341" s="9" t="n">
         <v>80500</v>
       </c>
       <c r="F341" s="9" t="n">
@@ -20054,7 +20054,7 @@
       <c r="D342" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E342" s="8" t="n">
+      <c r="E342" s="9" t="n">
         <v>79600</v>
       </c>
       <c r="F342" s="9" t="n">
@@ -20111,7 +20111,7 @@
       <c r="D343" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E343" s="8" t="n">
+      <c r="E343" s="9" t="n">
         <v>80300</v>
       </c>
       <c r="F343" s="9" t="n">
@@ -20168,7 +20168,7 @@
       <c r="D344" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E344" s="8" t="n">
+      <c r="E344" s="9" t="n">
         <v>80000</v>
       </c>
       <c r="F344" s="9" t="n">
@@ -20225,7 +20225,7 @@
       <c r="D345" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E345" s="8" t="n">
+      <c r="E345" s="9" t="n">
         <v>81100</v>
       </c>
       <c r="F345" s="9" t="n">
@@ -20282,7 +20282,7 @@
       <c r="D346" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E346" s="8" t="n">
+      <c r="E346" s="9" t="n">
         <v>82000</v>
       </c>
       <c r="F346" s="9" t="n">
@@ -20339,7 +20339,7 @@
       <c r="D347" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E347" s="8" t="n">
+      <c r="E347" s="9" t="n">
         <v>78000</v>
       </c>
       <c r="F347" s="9" t="n">
@@ -20396,7 +20396,7 @@
       <c r="D348" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E348" s="8" t="n">
+      <c r="E348" s="9" t="n">
         <v>78300</v>
       </c>
       <c r="F348" s="9" t="n">
@@ -20453,7 +20453,7 @@
       <c r="D349" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E349" s="8" t="n">
+      <c r="E349" s="9" t="n">
         <v>76000</v>
       </c>
       <c r="F349" s="9" t="n">
@@ -20510,7 +20510,7 @@
       <c r="D350" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E350" s="8" t="n">
+      <c r="E350" s="9" t="n">
         <v>76100</v>
       </c>
       <c r="F350" s="9" t="n">
@@ -20567,7 +20567,7 @@
       <c r="D351" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E351" s="8" t="n">
+      <c r="E351" s="9" t="n">
         <v>74600</v>
       </c>
       <c r="F351" s="9" t="n">
@@ -20624,7 +20624,7 @@
       <c r="D352" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E352" s="8" t="n">
+      <c r="E352" s="9" t="n">
         <v>75700</v>
       </c>
       <c r="F352" s="9" t="n">
@@ -20681,7 +20681,7 @@
       <c r="D353" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E353" s="8" t="n">
+      <c r="E353" s="9" t="n">
         <v>77900</v>
       </c>
       <c r="F353" s="9" t="n">
@@ -20738,7 +20738,7 @@
       <c r="D354" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E354" s="8" t="n">
+      <c r="E354" s="9" t="n">
         <v>78900</v>
       </c>
       <c r="F354" s="9" t="n">
@@ -20795,7 +20795,7 @@
       <c r="D355" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E355" s="8" t="n">
+      <c r="E355" s="9" t="n">
         <v>77800</v>
       </c>
       <c r="F355" s="9" t="n">
@@ -20852,7 +20852,7 @@
       <c r="D356" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E356" s="8" t="n">
+      <c r="E356" s="9" t="n">
         <v>78200</v>
       </c>
       <c r="F356" s="9" t="n">
@@ -20909,7 +20909,7 @@
       <c r="D357" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E357" s="8" t="n">
+      <c r="E357" s="9" t="n">
         <v>82500</v>
       </c>
       <c r="F357" s="9" t="n">
@@ -20968,7 +20968,7 @@
       <c r="D358" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E358" s="8" t="n">
+      <c r="E358" s="9" t="n">
         <v>84000</v>
       </c>
       <c r="F358" s="9" t="n">
@@ -21025,7 +21025,7 @@
       <c r="D359" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E359" s="8" t="n">
+      <c r="E359" s="9" t="n">
         <v>79300</v>
       </c>
       <c r="F359" s="9" t="n">
@@ -21082,7 +21082,7 @@
       <c r="D360" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E360" s="8" t="n">
+      <c r="E360" s="9" t="n">
         <v>80300</v>
       </c>
       <c r="F360" s="9" t="n">
@@ -21139,7 +21139,7 @@
       <c r="D361" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E361" s="8" t="n">
+      <c r="E361" s="9" t="n">
         <v>80500</v>
       </c>
       <c r="F361" s="9" t="n">
@@ -21196,7 +21196,7 @@
       <c r="D362" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E362" s="8" t="n">
+      <c r="E362" s="9" t="n">
         <v>79000</v>
       </c>
       <c r="F362" s="9" t="n">
@@ -21253,7 +21253,7 @@
       <c r="D363" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E363" s="8" t="n">
+      <c r="E363" s="9" t="n">
         <v>78900</v>
       </c>
       <c r="F363" s="9" t="n">
@@ -21310,7 +21310,7 @@
       <c r="D364" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E364" s="8" t="n">
+      <c r="E364" s="9" t="n">
         <v>80700</v>
       </c>
       <c r="F364" s="9" t="n">
@@ -21367,7 +21367,7 @@
       <c r="D365" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E365" s="8" t="n">
+      <c r="E365" s="9" t="n">
         <v>82300</v>
       </c>
       <c r="F365" s="9" t="n">
@@ -21424,7 +21424,7 @@
       <c r="D366" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E366" s="8" t="n">
+      <c r="E366" s="9" t="n">
         <v>81600</v>
       </c>
       <c r="F366" s="9" t="n">
@@ -21481,7 +21481,7 @@
       <c r="D367" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E367" s="8" t="n">
+      <c r="E367" s="9" t="n">
         <v>81000</v>
       </c>
       <c r="F367" s="9" t="n">
@@ -21538,7 +21538,7 @@
       <c r="D368" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E368" s="8" t="n">
+      <c r="E368" s="9" t="n">
         <v>84400</v>
       </c>
       <c r="F368" s="9" t="n">
@@ -21595,7 +21595,7 @@
       <c r="D369" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E369" s="8" t="n">
+      <c r="E369" s="9" t="n">
         <v>86000</v>
       </c>
       <c r="F369" s="9" t="n">
@@ -21652,7 +21652,7 @@
       <c r="D370" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E370" s="8" t="n">
+      <c r="E370" s="9" t="n">
         <v>82200</v>
       </c>
       <c r="F370" s="9" t="n">
@@ -21709,7 +21709,7 @@
       <c r="D371" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E371" s="8" t="n">
+      <c r="E371" s="9" t="n">
         <v>78600</v>
       </c>
       <c r="F371" s="9" t="n">
@@ -21766,7 +21766,7 @@
       <c r="D372" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E372" s="8" t="n">
+      <c r="E372" s="9" t="n">
         <v>76400</v>
       </c>
       <c r="F372" s="9" t="n">
@@ -21823,7 +21823,7 @@
       <c r="D373" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E373" s="8" t="n">
+      <c r="E373" s="9" t="n">
         <v>74000</v>
       </c>
       <c r="F373" s="9" t="n">
@@ -21880,7 +21880,7 @@
       <c r="D374" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E374" s="8" t="n">
+      <c r="E374" s="9" t="n">
         <v>72800</v>
       </c>
       <c r="F374" s="9" t="n">
@@ -21937,7 +21937,7 @@
       <c r="D375" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E375" s="8" t="n">
+      <c r="E375" s="9" t="n">
         <v>73600</v>
       </c>
       <c r="F375" s="9" t="n">
@@ -21994,7 +21994,7 @@
       <c r="D376" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E376" s="8" t="n">
+      <c r="E376" s="9" t="n">
         <v>70800</v>
       </c>
       <c r="F376" s="9" t="n">
@@ -22051,7 +22051,7 @@
       <c r="D377" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E377" s="8" t="n">
+      <c r="E377" s="9" t="n">
         <v>71100</v>
       </c>
       <c r="F377" s="9" t="n">
@@ -22110,7 +22110,7 @@
       <c r="D378" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E378" s="8" t="n">
+      <c r="E378" s="9" t="n">
         <v>70800</v>
       </c>
       <c r="F378" s="9" t="n">
@@ -22167,7 +22167,7 @@
       <c r="D379" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E379" s="8" t="n">
+      <c r="E379" s="9" t="n">
         <v>70100</v>
       </c>
       <c r="F379" s="9" t="n">
@@ -22224,7 +22224,7 @@
       <c r="D380" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E380" s="8" t="n">
+      <c r="E380" s="9" t="n">
         <v>71000</v>
       </c>
       <c r="F380" s="9" t="n">
@@ -22281,7 +22281,7 @@
       <c r="D381" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E381" s="8" t="n">
+      <c r="E381" s="9" t="n">
         <v>68800</v>
       </c>
       <c r="F381" s="9" t="n">
@@ -22338,7 +22338,7 @@
       <c r="D382" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E382" s="8" t="n">
+      <c r="E382" s="9" t="n">
         <v>67100</v>
       </c>
       <c r="F382" s="9" t="n">
@@ -22395,7 +22395,7 @@
       <c r="D383" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E383" s="8" t="n">
+      <c r="E383" s="9" t="n">
         <v>69500</v>
       </c>
       <c r="F383" s="9" t="n">
@@ -22452,7 +22452,7 @@
       <c r="D384" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E384" s="8" t="n">
+      <c r="E384" s="9" t="n">
         <v>72500</v>
       </c>
       <c r="F384" s="9" t="n">
@@ -22509,7 +22509,7 @@
       <c r="D385" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E385" s="8" t="n">
+      <c r="E385" s="9" t="n">
         <v>69800</v>
       </c>
       <c r="F385" s="9" t="n">
@@ -22566,7 +22566,7 @@
       <c r="D386" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E386" s="8" t="n">
+      <c r="E386" s="9" t="n">
         <v>68600</v>
       </c>
       <c r="F386" s="9" t="n">
@@ -22623,7 +22623,7 @@
       <c r="D387" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E387" s="8" t="n">
+      <c r="E387" s="9" t="n">
         <v>71500</v>
       </c>
       <c r="F387" s="9" t="n">
@@ -22680,7 +22680,7 @@
       <c r="D388" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E388" s="8" t="n">
+      <c r="E388" s="9" t="n">
         <v>73700</v>
       </c>
       <c r="F388" s="9" t="n">
@@ -22737,7 +22737,7 @@
       <c r="D389" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E389" s="8" t="n">
+      <c r="E389" s="9" t="n">
         <v>71700</v>
       </c>
       <c r="F389" s="9" t="n">
@@ -22794,7 +22794,7 @@
       <c r="D390" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E390" s="8" t="n">
+      <c r="E390" s="9" t="n">
         <v>67100</v>
       </c>
       <c r="F390" s="9" t="n">
@@ -22851,7 +22851,7 @@
       <c r="D391" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E391" s="8" t="n">
+      <c r="E391" s="9" t="n">
         <v>62800</v>
       </c>
       <c r="F391" s="9" t="n">
@@ -22908,7 +22908,7 @@
       <c r="D392" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E392" s="8" t="n">
+      <c r="E392" s="9" t="n">
         <v>67500</v>
       </c>
       <c r="F392" s="9" t="n">
@@ -22965,7 +22965,7 @@
       <c r="D393" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E393" s="8" t="n">
+      <c r="E393" s="9" t="n">
         <v>72500</v>
       </c>
       <c r="F393" s="9" t="n">
@@ -23022,7 +23022,7 @@
       <c r="D394" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E394" s="8" t="n">
+      <c r="E394" s="9" t="n">
         <v>76800</v>
       </c>
       <c r="F394" s="9" t="n">
@@ -23079,7 +23079,7 @@
       <c r="D395" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E395" s="8" t="n">
+      <c r="E395" s="9" t="n">
         <v>82500</v>
       </c>
       <c r="F395" s="9" t="n">
@@ -23136,7 +23136,7 @@
       <c r="D396" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E396" s="8" t="n">
+      <c r="E396" s="9" t="n">
         <v>83400</v>
       </c>
       <c r="F396" s="9" t="n">
@@ -23193,7 +23193,7 @@
       <c r="D397" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E397" s="8" t="n">
+      <c r="E397" s="9" t="n">
         <v>83300</v>
       </c>
       <c r="F397" s="9" t="n">
@@ -23252,7 +23252,7 @@
       <c r="D398" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E398" s="8" t="n">
+      <c r="E398" s="9" t="n">
         <v>82000</v>
       </c>
       <c r="F398" s="9" t="n">
@@ -23309,7 +23309,7 @@
       <c r="D399" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E399" s="8" t="n">
+      <c r="E399" s="9" t="n">
         <v>84900</v>
       </c>
       <c r="F399" s="9" t="n">
@@ -23366,7 +23366,7 @@
       <c r="D400" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E400" s="8" t="n">
+      <c r="E400" s="9" t="n">
         <v>86600</v>
       </c>
       <c r="F400" s="9" t="n">
@@ -23423,7 +23423,7 @@
       <c r="D401" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E401" s="8" t="n">
+      <c r="E401" s="9" t="n">
         <v>87800</v>
       </c>
       <c r="F401" s="9" t="n">
@@ -23480,7 +23480,7 @@
       <c r="D402" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E402" s="8" t="n">
+      <c r="E402" s="9" t="n">
         <v>88500</v>
       </c>
       <c r="F402" s="9" t="n">
@@ -23537,7 +23537,7 @@
       <c r="D403" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E403" s="8" t="n">
+      <c r="E403" s="9" t="n">
         <v>89600</v>
       </c>
       <c r="F403" s="9" t="n">
@@ -23594,7 +23594,7 @@
       <c r="D404" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E404" s="8" t="n">
+      <c r="E404" s="9" t="n">
         <v>89800</v>
       </c>
       <c r="F404" s="9" t="n">
@@ -23651,7 +23651,7 @@
       <c r="D405" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E405" s="8" t="n">
+      <c r="E405" s="9" t="n">
         <v>88200</v>
       </c>
       <c r="F405" s="9" t="n">
@@ -23708,7 +23708,7 @@
       <c r="D406" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E406" s="8" t="n">
+      <c r="E406" s="9" t="n">
         <v>88200</v>
       </c>
       <c r="F406" s="9" t="n">
@@ -23765,7 +23765,7 @@
       <c r="D407" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E407" s="8" t="n">
+      <c r="E407" s="9" t="n">
         <v>87900</v>
       </c>
       <c r="F407" s="9" t="n">
@@ -23822,7 +23822,7 @@
       <c r="D408" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E408" s="8" t="n">
+      <c r="E408" s="9" t="n">
         <v>87400</v>
       </c>
       <c r="F408" s="9" t="n">
@@ -23879,7 +23879,7 @@
       <c r="D409" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E409" s="8" t="n">
+      <c r="E409" s="9" t="n">
         <v>90000</v>
       </c>
       <c r="F409" s="9" t="n">
@@ -23936,7 +23936,7 @@
       <c r="D410" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E410" s="8" t="n">
+      <c r="E410" s="9" t="n">
         <v>91000</v>
       </c>
       <c r="F410" s="9" t="n">
@@ -23993,7 +23993,7 @@
       <c r="D411" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E411" s="8" t="n">
+      <c r="E411" s="9" t="n">
         <v>93400</v>
       </c>
       <c r="F411" s="9" t="n">
@@ -24050,7 +24050,7 @@
       <c r="D412" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E412" s="8" t="n">
+      <c r="E412" s="9" t="n">
         <v>93300</v>
       </c>
       <c r="F412" s="9" t="n">
@@ -24107,7 +24107,7 @@
       <c r="D413" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E413" s="8" t="n">
+      <c r="E413" s="9" t="n">
         <v>93900</v>
       </c>
       <c r="F413" s="9" t="n">
@@ -24164,7 +24164,7 @@
       <c r="D414" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E414" s="8" t="n">
+      <c r="E414" s="9" t="n">
         <v>93700</v>
       </c>
       <c r="F414" s="9" t="n">
@@ -24221,7 +24221,7 @@
       <c r="D415" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E415" s="8" t="n">
+      <c r="E415" s="9" t="n">
         <v>93000</v>
       </c>
       <c r="F415" s="9" t="n">
@@ -24278,7 +24278,7 @@
       <c r="D416" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E416" s="8" t="n">
+      <c r="E416" s="9" t="n">
         <v>94200</v>
       </c>
       <c r="F416" s="9" t="n">
@@ -24335,7 +24335,7 @@
       <c r="D417" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E417" s="8" t="n">
+      <c r="E417" s="9" t="n">
         <v>94100</v>
       </c>
       <c r="F417" s="9" t="n">
@@ -24392,7 +24392,7 @@
       <c r="D418" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E418" s="8" t="n">
+      <c r="E418" s="9" t="n">
         <v>94000</v>
       </c>
       <c r="F418" s="9" t="n">
@@ -24451,7 +24451,7 @@
       <c r="D419" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E419" s="8" t="n">
+      <c r="E419" s="9" t="n">
         <v>94700</v>
       </c>
       <c r="F419" s="9" t="n">
@@ -24508,7 +24508,7 @@
       <c r="D420" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E420" s="8" t="n">
+      <c r="E420" s="9" t="n">
         <v>95600</v>
       </c>
       <c r="F420" s="9" t="n">
@@ -24565,7 +24565,7 @@
       <c r="D421" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E421" s="8" t="n">
+      <c r="E421" s="9" t="n">
         <v>95500</v>
       </c>
       <c r="F421" s="9" t="n">
@@ -24622,7 +24622,7 @@
       <c r="D422" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E422" s="8" t="n">
+      <c r="E422" s="9" t="n">
         <v>94600</v>
       </c>
       <c r="F422" s="9" t="n">
@@ -24679,7 +24679,7 @@
       <c r="D423" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E423" s="8" t="n">
+      <c r="E423" s="9" t="n">
         <v>94300</v>
       </c>
       <c r="F423" s="9" t="n">
@@ -24736,7 +24736,7 @@
       <c r="D424" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E424" s="8" t="n">
+      <c r="E424" s="9" t="n">
         <v>94100</v>
       </c>
       <c r="F424" s="9" t="n">
@@ -24793,7 +24793,7 @@
       <c r="D425" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E425" s="8" t="n">
+      <c r="E425" s="9" t="n">
         <v>95000</v>
       </c>
       <c r="F425" s="9" t="n">
@@ -24850,7 +24850,7 @@
       <c r="D426" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E426" s="8" t="n">
+      <c r="E426" s="9" t="n">
         <v>93600</v>
       </c>
       <c r="F426" s="9" t="n">
@@ -24907,7 +24907,7 @@
       <c r="D427" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E427" s="8" t="n">
+      <c r="E427" s="9" t="n">
         <v>95400</v>
       </c>
       <c r="F427" s="9" t="n">
@@ -24964,7 +24964,7 @@
       <c r="D428" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E428" s="8" t="n">
+      <c r="E428" s="9" t="n">
         <v>95600</v>
       </c>
       <c r="F428" s="9" t="n">
@@ -25021,7 +25021,7 @@
       <c r="D429" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E429" s="8" t="n">
+      <c r="E429" s="9" t="n">
         <v>95000</v>
       </c>
       <c r="F429" s="9" t="n">
@@ -25078,7 +25078,7 @@
       <c r="D430" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E430" s="8" t="n">
+      <c r="E430" s="9" t="n">
         <v>95000</v>
       </c>
       <c r="F430" s="9" t="n">
@@ -25135,7 +25135,7 @@
       <c r="D431" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E431" s="8" t="n">
+      <c r="E431" s="9" t="n">
         <v>94500</v>
       </c>
       <c r="F431" s="9" t="n">
@@ -25192,7 +25192,7 @@
       <c r="D432" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E432" s="8" t="n">
+      <c r="E432" s="9" t="n">
         <v>95200</v>
       </c>
       <c r="F432" s="9" t="n">
@@ -25249,7 +25249,7 @@
       <c r="D433" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E433" s="8" t="n">
+      <c r="E433" s="9" t="n">
         <v>98300</v>
       </c>
       <c r="F433" s="9" t="n">
@@ -25306,7 +25306,7 @@
       <c r="D434" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E434" s="8" t="n">
+      <c r="E434" s="9" t="n">
         <v>99600</v>
       </c>
       <c r="F434" s="9" t="n">
@@ -25363,7 +25363,7 @@
       <c r="D435" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E435" s="8" t="n">
+      <c r="E435" s="9" t="n">
         <v>98200</v>
       </c>
       <c r="F435" s="9" t="n">
@@ -25420,7 +25420,7 @@
       <c r="D436" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E436" s="8" t="n">
+      <c r="E436" s="9" t="n">
         <v>98200</v>
       </c>
       <c r="F436" s="9" t="n">
@@ -25477,7 +25477,7 @@
       <c r="D437" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E437" s="8" t="n">
+      <c r="E437" s="9" t="n">
         <v>98100</v>
       </c>
       <c r="F437" s="9" t="n">
@@ -25534,7 +25534,7 @@
       <c r="D438" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E438" s="8" t="n">
+      <c r="E438" s="9" t="n">
         <v>97600</v>
       </c>
       <c r="F438" s="9" t="n">
@@ -25593,7 +25593,7 @@
       <c r="D439" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E439" s="8" t="n">
+      <c r="E439" s="9" t="n">
         <v>97100</v>
       </c>
       <c r="F439" s="9" t="n">
@@ -25650,7 +25650,7 @@
       <c r="D440" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E440" s="8" t="n">
+      <c r="E440" s="9" t="n">
         <v>95800</v>
       </c>
       <c r="F440" s="9" t="n">
@@ -25707,7 +25707,7 @@
       <c r="D441" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E441" s="8" t="n">
+      <c r="E441" s="9" t="n">
         <v>95600</v>
       </c>
       <c r="F441" s="9" t="n">
@@ -25764,7 +25764,7 @@
       <c r="D442" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E442" s="8" t="n">
+      <c r="E442" s="9" t="n">
         <v>96100</v>
       </c>
       <c r="F442" s="9" t="n">
@@ -25821,7 +25821,7 @@
       <c r="D443" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E443" s="8" t="n">
+      <c r="E443" s="9" t="n">
         <v>95200</v>
       </c>
       <c r="F443" s="9" t="n">
@@ -25878,7 +25878,7 @@
       <c r="D444" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E444" s="8" t="n">
+      <c r="E444" s="9" t="n">
         <v>95000</v>
       </c>
       <c r="F444" s="9" t="n">
@@ -25935,7 +25935,7 @@
       <c r="D445" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E445" s="8" t="n">
+      <c r="E445" s="9" t="n">
         <v>94300</v>
       </c>
       <c r="F445" s="9" t="n">
@@ -25992,7 +25992,7 @@
       <c r="D446" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E446" s="8" t="n">
+      <c r="E446" s="9" t="n">
         <v>95400</v>
       </c>
       <c r="F446" s="9" t="n">
@@ -26049,7 +26049,7 @@
       <c r="D447" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E447" s="8" t="n">
+      <c r="E447" s="9" t="n">
         <v>94400</v>
       </c>
       <c r="F447" s="9" t="n">
@@ -26106,7 +26106,7 @@
       <c r="D448" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E448" s="8" t="n">
+      <c r="E448" s="9" t="n">
         <v>93800</v>
       </c>
       <c r="F448" s="9" t="n">
@@ -26163,7 +26163,7 @@
       <c r="D449" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E449" s="8" t="n">
+      <c r="E449" s="9" t="n">
         <v>95100</v>
       </c>
       <c r="F449" s="9" t="n">
@@ -26220,7 +26220,7 @@
       <c r="D450" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E450" s="8" t="n">
+      <c r="E450" s="9" t="n">
         <v>96000</v>
       </c>
       <c r="F450" s="9" t="n">
@@ -26277,7 +26277,7 @@
       <c r="D451" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E451" s="8" t="n">
+      <c r="E451" s="9" t="n">
         <v>94600</v>
       </c>
       <c r="F451" s="9" t="n">
@@ -26334,7 +26334,7 @@
       <c r="D452" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E452" s="8" t="n">
+      <c r="E452" s="9" t="n">
         <v>96800</v>
       </c>
       <c r="F452" s="9" t="n">
@@ -26391,7 +26391,7 @@
       <c r="D453" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E453" s="8" t="n">
+      <c r="E453" s="9" t="n">
         <v>96600</v>
       </c>
       <c r="F453" s="9" t="n">
@@ -26448,7 +26448,7 @@
       <c r="D454" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E454" s="8" t="n">
+      <c r="E454" s="9" t="n">
         <v>97900</v>
       </c>
       <c r="F454" s="9" t="n">
@@ -26505,7 +26505,7 @@
       <c r="D455" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E455" s="8" t="n">
+      <c r="E455" s="9" t="n">
         <v>97900</v>
       </c>
       <c r="F455" s="9" t="n">
@@ -26573,7 +26573,7 @@
       <c r="D456" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E456" s="8" t="n">
+      <c r="E456" s="9" t="n">
         <v>97500</v>
       </c>
       <c r="F456" s="9" t="n">
@@ -26630,7 +26630,7 @@
       <c r="D457" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E457" s="8" t="n">
+      <c r="E457" s="9" t="n">
         <v>97600</v>
       </c>
       <c r="F457" s="9" t="n">
@@ -26687,7 +26687,7 @@
       <c r="D458" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E458" s="8" t="n">
+      <c r="E458" s="9" t="n">
         <v>97500</v>
       </c>
       <c r="F458" s="9" t="n">
@@ -26744,7 +26744,7 @@
       <c r="D459" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E459" s="8" t="n">
+      <c r="E459" s="9" t="n">
         <v>97600</v>
       </c>
       <c r="F459" s="9" t="n">
@@ -26801,7 +26801,7 @@
       <c r="D460" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E460" s="8" t="n">
+      <c r="E460" s="9" t="n">
         <v>97200</v>
       </c>
       <c r="F460" s="9" t="n">
@@ -26858,7 +26858,7 @@
       <c r="D461" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E461" s="8" t="n">
+      <c r="E461" s="9" t="n">
         <v>97300</v>
       </c>
       <c r="F461" s="9" t="n">
@@ -26915,7 +26915,7 @@
       <c r="D462" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E462" s="8" t="n">
+      <c r="E462" s="9" t="n">
         <v>97000</v>
       </c>
       <c r="F462" s="9" t="n">
@@ -26972,7 +26972,7 @@
       <c r="D463" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E463" s="8" t="n">
+      <c r="E463" s="9" t="n">
         <v>97400</v>
       </c>
       <c r="F463" s="9" t="n">
@@ -27029,7 +27029,7 @@
       <c r="D464" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E464" s="8" t="n">
+      <c r="E464" s="9" t="n">
         <v>97500</v>
       </c>
       <c r="F464" s="9" t="n">
@@ -27086,7 +27086,7 @@
       <c r="D465" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E465" s="8" t="n">
+      <c r="E465" s="9" t="n">
         <v>97800</v>
       </c>
       <c r="F465" s="9" t="n">
@@ -27143,7 +27143,7 @@
       <c r="D466" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E466" s="8" t="n">
+      <c r="E466" s="9" t="n">
         <v>98200</v>
       </c>
       <c r="F466" s="9" t="n">
@@ -27200,7 +27200,7 @@
       <c r="D467" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E467" s="8" t="n">
+      <c r="E467" s="9" t="n">
         <v>97000</v>
       </c>
       <c r="F467" s="9" t="n">
@@ -27257,7 +27257,7 @@
       <c r="D468" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E468" s="8" t="n">
+      <c r="E468" s="9" t="n">
         <v>96800</v>
       </c>
       <c r="F468" s="9" t="n">
@@ -27314,7 +27314,7 @@
       <c r="D469" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E469" s="8" t="n">
+      <c r="E469" s="9" t="n">
         <v>96800</v>
       </c>
       <c r="F469" s="9" t="n">
@@ -27371,7 +27371,7 @@
       <c r="D470" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E470" s="8" t="n">
+      <c r="E470" s="9" t="n">
         <v>97000</v>
       </c>
       <c r="F470" s="9" t="n">
@@ -27428,7 +27428,7 @@
       <c r="D471" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E471" s="8" t="n">
+      <c r="E471" s="9" t="n">
         <v>96800</v>
       </c>
       <c r="F471" s="9" t="n">
@@ -27485,7 +27485,7 @@
       <c r="D472" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E472" s="8" t="n">
+      <c r="E472" s="9" t="n">
         <v>96400</v>
       </c>
       <c r="F472" s="9" t="n">
@@ -27542,7 +27542,7 @@
       <c r="D473" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E473" s="8" t="n">
+      <c r="E473" s="9" t="n">
         <v>96000</v>
       </c>
       <c r="F473" s="9" t="n">
@@ -27599,7 +27599,7 @@
       <c r="D474" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E474" s="8" t="n">
+      <c r="E474" s="9" t="n">
         <v>94200</v>
       </c>
       <c r="F474" s="9" t="n">
@@ -27656,7 +27656,7 @@
       <c r="D475" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E475" s="8" t="n">
+      <c r="E475" s="9" t="n">
         <v>93600</v>
       </c>
       <c r="F475" s="9" t="n">
@@ -27713,7 +27713,7 @@
       <c r="D476" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E476" s="8" t="n">
+      <c r="E476" s="9" t="n">
         <v>94000</v>
       </c>
       <c r="F476" s="9" t="n">
@@ -27770,7 +27770,7 @@
       <c r="D477" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E477" s="8" t="n">
+      <c r="E477" s="9" t="n">
         <v>92900</v>
       </c>
       <c r="F477" s="9" t="n">
@@ -27829,7 +27829,7 @@
       <c r="D478" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E478" s="8" t="n">
+      <c r="E478" s="9" t="n">
         <v>92800</v>
       </c>
       <c r="F478" s="9" t="n">
@@ -27886,7 +27886,7 @@
       <c r="D479" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E479" s="8" t="n">
+      <c r="E479" s="9" t="n">
         <v>93000</v>
       </c>
       <c r="F479" s="9" t="n">
@@ -27943,7 +27943,7 @@
       <c r="D480" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E480" s="8" t="n">
+      <c r="E480" s="9" t="n">
         <v>92800</v>
       </c>
       <c r="F480" s="9" t="n">
@@ -28000,7 +28000,7 @@
       <c r="D481" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E481" s="8" t="n">
+      <c r="E481" s="9" t="n">
         <v>92900</v>
       </c>
       <c r="F481" s="9" t="n">
@@ -28057,7 +28057,7 @@
       <c r="D482" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E482" s="8" t="n">
+      <c r="E482" s="9" t="n">
         <v>92900</v>
       </c>
       <c r="F482" s="9" t="n">
@@ -28114,7 +28114,7 @@
       <c r="D483" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E483" s="8" t="n">
+      <c r="E483" s="9" t="n">
         <v>94000</v>
       </c>
       <c r="F483" s="9" t="n">
@@ -28171,7 +28171,7 @@
       <c r="D484" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E484" s="8" t="n">
+      <c r="E484" s="9" t="n">
         <v>92800</v>
       </c>
       <c r="F484" s="9" t="n">
@@ -28228,7 +28228,7 @@
       <c r="D485" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E485" s="8" t="n">
+      <c r="E485" s="9" t="n">
         <v>91700</v>
       </c>
       <c r="F485" s="9" t="n">
@@ -28285,7 +28285,7 @@
       <c r="D486" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E486" s="8" t="n">
+      <c r="E486" s="9" t="n">
         <v>91900</v>
       </c>
       <c r="F486" s="9" t="n">
@@ -28342,7 +28342,7 @@
       <c r="D487" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E487" s="8" t="n">
+      <c r="E487" s="9" t="n">
         <v>91400</v>
       </c>
       <c r="F487" s="9" t="n">
@@ -28399,7 +28399,7 @@
       <c r="D488" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E488" s="8" t="n">
+      <c r="E488" s="9" t="n">
         <v>93000</v>
       </c>
       <c r="F488" s="9" t="n">
@@ -28456,7 +28456,7 @@
       <c r="D489" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E489" s="8" t="n">
+      <c r="E489" s="9" t="n">
         <v>93000</v>
       </c>
       <c r="F489" s="9" t="n">
@@ -28513,7 +28513,7 @@
       <c r="D490" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E490" s="8" t="n">
+      <c r="E490" s="9" t="n">
         <v>93200</v>
       </c>
       <c r="F490" s="9" t="n">
@@ -28570,7 +28570,7 @@
       <c r="D491" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E491" s="8" t="n">
+      <c r="E491" s="9" t="n">
         <v>92900</v>
       </c>
       <c r="F491" s="9" t="n">
@@ -28627,7 +28627,7 @@
       <c r="D492" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E492" s="8" t="n">
+      <c r="E492" s="9" t="n">
         <v>93000</v>
       </c>
       <c r="F492" s="9" t="n">
@@ -28684,7 +28684,7 @@
       <c r="D493" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E493" s="8" t="n">
+      <c r="E493" s="9" t="n">
         <v>93300</v>
       </c>
       <c r="F493" s="9" t="n">
@@ -28741,7 +28741,7 @@
       <c r="D494" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E494" s="8" t="n">
+      <c r="E494" s="9" t="n">
         <v>94300</v>
       </c>
       <c r="F494" s="9" t="n">
@@ -28798,7 +28798,7 @@
       <c r="D495" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E495" s="8" t="n">
+      <c r="E495" s="9" t="n">
         <v>93500</v>
       </c>
       <c r="F495" s="9" t="n">
@@ -28855,7 +28855,7 @@
       <c r="D496" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E496" s="8" t="n">
+      <c r="E496" s="9" t="n">
         <v>92700</v>
       </c>
       <c r="F496" s="9" t="n">
@@ -28912,7 +28912,7 @@
       <c r="D497" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E497" s="8" t="n">
+      <c r="E497" s="9" t="n">
         <v>91400</v>
       </c>
       <c r="F497" s="9" t="n">
@@ -28969,7 +28969,7 @@
       <c r="D498" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E498" s="8" t="n">
+      <c r="E498" s="9" t="n">
         <v>94800</v>
       </c>
       <c r="F498" s="9" t="n">
@@ -29028,7 +29028,7 @@
       <c r="D499" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E499" s="8" t="n">
+      <c r="E499" s="9" t="n">
         <v>95500</v>
       </c>
       <c r="F499" s="9" t="n">
@@ -29085,7 +29085,7 @@
       <c r="D500" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E500" s="8" t="n">
+      <c r="E500" s="9" t="n">
         <v>96300</v>
       </c>
       <c r="F500" s="9" t="n">
@@ -29142,7 +29142,7 @@
       <c r="D501" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E501" s="8" t="n">
+      <c r="E501" s="9" t="n">
         <v>94900</v>
       </c>
       <c r="F501" s="9" t="n">
@@ -29199,7 +29199,7 @@
       <c r="D502" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E502" s="8" t="n">
+      <c r="E502" s="9" t="n">
         <v>94100</v>
       </c>
       <c r="F502" s="9" t="n">
@@ -29256,7 +29256,7 @@
       <c r="D503" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E503" s="8" t="n">
+      <c r="E503" s="9" t="n">
         <v>94000</v>
       </c>
       <c r="F503" s="9" t="n">
@@ -29313,7 +29313,7 @@
       <c r="D504" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E504" s="8" t="n">
+      <c r="E504" s="9" t="n">
         <v>93800</v>
       </c>
       <c r="F504" s="9" t="n">
@@ -29370,7 +29370,7 @@
       <c r="D505" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E505" s="8" t="n">
+      <c r="E505" s="9" t="n">
         <v>93000</v>
       </c>
       <c r="F505" s="9" t="n">
@@ -29427,7 +29427,7 @@
       <c r="D506" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E506" s="8" t="n">
+      <c r="E506" s="9" t="n">
         <v>94600</v>
       </c>
       <c r="F506" s="9" t="n">
@@ -29484,7 +29484,7 @@
       <c r="D507" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E507" s="8" t="n">
+      <c r="E507" s="9" t="n">
         <v>94900</v>
       </c>
       <c r="F507" s="9" t="n">
@@ -29541,7 +29541,7 @@
       <c r="D508" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E508" s="8" t="n">
+      <c r="E508" s="9" t="n">
         <v>95100</v>
       </c>
       <c r="F508" s="9" t="n">
@@ -29598,7 +29598,7 @@
       <c r="D509" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E509" s="8" t="n">
+      <c r="E509" s="9" t="n">
         <v>94600</v>
       </c>
       <c r="F509" s="9" t="n">
@@ -29655,7 +29655,7 @@
       <c r="D510" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E510" s="8" t="n">
+      <c r="E510" s="9" t="n">
         <v>94100</v>
       </c>
       <c r="F510" s="9" t="n">
@@ -29712,7 +29712,7 @@
       <c r="D511" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E511" s="8" t="n">
+      <c r="E511" s="9" t="n">
         <v>94700</v>
       </c>
       <c r="F511" s="9" t="n">
@@ -29769,7 +29769,7 @@
       <c r="D512" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E512" s="8" t="n">
+      <c r="E512" s="9" t="n">
         <v>95400</v>
       </c>
       <c r="F512" s="9" t="n">
@@ -29826,7 +29826,7 @@
       <c r="D513" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E513" s="8" t="n">
+      <c r="E513" s="9" t="n">
         <v>95500</v>
       </c>
       <c r="F513" s="9" t="n">
@@ -29883,7 +29883,7 @@
       <c r="D514" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E514" s="8" t="n">
+      <c r="E514" s="9" t="n">
         <v>94400</v>
       </c>
       <c r="F514" s="9" t="n">
@@ -29940,7 +29940,7 @@
       <c r="D515" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E515" s="8" t="n">
+      <c r="E515" s="9" t="n">
         <v>94800</v>
       </c>
       <c r="F515" s="9" t="n">
@@ -29997,7 +29997,7 @@
       <c r="D516" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E516" s="8" t="n">
+      <c r="E516" s="9" t="n">
         <v>95400</v>
       </c>
       <c r="F516" s="9" t="n">
@@ -30054,7 +30054,7 @@
       <c r="D517" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E517" s="8" t="n">
+      <c r="E517" s="9" t="n">
         <v>95400</v>
       </c>
       <c r="F517" s="9" t="n">
@@ -30111,7 +30111,7 @@
       <c r="D518" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E518" s="8" t="n">
+      <c r="E518" s="9" t="n">
         <v>97200</v>
       </c>
       <c r="F518" s="9" t="n">
@@ -30168,7 +30168,7 @@
       <c r="D519" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E519" s="8" t="n">
+      <c r="E519" s="9" t="n">
         <v>98000</v>
       </c>
       <c r="F519" s="9" t="n">
@@ -30225,7 +30225,7 @@
       <c r="D520" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E520" s="8" t="n">
+      <c r="E520" s="9" t="n">
         <v>98400</v>
       </c>
       <c r="F520" s="9" t="n">
@@ -30282,7 +30282,7 @@
       <c r="D521" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E521" s="8" t="n">
+      <c r="E521" s="9" t="n">
         <v>98800</v>
       </c>
       <c r="F521" s="9" t="n">
@@ -30341,7 +30341,7 @@
       <c r="D522" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E522" s="8" t="n">
+      <c r="E522" s="9" t="n">
         <v>99000</v>
       </c>
       <c r="F522" s="9" t="n">
@@ -30398,7 +30398,7 @@
       <c r="D523" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E523" s="8" t="n">
+      <c r="E523" s="9" t="n">
         <v>99300</v>
       </c>
       <c r="F523" s="9" t="n">
@@ -30455,7 +30455,7 @@
       <c r="D524" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E524" s="8" t="n">
+      <c r="E524" s="9" t="n">
         <v>99600</v>
       </c>
       <c r="F524" s="9" t="n">
@@ -30512,7 +30512,7 @@
       <c r="D525" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E525" s="8" t="n">
+      <c r="E525" s="9" t="n">
         <v>99400</v>
       </c>
       <c r="F525" s="9" t="n">
@@ -30569,7 +30569,7 @@
       <c r="D526" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E526" s="8" t="n">
+      <c r="E526" s="9" t="n">
         <v>99100</v>
       </c>
       <c r="F526" s="9" t="n">
@@ -30626,7 +30626,7 @@
       <c r="D527" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E527" s="8" t="n">
+      <c r="E527" s="9" t="n">
         <v>98800</v>
       </c>
       <c r="F527" s="9" t="n">
@@ -30683,7 +30683,7 @@
       <c r="D528" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E528" s="8" t="n">
+      <c r="E528" s="9" t="n">
         <v>98900</v>
       </c>
       <c r="F528" s="9" t="n">
@@ -30740,7 +30740,7 @@
       <c r="D529" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E529" s="8" t="n">
+      <c r="E529" s="9" t="n">
         <v>100000</v>
       </c>
       <c r="F529" s="9" t="n">
@@ -30797,7 +30797,7 @@
       <c r="D530" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E530" s="8" t="n">
+      <c r="E530" s="9" t="n">
         <v>100000</v>
       </c>
       <c r="F530" s="9" t="n">
@@ -30854,7 +30854,7 @@
       <c r="D531" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E531" s="8" t="n">
+      <c r="E531" s="9" t="n">
         <v>99500</v>
       </c>
       <c r="F531" s="9" t="n">
@@ -30911,7 +30911,7 @@
       <c r="D532" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E532" s="8" t="n">
+      <c r="E532" s="9" t="n">
         <v>99800</v>
       </c>
       <c r="F532" s="9" t="n">
@@ -30968,7 +30968,7 @@
       <c r="D533" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E533" s="8" t="n">
+      <c r="E533" s="9" t="n">
         <v>99400</v>
       </c>
       <c r="F533" s="9" t="n">
@@ -31025,7 +31025,7 @@
       <c r="D534" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E534" s="8" t="n">
+      <c r="E534" s="9" t="n">
         <v>99200</v>
       </c>
       <c r="F534" s="9" t="n">
@@ -31082,7 +31082,7 @@
       <c r="D535" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E535" s="8" t="n">
+      <c r="E535" s="9" t="n">
         <v>99000</v>
       </c>
       <c r="F535" s="9" t="n">
@@ -31139,7 +31139,7 @@
       <c r="D536" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E536" s="8" t="n">
+      <c r="E536" s="9" t="n">
         <v>99500</v>
       </c>
       <c r="F536" s="9" t="n">
@@ -31196,7 +31196,7 @@
       <c r="D537" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E537" s="8" t="n">
+      <c r="E537" s="9" t="n">
         <v>99600</v>
       </c>
       <c r="F537" s="9" t="n">
@@ -31253,7 +31253,7 @@
       <c r="D538" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E538" s="8" t="n">
+      <c r="E538" s="9" t="n">
         <v>100100</v>
       </c>
       <c r="F538" s="9" t="n">
@@ -31310,7 +31310,7 @@
       <c r="D539" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E539" s="8" t="n">
+      <c r="E539" s="9" t="n">
         <v>101200</v>
       </c>
       <c r="F539" s="9" t="n">
@@ -31367,7 +31367,7 @@
       <c r="D540" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E540" s="8" t="n">
+      <c r="E540" s="9" t="n">
         <v>102200</v>
       </c>
       <c r="F540" s="9" t="n">
@@ -31426,7 +31426,7 @@
       <c r="D541" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E541" s="8" t="n">
+      <c r="E541" s="9" t="n">
         <v>101000</v>
       </c>
       <c r="F541" s="9" t="n">
@@ -31483,7 +31483,7 @@
       <c r="D542" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E542" s="8" t="n">
+      <c r="E542" s="9" t="n">
         <v>101600</v>
       </c>
       <c r="F542" s="9" t="n">
@@ -31540,7 +31540,7 @@
       <c r="D543" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E543" s="8" t="n">
+      <c r="E543" s="9" t="n">
         <v>103000</v>
       </c>
       <c r="F543" s="9" t="n">
@@ -31597,7 +31597,7 @@
       <c r="D544" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E544" s="8" t="n">
+      <c r="E544" s="9" t="n">
         <v>102600</v>
       </c>
       <c r="F544" s="9" t="n">
@@ -31654,7 +31654,7 @@
       <c r="D545" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E545" s="8" t="n">
+      <c r="E545" s="9" t="n">
         <v>108900</v>
       </c>
       <c r="F545" s="9" t="n">
@@ -31711,7 +31711,7 @@
       <c r="D546" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E546" s="8" t="n">
+      <c r="E546" s="9" t="n">
         <v>109300</v>
       </c>
       <c r="F546" s="9" t="n">
@@ -31768,7 +31768,7 @@
       <c r="D547" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E547" s="8" t="n">
+      <c r="E547" s="9" t="n">
         <v>108400</v>
       </c>
       <c r="F547" s="9" t="n">
@@ -31825,7 +31825,7 @@
       <c r="D548" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E548" s="8" t="n">
+      <c r="E548" s="9" t="n">
         <v>108000</v>
       </c>
       <c r="F548" s="9" t="n">
@@ -31882,7 +31882,7 @@
       <c r="D549" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E549" s="8" t="n">
+      <c r="E549" s="9" t="n">
         <v>104900</v>
       </c>
       <c r="F549" s="9" t="n">
@@ -31939,7 +31939,7 @@
       <c r="D550" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E550" s="8" t="n">
+      <c r="E550" s="9" t="n">
         <v>98100</v>
       </c>
       <c r="F550" s="9" t="n">
@@ -31996,7 +31996,7 @@
       <c r="D551" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E551" s="8" t="n">
+      <c r="E551" s="9" t="n">
         <v>96900</v>
       </c>
       <c r="F551" s="9" t="n">
@@ -32053,7 +32053,7 @@
       <c r="D552" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E552" s="8" t="n">
+      <c r="E552" s="9" t="n">
         <v>97400</v>
       </c>
       <c r="F552" s="9" t="n">
@@ -32110,7 +32110,7 @@
       <c r="D553" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E553" s="8" t="n">
+      <c r="E553" s="9" t="n">
         <v>97400</v>
       </c>
       <c r="F553" s="9" t="n">
@@ -32167,7 +32167,7 @@
       <c r="D554" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E554" s="8" t="n">
+      <c r="E554" s="9" t="n">
         <v>97000</v>
       </c>
       <c r="F554" s="9" t="n">
@@ -32224,7 +32224,7 @@
       <c r="D555" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E555" s="8" t="n">
+      <c r="E555" s="9" t="n">
         <v>95600</v>
       </c>
       <c r="F555" s="9" t="n">
@@ -32281,7 +32281,7 @@
       <c r="D556" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E556" s="8" t="n">
+      <c r="E556" s="9" t="n">
         <v>94300</v>
       </c>
       <c r="F556" s="9" t="n">
@@ -32338,7 +32338,7 @@
       <c r="D557" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E557" s="8" t="n">
+      <c r="E557" s="9" t="n">
         <v>95500</v>
       </c>
       <c r="F557" s="9" t="n">
@@ -32395,7 +32395,7 @@
       <c r="D558" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E558" s="8" t="n">
+      <c r="E558" s="9" t="n">
         <v>95600</v>
       </c>
       <c r="F558" s="9" t="n">
@@ -32452,7 +32452,7 @@
       <c r="D559" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E559" s="8" t="n">
+      <c r="E559" s="9" t="n">
         <v>95200</v>
       </c>
       <c r="F559" s="9" t="n">
@@ -32509,7 +32509,7 @@
       <c r="D560" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E560" s="8" t="n">
+      <c r="E560" s="9" t="n">
         <v>99000</v>
       </c>
       <c r="F560" s="9" t="n">
@@ -32566,7 +32566,7 @@
       <c r="D561" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E561" s="8" t="n">
+      <c r="E561" s="9" t="n">
         <v>97800</v>
       </c>
       <c r="F561" s="9" t="n">
@@ -32623,7 +32623,7 @@
       <c r="D562" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E562" s="8" t="n">
+      <c r="E562" s="9" t="n">
         <v>97100</v>
       </c>
       <c r="F562" s="9" t="n">
@@ -32682,7 +32682,7 @@
       <c r="D563" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E563" s="8" t="n">
+      <c r="E563" s="9" t="n">
         <v>96900</v>
       </c>
       <c r="F563" s="9" t="n">
@@ -32739,7 +32739,7 @@
       <c r="D564" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E564" s="8" t="n">
+      <c r="E564" s="9" t="n">
         <v>96800</v>
       </c>
       <c r="F564" s="9" t="n">
@@ -32796,7 +32796,7 @@
       <c r="D565" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E565" s="8" t="n">
+      <c r="E565" s="9" t="n">
         <v>96200</v>
       </c>
       <c r="F565" s="9" t="n">
@@ -32853,7 +32853,7 @@
       <c r="D566" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E566" s="8" t="n">
+      <c r="E566" s="9" t="n">
         <v>94800</v>
       </c>
       <c r="F566" s="9" t="n">
@@ -32910,7 +32910,7 @@
       <c r="D567" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E567" s="8" t="n">
+      <c r="E567" s="9" t="n">
         <v>94800</v>
       </c>
       <c r="F567" s="9" t="n">
@@ -32967,7 +32967,7 @@
       <c r="D568" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E568" s="8" t="n">
+      <c r="E568" s="9" t="n">
         <v>93800</v>
       </c>
       <c r="F568" s="9" t="n">
@@ -33024,7 +33024,7 @@
       <c r="D569" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E569" s="8" t="n">
+      <c r="E569" s="9" t="n">
         <v>94200</v>
       </c>
       <c r="F569" s="9" t="n">
@@ -33081,7 +33081,7 @@
       <c r="D570" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E570" s="8" t="n">
+      <c r="E570" s="9" t="n">
         <v>95700</v>
       </c>
       <c r="F570" s="9" t="n">
@@ -33138,7 +33138,7 @@
       <c r="D571" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E571" s="8" t="n">
+      <c r="E571" s="9" t="n">
         <v>96000</v>
       </c>
       <c r="F571" s="9" t="n">
@@ -33195,7 +33195,7 @@
       <c r="D572" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E572" s="8" t="n">
+      <c r="E572" s="9" t="n">
         <v>95900</v>
       </c>
       <c r="F572" s="9" t="n">
@@ -33252,7 +33252,7 @@
       <c r="D573" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E573" s="8" t="n">
+      <c r="E573" s="9" t="n">
         <v>97100</v>
       </c>
       <c r="F573" s="9" t="n">
@@ -33309,7 +33309,7 @@
       <c r="D574" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E574" s="8" t="n">
+      <c r="E574" s="9" t="n">
         <v>97700</v>
       </c>
       <c r="F574" s="9" t="n">
@@ -33366,7 +33366,7 @@
       <c r="D575" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E575" s="8" t="n">
+      <c r="E575" s="9" t="n">
         <v>97700</v>
       </c>
       <c r="F575" s="9" t="n">
@@ -33423,7 +33423,7 @@
       <c r="D576" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E576" s="8" t="n">
+      <c r="E576" s="9" t="n">
         <v>97400</v>
       </c>
       <c r="F576" s="9" t="n">
@@ -33480,7 +33480,7 @@
       <c r="D577" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E577" s="8" t="n">
+      <c r="E577" s="9" t="n">
         <v>98000</v>
       </c>
       <c r="F577" s="9" t="n">
@@ -33537,7 +33537,7 @@
       <c r="D578" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E578" s="8" t="n">
+      <c r="E578" s="9" t="n">
         <v>98700</v>
       </c>
       <c r="F578" s="9" t="n">
@@ -33594,7 +33594,7 @@
       <c r="D579" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E579" s="8" t="n">
+      <c r="E579" s="9" t="n">
         <v>95400</v>
       </c>
       <c r="F579" s="9" t="n">
@@ -33651,7 +33651,7 @@
       <c r="D580" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E580" s="8" t="n">
+      <c r="E580" s="9" t="n">
         <v>95000</v>
       </c>
       <c r="F580" s="9" t="n">
@@ -33708,7 +33708,7 @@
       <c r="D581" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E581" s="8" t="n">
+      <c r="E581" s="9" t="n">
         <v>94900</v>
       </c>
       <c r="F581" s="9" t="n">
@@ -33765,7 +33765,7 @@
       <c r="D582" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E582" s="8" t="n">
+      <c r="E582" s="9" t="n">
         <v>94600</v>
       </c>
       <c r="F582" s="9" t="n">
@@ -33822,7 +33822,7 @@
       <c r="D583" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E583" s="8" t="n">
+      <c r="E583" s="9" t="n">
         <v>95000</v>
       </c>
       <c r="F583" s="9" t="n">
@@ -33879,7 +33879,7 @@
       <c r="D584" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E584" s="8" t="n">
+      <c r="E584" s="9" t="n">
         <v>94000</v>
       </c>
       <c r="F584" s="9" t="n">
@@ -33936,7 +33936,7 @@
       <c r="D585" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E585" s="8" t="n">
+      <c r="E585" s="9" t="n">
         <v>95500</v>
       </c>
       <c r="F585" s="9" t="n">
@@ -33995,7 +33995,7 @@
       <c r="D586" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E586" s="8" t="n">
+      <c r="E586" s="9" t="n">
         <v>95500</v>
       </c>
       <c r="F586" s="9" t="n">
@@ -34052,7 +34052,7 @@
       <c r="D587" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E587" s="8" t="n">
+      <c r="E587" s="9" t="n">
         <v>96100</v>
       </c>
       <c r="F587" s="9" t="n">
@@ -34109,7 +34109,7 @@
       <c r="D588" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E588" s="8" t="n">
+      <c r="E588" s="9" t="n">
         <v>96500</v>
       </c>
       <c r="F588" s="9" t="n">
@@ -34166,7 +34166,7 @@
       <c r="D589" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E589" s="8" t="n">
+      <c r="E589" s="9" t="n">
         <v>97300</v>
       </c>
       <c r="F589" s="9" t="n">
@@ -34223,7 +34223,7 @@
       <c r="D590" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E590" s="8" t="n">
+      <c r="E590" s="9" t="n">
         <v>97700</v>
       </c>
       <c r="F590" s="9" t="n">
@@ -34280,7 +34280,7 @@
       <c r="D591" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E591" s="8" t="n">
+      <c r="E591" s="9" t="n">
         <v>97800</v>
       </c>
       <c r="F591" s="9" t="n">
@@ -34337,7 +34337,7 @@
       <c r="D592" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E592" s="8" t="n">
+      <c r="E592" s="9" t="n">
         <v>96800</v>
       </c>
       <c r="F592" s="9" t="n">
@@ -34394,7 +34394,7 @@
       <c r="D593" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E593" s="8" t="n">
+      <c r="E593" s="9" t="n">
         <v>96600</v>
       </c>
       <c r="F593" s="9" t="n">
@@ -34451,7 +34451,7 @@
       <c r="D594" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E594" s="8" t="n">
+      <c r="E594" s="9" t="n">
         <v>96000</v>
       </c>
       <c r="F594" s="9" t="n">
@@ -34508,7 +34508,7 @@
       <c r="D595" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E595" s="8" t="n">
+      <c r="E595" s="9" t="n">
         <v>95800</v>
       </c>
       <c r="F595" s="9" t="n">
@@ -34565,7 +34565,7 @@
       <c r="D596" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E596" s="8" t="n">
+      <c r="E596" s="9" t="n">
         <v>97300</v>
       </c>
       <c r="F596" s="9" t="n">
@@ -34622,7 +34622,7 @@
       <c r="D597" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E597" s="8" t="n">
+      <c r="E597" s="9" t="n">
         <v>96900</v>
       </c>
       <c r="F597" s="9" t="n">
@@ -34679,7 +34679,7 @@
       <c r="D598" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E598" s="8" t="n">
+      <c r="E598" s="9" t="n">
         <v>94300</v>
       </c>
       <c r="F598" s="9" t="n">
@@ -34736,7 +34736,7 @@
       <c r="D599" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E599" s="8" t="n">
+      <c r="E599" s="9" t="n">
         <v>94600</v>
       </c>
       <c r="F599" s="9" t="n">
@@ -34793,7 +34793,7 @@
       <c r="D600" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E600" s="8" t="n">
+      <c r="E600" s="9" t="n">
         <v>94600</v>
       </c>
       <c r="F600" s="9" t="n">
@@ -34850,7 +34850,7 @@
       <c r="D601" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E601" s="8" t="n">
+      <c r="E601" s="9" t="n">
         <v>95000</v>
       </c>
       <c r="F601" s="9" t="n">
@@ -34907,7 +34907,7 @@
       <c r="D602" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E602" s="8" t="n">
+      <c r="E602" s="9" t="n">
         <v>94400</v>
       </c>
       <c r="F602" s="9" t="n">
@@ -34964,7 +34964,7 @@
       <c r="D603" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E603" s="8" t="n">
+      <c r="E603" s="9" t="n">
         <v>94800</v>
       </c>
       <c r="F603" s="9" t="n">
@@ -35021,7 +35021,7 @@
       <c r="D604" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E604" s="8" t="n">
+      <c r="E604" s="9" t="n">
         <v>93600</v>
       </c>
       <c r="F604" s="9" t="n">
@@ -35078,7 +35078,7 @@
       <c r="D605" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E605" s="8" t="n">
+      <c r="E605" s="9" t="n">
         <v>93900</v>
       </c>
       <c r="F605" s="9" t="n">
@@ -35137,7 +35137,7 @@
       <c r="D606" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E606" s="8" t="n">
+      <c r="E606" s="9" t="n">
         <v>92900</v>
       </c>
       <c r="F606" s="9" t="n">
@@ -35194,7 +35194,7 @@
       <c r="D607" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E607" s="8" t="n">
+      <c r="E607" s="9" t="n">
         <v>93300</v>
       </c>
       <c r="F607" s="9" t="n">
@@ -35251,7 +35251,7 @@
       <c r="D608" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E608" s="8" t="n">
+      <c r="E608" s="9" t="n">
         <v>94900</v>
       </c>
       <c r="F608" s="9" t="n">
@@ -35308,7 +35308,7 @@
       <c r="D609" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E609" s="8" t="n">
+      <c r="E609" s="9" t="n">
         <v>94200</v>
       </c>
       <c r="F609" s="9" t="n">
@@ -35365,7 +35365,7 @@
       <c r="D610" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E610" s="8" t="n">
+      <c r="E610" s="9" t="n">
         <v>94900</v>
       </c>
       <c r="F610" s="9" t="n">
@@ -35422,7 +35422,7 @@
       <c r="D611" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E611" s="8" t="n">
+      <c r="E611" s="9" t="n">
         <v>98100</v>
       </c>
       <c r="F611" s="9" t="n">
@@ -35479,7 +35479,7 @@
       <c r="D612" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E612" s="8" t="n">
+      <c r="E612" s="9" t="n">
         <v>98100</v>
       </c>
       <c r="F612" s="9" t="n">
@@ -35536,7 +35536,7 @@
       <c r="D613" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E613" s="8" t="n">
+      <c r="E613" s="9" t="n">
         <v>98000</v>
       </c>
       <c r="F613" s="9" t="n">
@@ -35593,7 +35593,7 @@
       <c r="D614" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E614" s="8" t="n">
+      <c r="E614" s="9" t="n">
         <v>97400</v>
       </c>
       <c r="F614" s="9" t="n">
@@ -35650,7 +35650,7 @@
       <c r="D615" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E615" s="8" t="n">
+      <c r="E615" s="9" t="n">
         <v>99100</v>
       </c>
       <c r="F615" s="9" t="n">
@@ -35707,7 +35707,7 @@
       <c r="D616" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E616" s="8" t="n">
+      <c r="E616" s="9" t="n">
         <v>97200</v>
       </c>
       <c r="F616" s="9" t="n">
@@ -35764,7 +35764,7 @@
       <c r="D617" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E617" s="8" t="n">
+      <c r="E617" s="9" t="n">
         <v>96700</v>
       </c>
       <c r="F617" s="9" t="n">
@@ -35821,7 +35821,7 @@
       <c r="D618" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E618" s="8" t="n">
+      <c r="E618" s="9" t="n">
         <v>96400</v>
       </c>
       <c r="F618" s="9" t="n">
@@ -35878,7 +35878,7 @@
       <c r="D619" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E619" s="8" t="n">
+      <c r="E619" s="9" t="n">
         <v>97200</v>
       </c>
       <c r="F619" s="9" t="n">
@@ -35935,7 +35935,7 @@
       <c r="D620" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E620" s="8" t="n">
+      <c r="E620" s="9" t="n">
         <v>97500</v>
       </c>
       <c r="F620" s="9" t="n">
@@ -35992,7 +35992,7 @@
       <c r="D621" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E621" s="8" t="n">
+      <c r="E621" s="9" t="n">
         <v>96500</v>
       </c>
       <c r="F621" s="9" t="n">
@@ -36049,7 +36049,7 @@
       <c r="D622" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E622" s="8" t="n">
+      <c r="E622" s="9" t="n">
         <v>97600</v>
       </c>
       <c r="F622" s="9" t="n">
@@ -36106,7 +36106,7 @@
       <c r="D623" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E623" s="8" t="n">
+      <c r="E623" s="9" t="n">
         <v>98000</v>
       </c>
       <c r="F623" s="9" t="n">
@@ -36163,7 +36163,7 @@
       <c r="D624" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E624" s="8" t="n">
+      <c r="E624" s="9" t="n">
         <v>95900</v>
       </c>
       <c r="F624" s="9" t="n">
@@ -36220,7 +36220,7 @@
       <c r="D625" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E625" s="8" t="n">
+      <c r="E625" s="9" t="n">
         <v>96500</v>
       </c>
       <c r="F625" s="9" t="n">
@@ -36277,7 +36277,7 @@
       <c r="D626" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E626" s="8" t="n">
+      <c r="E626" s="9" t="n">
         <v>96100</v>
       </c>
       <c r="F626" s="9" t="n">
@@ -36334,7 +36334,7 @@
       <c r="D627" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E627" s="8" t="n">
+      <c r="E627" s="9" t="n">
         <v>95000</v>
       </c>
       <c r="F627" s="9" t="n">
@@ -36393,7 +36393,7 @@
       <c r="D628" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E628" s="8" t="n">
+      <c r="E628" s="9" t="n">
         <v>94200</v>
       </c>
       <c r="F628" s="9" t="n">
@@ -36450,7 +36450,7 @@
       <c r="D629" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E629" s="8" t="n">
+      <c r="E629" s="9" t="n">
         <v>94300</v>
       </c>
       <c r="F629" s="9" t="n">
@@ -36507,7 +36507,7 @@
       <c r="D630" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E630" s="8" t="n">
+      <c r="E630" s="9" t="n">
         <v>92500</v>
       </c>
       <c r="F630" s="9" t="n">
@@ -36564,7 +36564,7 @@
       <c r="D631" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E631" s="8" t="n">
+      <c r="E631" s="9" t="n">
         <v>93400</v>
       </c>
       <c r="F631" s="9" t="n">
@@ -36621,7 +36621,7 @@
       <c r="D632" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E632" s="8" t="n">
+      <c r="E632" s="9" t="n">
         <v>91500</v>
       </c>
       <c r="F632" s="9" t="n">
@@ -36678,7 +36678,7 @@
       <c r="D633" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E633" s="8" t="n">
+      <c r="E633" s="9" t="n">
         <v>92500</v>
       </c>
       <c r="F633" s="9" t="n">
@@ -36735,7 +36735,7 @@
       <c r="D634" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E634" s="8" t="n">
+      <c r="E634" s="9" t="n">
         <v>95900</v>
       </c>
       <c r="F634" s="9" t="n">
@@ -36792,7 +36792,7 @@
       <c r="D635" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E635" s="8" t="n">
+      <c r="E635" s="9" t="n">
         <v>96500</v>
       </c>
       <c r="F635" s="9" t="n">
@@ -36849,7 +36849,7 @@
       <c r="D636" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E636" s="8" t="n">
+      <c r="E636" s="9" t="n">
         <v>103100</v>
       </c>
       <c r="F636" s="9" t="n">
@@ -36906,7 +36906,7 @@
       <c r="D637" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E637" s="8" t="n">
+      <c r="E637" s="9" t="n">
         <v>100000</v>
       </c>
       <c r="F637" s="9" t="n">
@@ -36963,7 +36963,7 @@
       <c r="D638" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E638" s="8" t="n">
+      <c r="E638" s="9" t="n">
         <v>100600</v>
       </c>
       <c r="F638" s="9" t="n">
@@ -37020,7 +37020,7 @@
       <c r="D639" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E639" s="8" t="n">
+      <c r="E639" s="9" t="n">
         <v>97000</v>
       </c>
       <c r="F639" s="9" t="n">
@@ -37077,7 +37077,7 @@
       <c r="D640" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E640" s="8" t="n">
+      <c r="E640" s="9" t="n">
         <v>95500</v>
       </c>
       <c r="F640" s="9" t="n">
@@ -37134,7 +37134,7 @@
       <c r="D641" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E641" s="8" t="n">
+      <c r="E641" s="9" t="n">
         <v>96900</v>
       </c>
       <c r="F641" s="9" t="n">
@@ -37191,7 +37191,7 @@
       <c r="D642" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E642" s="8" t="n">
+      <c r="E642" s="9" t="n">
         <v>97500</v>
       </c>
       <c r="F642" s="9" t="n">
@@ -37248,7 +37248,7 @@
       <c r="D643" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E643" s="8" t="n">
+      <c r="E643" s="9" t="n">
         <v>97000</v>
       </c>
       <c r="F643" s="9" t="n">
@@ -37305,7 +37305,7 @@
       <c r="D644" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E644" s="8" t="n">
+      <c r="E644" s="9" t="n">
         <v>99000</v>
       </c>
       <c r="F644" s="9" t="n">
@@ -37362,7 +37362,7 @@
       <c r="D645" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E645" s="8" t="n">
+      <c r="E645" s="9" t="n">
         <v>98900</v>
       </c>
       <c r="F645" s="9" t="n">
@@ -37419,7 +37419,7 @@
       <c r="D646" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E646" s="8" t="n">
+      <c r="E646" s="9" t="n">
         <v>98900</v>
       </c>
       <c r="F646" s="9" t="n">
@@ -37478,7 +37478,7 @@
       <c r="D647" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E647" s="8" t="n">
+      <c r="E647" s="9" t="n">
         <v>97700</v>
       </c>
       <c r="F647" s="9" t="n">
@@ -37535,7 +37535,7 @@
       <c r="D648" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E648" s="8" t="n">
+      <c r="E648" s="9" t="n">
         <v>97500</v>
       </c>
       <c r="F648" s="9" t="n">
@@ -37592,7 +37592,7 @@
       <c r="D649" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E649" s="8" t="n">
+      <c r="E649" s="9" t="n">
         <v>97400</v>
       </c>
       <c r="F649" s="9" t="n">
@@ -37649,7 +37649,7 @@
       <c r="D650" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E650" s="8" t="n">
+      <c r="E650" s="9" t="n">
         <v>96000</v>
       </c>
       <c r="F650" s="9" t="n">
@@ -37706,7 +37706,7 @@
       <c r="D651" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E651" s="8" t="n">
+      <c r="E651" s="9" t="n">
         <v>98500</v>
       </c>
       <c r="F651" s="9" t="n">
@@ -37763,7 +37763,7 @@
       <c r="D652" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E652" s="8" t="n">
+      <c r="E652" s="9" t="n">
         <v>98700</v>
       </c>
       <c r="F652" s="9" t="n">
@@ -37820,7 +37820,7 @@
       <c r="D653" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E653" s="8" t="n">
+      <c r="E653" s="9" t="n">
         <v>98200</v>
       </c>
       <c r="F653" s="9" t="n">
@@ -37877,7 +37877,7 @@
       <c r="D654" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E654" s="8" t="n">
+      <c r="E654" s="9" t="n">
         <v>96500</v>
       </c>
       <c r="F654" s="9" t="n">
@@ -37934,7 +37934,7 @@
       <c r="D655" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E655" s="8" t="n">
+      <c r="E655" s="9" t="n">
         <v>97300</v>
       </c>
       <c r="F655" s="9" t="n">
@@ -37991,7 +37991,7 @@
       <c r="D656" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E656" s="8" t="n">
+      <c r="E656" s="9" t="n">
         <v>99500</v>
       </c>
       <c r="F656" s="9" t="n">
@@ -38048,7 +38048,7 @@
       <c r="D657" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E657" s="8" t="n">
+      <c r="E657" s="9" t="n">
         <v>100300.000003837</v>
       </c>
       <c r="F657" s="9" t="n">
@@ -38105,7 +38105,7 @@
       <c r="D658" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E658" s="8" t="n">
+      <c r="E658" s="9" t="n">
         <v>100896.4321148609</v>
       </c>
       <c r="F658" s="9" t="n">
@@ -38162,7 +38162,7 @@
       <c r="D659" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E659" s="8" t="n">
+      <c r="E659" s="9" t="n">
         <v>98411.29831892833</v>
       </c>
       <c r="F659" s="9" t="n">
@@ -38219,7 +38219,7 @@
       <c r="D660" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E660" s="8" t="n">
+      <c r="E660" s="9" t="n">
         <v>98411.29831892833</v>
       </c>
       <c r="F660" s="9" t="n">
@@ -38276,7 +38276,7 @@
       <c r="D661" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E661" s="8" t="n">
+      <c r="E661" s="9" t="n">
         <v>95926.16452299579</v>
       </c>
       <c r="F661" s="9" t="n">
@@ -38333,7 +38333,7 @@
       <c r="D662" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E662" s="8" t="n">
+      <c r="E662" s="9" t="n">
         <v>95926.16452299579</v>
       </c>
       <c r="F662" s="9" t="n">
@@ -38390,7 +38390,7 @@
       <c r="D663" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E663" s="8" t="n">
+      <c r="E663" s="9" t="n">
         <v>94435.08424543629</v>
       </c>
       <c r="F663" s="9" t="n">
@@ -38447,7 +38447,7 @@
       <c r="D664" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E664" s="8" t="n">
+      <c r="E664" s="9" t="n">
         <v>96224.3805785077</v>
       </c>
       <c r="F664" s="9" t="n">
@@ -38504,7 +38504,7 @@
       <c r="D665" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E665" s="8" t="n">
+      <c r="E665" s="9" t="n">
         <v>95031.51635646008</v>
       </c>
       <c r="F665" s="9" t="n">
@@ -38561,7 +38561,7 @@
       <c r="D666" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E666" s="8" t="n">
+      <c r="E666" s="9" t="n">
         <v>95130.92170829738</v>
       </c>
       <c r="F666" s="9" t="n">
@@ -38618,7 +38618,7 @@
       <c r="D667" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E667" s="8" t="n">
+      <c r="E667" s="9" t="n">
         <v>89862.43806092041</v>
       </c>
       <c r="F667" s="9" t="n">
@@ -38677,7 +38677,7 @@
       <c r="D668" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E668" s="8" t="n">
+      <c r="E668" s="9" t="n">
         <v>89663.62735724582</v>
       </c>
       <c r="F668" s="9" t="n">
@@ -38734,7 +38734,7 @@
       <c r="D669" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E669" s="8" t="n">
+      <c r="E669" s="9" t="n">
         <v>89365.41130173391</v>
       </c>
       <c r="F669" s="9" t="n">
@@ -38791,7 +38791,7 @@
       <c r="D670" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E670" s="8" t="n">
+      <c r="E670" s="9" t="n">
         <v>87973.73637601169</v>
       </c>
       <c r="F670" s="9" t="n">
@@ -38848,7 +38848,7 @@
       <c r="D671" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E671" s="8" t="n">
+      <c r="E671" s="9" t="n">
         <v>87277.89891315058</v>
       </c>
       <c r="F671" s="9" t="n">
@@ -38905,7 +38905,7 @@
       <c r="D672" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E672" s="8" t="n">
+      <c r="E672" s="9" t="n">
         <v>89067.19524622201</v>
       </c>
       <c r="F672" s="9" t="n">
@@ -38962,7 +38962,7 @@
       <c r="D673" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E673" s="8" t="n">
+      <c r="E673" s="9" t="n">
         <v>87576.11496866248</v>
       </c>
       <c r="F673" s="9" t="n">
@@ -39019,7 +39019,7 @@
       <c r="D674" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E674" s="8" t="n">
+      <c r="E674" s="9" t="n">
         <v>88172.54707968629</v>
       </c>
       <c r="F674" s="9" t="n">
@@ -39076,7 +39076,7 @@
       <c r="D675" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E675" s="8" t="n">
+      <c r="E675" s="9" t="n">
         <v>88172.54707968629</v>
       </c>
       <c r="F675" s="9" t="n">
@@ -39133,7 +39133,7 @@
       <c r="D676" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E676" s="8" t="n">
+      <c r="E676" s="9" t="n">
         <v>89961.84341275772</v>
       </c>
       <c r="F676" s="9" t="n">
@@ -39190,7 +39190,7 @@
       <c r="D677" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E677" s="8" t="n">
+      <c r="E677" s="9" t="n">
         <v>90359.46482010692</v>
       </c>
       <c r="F677" s="9" t="n">
@@ -39247,7 +39247,7 @@
       <c r="D678" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E678" s="8" t="n">
+      <c r="E678" s="9" t="n">
         <v>90657.68087561884</v>
       </c>
       <c r="F678" s="9" t="n">
@@ -39304,7 +39304,7 @@
       <c r="D679" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E679" s="8" t="n">
+      <c r="E679" s="9" t="n">
         <v>90458.87017194422</v>
       </c>
       <c r="F679" s="9" t="n">
@@ -39361,7 +39361,7 @@
       <c r="D680" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E680" s="8" t="n">
+      <c r="E680" s="9" t="n">
         <v>90458.87017194422</v>
       </c>
       <c r="F680" s="9" t="n">
@@ -39418,7 +39418,7 @@
       <c r="D681" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E681" s="8" t="n">
+      <c r="E681" s="9" t="n">
         <v>91353.51833847992</v>
       </c>
       <c r="F681" s="9" t="n">
@@ -39475,7 +39475,7 @@
       <c r="D682" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E682" s="8" t="n">
+      <c r="E682" s="9" t="n">
         <v>91154.70763480532</v>
       </c>
       <c r="F682" s="9" t="n">
@@ -39532,7 +39532,7 @@
       <c r="D683" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E683" s="8" t="n">
+      <c r="E683" s="9" t="n">
         <v>90955.89693113072</v>
       </c>
       <c r="F683" s="9" t="n">
@@ -39591,7 +39591,7 @@
       <c r="D684" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E684" s="8" t="n">
+      <c r="E684" s="9" t="n">
         <v>90856.49157929342</v>
       </c>
       <c r="F684" s="9" t="n">
@@ -39648,7 +39648,7 @@
       <c r="D685" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E685" s="8" t="n">
+      <c r="E685" s="9" t="n">
         <v>90757.08622745612</v>
       </c>
       <c r="F685" s="9" t="n">
@@ -39705,7 +39705,7 @@
       <c r="D686" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E686" s="8" t="n">
+      <c r="E686" s="9" t="n">
         <v>88967.7898943847</v>
       </c>
       <c r="F686" s="9" t="n">
@@ -39762,7 +39762,7 @@
       <c r="D687" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E687" s="8" t="n">
+      <c r="E687" s="9" t="n">
         <v>88967.7898943847</v>
       </c>
       <c r="F687" s="9" t="n">
@@ -39819,7 +39819,7 @@
       <c r="D688" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E688" s="8" t="n">
+      <c r="E688" s="9" t="n">
         <v>88868.3845425474</v>
       </c>
       <c r="F688" s="9" t="n">
@@ -39876,7 +39876,7 @@
       <c r="D689" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E689" s="8" t="n">
+      <c r="E689" s="9" t="n">
         <v>89266.0059498966</v>
       </c>
       <c r="F689" s="9" t="n">
@@ -39933,7 +39933,7 @@
       <c r="D690" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E690" s="8" t="n">
+      <c r="E690" s="9" t="n">
         <v>87178.49356131327</v>
       </c>
       <c r="F690" s="9" t="n">
@@ -39990,7 +39990,7 @@
       <c r="D691" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E691" s="8" t="n">
+      <c r="E691" s="9" t="n">
         <v>87675.52032049978</v>
       </c>
       <c r="F691" s="9" t="n">
@@ -40047,7 +40047,7 @@
       <c r="D692" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E692" s="8" t="n">
+      <c r="E692" s="9" t="n">
         <v>88470.7631351982</v>
       </c>
       <c r="F692" s="9" t="n">
@@ -40104,7 +40104,7 @@
       <c r="D693" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E693" s="8" t="n">
+      <c r="E693" s="9" t="n">
         <v>88073.14172784898</v>
       </c>
       <c r="F693" s="9" t="n">
@@ -40161,7 +40161,7 @@
       <c r="D694" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E694" s="8" t="n">
+      <c r="E694" s="9" t="n">
         <v>85886.22398742836</v>
       </c>
       <c r="F694" s="9" t="n">
@@ -40218,7 +40218,7 @@
       <c r="D695" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E695" s="8" t="n">
+      <c r="E695" s="9" t="n">
         <v>83997.52230251963</v>
       </c>
       <c r="F695" s="9" t="n">
@@ -40275,7 +40275,7 @@
       <c r="D696" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E696" s="8" t="n">
+      <c r="E696" s="9" t="n">
         <v>84494.54906170614</v>
       </c>
       <c r="F696" s="9" t="n">
@@ -40332,7 +40332,7 @@
       <c r="D697" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E697" s="8" t="n">
+      <c r="E697" s="9" t="n">
         <v>85687.41328375376</v>
       </c>
       <c r="F697" s="9" t="n">
@@ -40389,7 +40389,7 @@
       <c r="D698" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E698" s="8" t="n">
+      <c r="E698" s="9" t="n">
         <v>86383.25074661487</v>
       </c>
       <c r="F698" s="9" t="n">
@@ -40446,7 +40446,7 @@
       <c r="D699" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E699" s="8" t="n">
+      <c r="E699" s="9" t="n">
         <v>84991.57582089264</v>
       </c>
       <c r="F699" s="9" t="n">
@@ -40503,7 +40503,7 @@
       <c r="D700" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E700" s="8" t="n">
+      <c r="E700" s="9" t="n">
         <v>83798.71159884502</v>
       </c>
       <c r="F700" s="9" t="n">
@@ -40560,7 +40560,7 @@
       <c r="D701" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E701" s="8" t="n">
+      <c r="E701" s="9" t="n">
         <v>82904.06343230931</v>
       </c>
       <c r="F701" s="9" t="n">
@@ -40617,7 +40617,7 @@
       <c r="D702" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E702" s="8" t="n">
+      <c r="E702" s="9" t="n">
         <v>84096.92765435693</v>
       </c>
       <c r="F702" s="9" t="n">
@@ -40674,7 +40674,7 @@
       <c r="D703" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E703" s="8" t="n">
+      <c r="E703" s="9" t="n">
         <v>85488.60258007915</v>
       </c>
       <c r="F703" s="9" t="n">
@@ -40731,7 +40731,7 @@
       <c r="D704" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E704" s="8" t="n">
+      <c r="E704" s="9" t="n">
         <v>85488.60258007915</v>
       </c>
       <c r="F704" s="9" t="n">
@@ -40788,7 +40788,7 @@
       <c r="D705" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E705" s="8" t="n">
+      <c r="E705" s="9" t="n">
         <v>85488.60258007915</v>
       </c>
       <c r="F705" s="9" t="n">
@@ -40856,7 +40856,7 @@
       <c r="D706" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E706" s="8" t="n">
+      <c r="E706" s="9" t="n">
         <v>84295.73835803154</v>
       </c>
       <c r="F706" s="9" t="n">
@@ -40913,7 +40913,7 @@
       <c r="D707" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E707" s="8" t="n">
+      <c r="E707" s="9" t="n">
         <v>84792.76511721805</v>
       </c>
       <c r="F707" s="9" t="n">
@@ -40970,7 +40970,7 @@
       <c r="D708" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E708" s="8" t="n">
+      <c r="E708" s="9" t="n">
         <v>85090.98117272995</v>
       </c>
       <c r="F708" s="9" t="n">
@@ -41027,7 +41027,7 @@
       <c r="D709" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E709" s="8" t="n">
+      <c r="E709" s="9" t="n">
         <v>83997.52230251963</v>
       </c>
       <c r="F709" s="9" t="n">
@@ -41084,7 +41084,7 @@
       <c r="D710" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E710" s="8" t="n">
+      <c r="E710" s="9" t="n">
         <v>83301.68483965853</v>
       </c>
       <c r="F710" s="9" t="n">
@@ -41141,7 +41141,7 @@
       <c r="D711" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E711" s="8" t="n">
+      <c r="E711" s="9" t="n">
         <v>83401.09019149582</v>
       </c>
       <c r="F711" s="9" t="n">
@@ -41198,7 +41198,7 @@
       <c r="D712" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E712" s="8" t="n">
+      <c r="E712" s="9" t="n">
         <v>79822.49752535297</v>
       </c>
       <c r="F712" s="9" t="n">
@@ -41255,7 +41255,7 @@
       <c r="D713" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E713" s="8" t="n">
+      <c r="E713" s="9" t="n">
         <v>78927.84935881727</v>
       </c>
       <c r="F713" s="9" t="n">
@@ -41312,7 +41312,7 @@
       <c r="D714" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E714" s="8" t="n">
+      <c r="E714" s="9" t="n">
         <v>79027.25471065457</v>
       </c>
       <c r="F714" s="9" t="n">
@@ -41369,7 +41369,7 @@
       <c r="D715" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E715" s="8" t="n">
+      <c r="E715" s="9" t="n">
         <v>78729.03865514266</v>
       </c>
       <c r="F715" s="9" t="n">
@@ -41426,7 +41426,7 @@
       <c r="D716" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E716" s="8" t="n">
+      <c r="E716" s="9" t="n">
         <v>79126.66006249186</v>
       </c>
       <c r="F716" s="9" t="n">
@@ -41483,7 +41483,7 @@
       <c r="D717" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E717" s="8" t="n">
+      <c r="E717" s="9" t="n">
         <v>79921.90287719028</v>
       </c>
       <c r="F717" s="9" t="n">
@@ -41540,7 +41540,7 @@
       <c r="D718" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E718" s="8" t="n">
+      <c r="E718" s="9" t="n">
         <v>79822.49752535297</v>
       </c>
       <c r="F718" s="9" t="n">
@@ -41597,7 +41597,7 @@
       <c r="D719" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E719" s="8" t="n">
+      <c r="E719" s="9" t="n">
         <v>79524.28146984107</v>
       </c>
       <c r="F719" s="9" t="n">
@@ -41654,7 +41654,7 @@
       <c r="D720" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E720" s="8" t="n">
+      <c r="E720" s="9" t="n">
         <v>78132.60654411885</v>
       </c>
       <c r="F720" s="9" t="n">
@@ -41711,7 +41711,7 @@
       <c r="D721" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E721" s="8" t="n">
+      <c r="E721" s="9" t="n">
         <v>78033.20119228156</v>
       </c>
       <c r="F721" s="9" t="n">
@@ -41768,7 +41768,7 @@
       <c r="D722" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E722" s="8" t="n">
+      <c r="E722" s="9" t="n">
         <v>79623.68682167838</v>
       </c>
       <c r="F722" s="9" t="n">
@@ -41825,7 +41825,7 @@
       <c r="D723" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E723" s="8" t="n">
+      <c r="E723" s="9" t="n">
         <v>79524.28146984107</v>
       </c>
       <c r="F723" s="9" t="n">
@@ -41882,7 +41882,7 @@
       <c r="D724" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E724" s="8" t="n">
+      <c r="E724" s="9" t="n">
         <v>80021.30822902758</v>
       </c>
       <c r="F724" s="9" t="n">
@@ -41939,7 +41939,7 @@
       <c r="D725" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E725" s="8" t="n">
+      <c r="E725" s="9" t="n">
         <v>79822.49752535297</v>
       </c>
       <c r="F725" s="9" t="n">
@@ -41996,7 +41996,7 @@
       <c r="D726" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E726" s="8" t="n">
+      <c r="E726" s="9" t="n">
         <v>80021.30822902758</v>
       </c>
       <c r="F726" s="9" t="n">
@@ -42055,7 +42055,7 @@
       <c r="D727" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E727" s="8" t="n">
+      <c r="E727" s="9" t="n">
         <v>79424.87611800377</v>
       </c>
       <c r="F727" s="9" t="n">
@@ -42112,7 +42112,7 @@
       <c r="D728" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E728" s="8" t="n">
+      <c r="E728" s="9" t="n">
         <v>78629.63330330537</v>
       </c>
       <c r="F728" s="9" t="n">
@@ -42169,7 +42169,7 @@
       <c r="D729" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E729" s="8" t="n">
+      <c r="E729" s="9" t="n">
         <v>79027.25471065457</v>
       </c>
       <c r="F729" s="9" t="n">
@@ -42226,7 +42226,7 @@
       <c r="D730" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E730" s="8" t="n">
+      <c r="E730" s="9" t="n">
         <v>79921.90287719028</v>
       </c>
       <c r="F730" s="9" t="n">
@@ -42283,7 +42283,7 @@
       <c r="D731" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E731" s="8" t="n">
+      <c r="E731" s="9" t="n">
         <v>80319.52428453948</v>
       </c>
       <c r="F731" s="9" t="n">
@@ -42340,7 +42340,7 @@
       <c r="D732" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E732" s="8" t="n">
+      <c r="E732" s="9" t="n">
         <v>80717.14569188868</v>
       </c>
       <c r="F732" s="9" t="n">
@@ -42397,7 +42397,7 @@
       <c r="D733" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E733" s="8" t="n">
+      <c r="E733" s="9" t="n">
         <v>80617.74034005139</v>
       </c>
       <c r="F733" s="9" t="n">
@@ -42454,7 +42454,7 @@
       <c r="D734" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E734" s="8" t="n">
+      <c r="E734" s="9" t="n">
         <v>78530.22795146806</v>
       </c>
       <c r="F734" s="9" t="n">
@@ -42511,7 +42511,7 @@
       <c r="D735" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E735" s="8" t="n">
+      <c r="E735" s="9" t="n">
         <v>78430.82259963076</v>
       </c>
       <c r="F735" s="9" t="n">
@@ -42568,7 +42568,7 @@
       <c r="D736" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E736" s="8" t="n">
+      <c r="E736" s="9" t="n">
         <v>77536.17443309505</v>
       </c>
       <c r="F736" s="9" t="n">
@@ -42625,7 +42625,7 @@
       <c r="D737" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E737" s="8" t="n">
+      <c r="E737" s="9" t="n">
         <v>77834.39048860695</v>
       </c>
       <c r="F737" s="9" t="n">
@@ -42682,7 +42682,7 @@
       <c r="D738" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E738" s="8" t="n">
+      <c r="E738" s="9" t="n">
         <v>77635.57978493234</v>
       </c>
       <c r="F738" s="9" t="n">
@@ -42739,7 +42739,7 @@
       <c r="D739" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E739" s="8" t="n">
+      <c r="E739" s="9" t="n">
         <v>75647.47274818632</v>
       </c>
       <c r="F739" s="9" t="n">
@@ -42796,7 +42796,7 @@
       <c r="D740" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E740" s="8" t="n">
+      <c r="E740" s="9" t="n">
         <v>75548.06739634901</v>
       </c>
       <c r="F740" s="9" t="n">
@@ -42853,7 +42853,7 @@
       <c r="D741" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E741" s="8" t="n">
+      <c r="E741" s="9" t="n">
         <v>76045.09415553552</v>
       </c>
       <c r="F741" s="9" t="n">
@@ -42910,7 +42910,7 @@
       <c r="D742" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E742" s="8" t="n">
+      <c r="E742" s="9" t="n">
         <v>76542.12091472204</v>
       </c>
       <c r="F742" s="9" t="n">
@@ -42967,7 +42967,7 @@
       <c r="D743" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E743" s="8" t="n">
+      <c r="E743" s="9" t="n">
         <v>75448.66204451172</v>
       </c>
       <c r="F743" s="9" t="n">
@@ -43024,7 +43024,7 @@
       <c r="D744" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E744" s="8" t="n">
+      <c r="E744" s="9" t="n">
         <v>76144.49950737282</v>
       </c>
       <c r="F744" s="9" t="n">
@@ -43081,7 +43081,7 @@
       <c r="D745" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E745" s="8" t="n">
+      <c r="E745" s="9" t="n">
         <v>73361.14965592838</v>
       </c>
       <c r="F745" s="9" t="n">
@@ -43138,7 +43138,7 @@
       <c r="D746" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E746" s="8" t="n">
+      <c r="E746" s="9" t="n">
         <v>73361.14965592838</v>
       </c>
       <c r="F746" s="9" t="n">
@@ -43195,7 +43195,7 @@
       <c r="D747" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E747" s="8" t="n">
+      <c r="E747" s="9" t="n">
         <v>71571.85332285697</v>
       </c>
       <c r="F747" s="9" t="n">
@@ -43252,7 +43252,7 @@
       <c r="D748" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E748" s="8" t="n">
+      <c r="E748" s="9" t="n">
         <v>71571.85332285697</v>
       </c>
       <c r="F748" s="9" t="n">
@@ -43311,7 +43311,7 @@
       <c r="D749" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E749" s="8" t="n">
+      <c r="E749" s="9" t="n">
         <v>72466.50148939267</v>
       </c>
       <c r="F749" s="9" t="n">
@@ -43368,7 +43368,7 @@
       <c r="D750" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E750" s="8" t="n">
+      <c r="E750" s="9" t="n">
         <v>73162.33895225379</v>
       </c>
       <c r="F750" s="9" t="n">
@@ -43425,7 +43425,7 @@
       <c r="D751" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E751" s="8" t="n">
+      <c r="E751" s="9" t="n">
         <v>73559.96035960299</v>
       </c>
       <c r="F751" s="9" t="n">
@@ -43482,7 +43482,7 @@
       <c r="D752" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E752" s="8" t="n">
+      <c r="E752" s="9" t="n">
         <v>73858.1764151149</v>
       </c>
       <c r="F752" s="9" t="n">
@@ -43539,7 +43539,7 @@
       <c r="D753" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E753" s="8" t="n">
+      <c r="E753" s="9" t="n">
         <v>74355.20317430141</v>
       </c>
       <c r="F753" s="9" t="n">
@@ -43596,7 +43596,7 @@
       <c r="D754" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E754" s="8" t="n">
+      <c r="E754" s="9" t="n">
         <v>73858.1764151149</v>
       </c>
       <c r="F754" s="9" t="n">
@@ -43653,7 +43653,7 @@
       <c r="D755" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E755" s="8" t="n">
+      <c r="E755" s="9" t="n">
         <v>74951.63528532522</v>
       </c>
       <c r="F755" s="9" t="n">
@@ -43710,7 +43710,7 @@
       <c r="D756" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E756" s="8" t="n">
+      <c r="E756" s="9" t="n">
         <v>74653.4192284953</v>
       </c>
       <c r="F756" s="9" t="n">
@@ -43767,7 +43767,7 @@
       <c r="D757" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E757" s="8" t="n">
+      <c r="E757" s="9" t="n">
         <v>75735.35284050248</v>
       </c>
       <c r="F757" s="9" t="n">
@@ -43824,7 +43824,7 @@
       <c r="D758" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E758" s="8" t="n">
+      <c r="E758" s="9" t="n">
         <v>77800.86246342528</v>
       </c>
       <c r="F758" s="9" t="n">
@@ -43881,7 +43881,7 @@
       <c r="D759" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E759" s="8" t="n">
+      <c r="E759" s="9" t="n">
         <v>78587.72327215777</v>
       </c>
       <c r="F759" s="9" t="n">
@@ -43938,7 +43938,7 @@
       <c r="D760" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E760" s="8" t="n">
+      <c r="E760" s="9" t="n">
         <v>78489.36567106622</v>
       </c>
       <c r="F760" s="9" t="n">
@@ -43995,7 +43995,7 @@
       <c r="D761" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E761" s="8" t="n">
+      <c r="E761" s="9" t="n">
         <v>78686.08087324933</v>
       </c>
       <c r="F761" s="9" t="n">
@@ -44052,7 +44052,7 @@
       <c r="D762" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E762" s="8" t="n">
+      <c r="E762" s="9" t="n">
         <v>78981.15367652402</v>
       </c>
       <c r="F762" s="9" t="n">
@@ -44109,7 +44109,7 @@
       <c r="D763" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E763" s="8" t="n">
+      <c r="E763" s="9" t="n">
         <v>78194.29286779153</v>
       </c>
       <c r="F763" s="9" t="n">
@@ -44166,7 +44166,7 @@
       <c r="D764" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E764" s="8" t="n">
+      <c r="E764" s="9" t="n">
         <v>78686.08087324933</v>
       </c>
       <c r="F764" s="9" t="n">
@@ -44223,7 +44223,7 @@
       <c r="D765" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E765" s="8" t="n">
+      <c r="E765" s="9" t="n">
         <v>76718.9288514181</v>
       </c>
       <c r="F765" s="9" t="n">
@@ -44280,7 +44280,7 @@
       <c r="D766" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E766" s="8" t="n">
+      <c r="E766" s="9" t="n">
         <v>76522.21364923498</v>
       </c>
       <c r="F766" s="9" t="n">
@@ -44337,7 +44337,7 @@
       <c r="D767" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E767" s="8" t="n">
+      <c r="E767" s="9" t="n">
         <v>76325.49844705185</v>
       </c>
       <c r="F767" s="9" t="n">
@@ -44394,7 +44394,7 @@
       <c r="D768" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E768" s="8" t="n">
+      <c r="E768" s="9" t="n">
         <v>76227.1408459603</v>
       </c>
       <c r="F768" s="9" t="n">
@@ -44451,7 +44451,7 @@
       <c r="D769" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E769" s="8" t="n">
+      <c r="E769" s="9" t="n">
         <v>77604.14726124216</v>
       </c>
       <c r="F769" s="9" t="n">
@@ -44508,7 +44508,7 @@
       <c r="D770" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E770" s="8" t="n">
+      <c r="E770" s="9" t="n">
         <v>77505.78966015059</v>
       </c>
       <c r="F770" s="9" t="n">
@@ -44567,7 +44567,7 @@
       <c r="D771" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E771" s="8" t="n">
+      <c r="E771" s="9" t="n">
         <v>77210.71685687591</v>
       </c>
       <c r="F771" s="9" t="n">
@@ -44624,7 +44624,7 @@
       <c r="D772" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E772" s="8" t="n">
+      <c r="E772" s="9" t="n">
         <v>77800.86246342528</v>
       </c>
       <c r="F772" s="9" t="n">
@@ -44681,7 +44681,7 @@
       <c r="D773" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E773" s="8" t="n">
+      <c r="E773" s="9" t="n">
         <v>77210.71685687591</v>
       </c>
       <c r="F773" s="9" t="n">
@@ -44738,7 +44738,7 @@
       <c r="D774" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E774" s="8" t="n">
+      <c r="E774" s="9" t="n">
         <v>78489.36567106622</v>
       </c>
       <c r="F774" s="9" t="n">
@@ -44795,7 +44795,7 @@
       <c r="D775" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E775" s="8" t="n">
+      <c r="E775" s="9" t="n">
         <v>79669.65688416496</v>
       </c>
       <c r="F775" s="9" t="n">
@@ -44852,7 +44852,7 @@
       <c r="D776" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E776" s="8" t="n">
+      <c r="E776" s="9" t="n">
         <v>81243.37850162994</v>
       </c>
       <c r="F776" s="9" t="n">
@@ -44909,7 +44909,7 @@
       <c r="D777" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E777" s="8" t="n">
+      <c r="E777" s="9" t="n">
         <v>81341.73610272149</v>
       </c>
       <c r="F777" s="9" t="n">
@@ -44966,7 +44966,7 @@
       <c r="D778" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E778" s="8" t="n">
+      <c r="E778" s="9" t="n">
         <v>79866.37208634807</v>
       </c>
       <c r="F778" s="9" t="n">
@@ -45023,7 +45023,7 @@
       <c r="D779" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E779" s="8" t="n">
+      <c r="E779" s="9" t="n">
         <v>80161.44488962275</v>
       </c>
       <c r="F779" s="9" t="n">
@@ -45080,7 +45080,7 @@
       <c r="D780" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E780" s="8" t="n">
+      <c r="E780" s="9" t="n">
         <v>80063.0872885312</v>
       </c>
       <c r="F780" s="9" t="n">
@@ -45137,7 +45137,7 @@
       <c r="D781" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E781" s="8" t="n">
+      <c r="E781" s="9" t="n">
         <v>79866.37208634807</v>
       </c>
       <c r="F781" s="9" t="n">
@@ -45194,7 +45194,7 @@
       <c r="D782" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E782" s="8" t="n">
+      <c r="E782" s="9" t="n">
         <v>81931.88170927086</v>
       </c>
       <c r="F782" s="9" t="n">
@@ -45251,7 +45251,7 @@
       <c r="D783" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E783" s="8" t="n">
+      <c r="E783" s="9" t="n">
         <v>82226.95451254556</v>
       </c>
       <c r="F783" s="9" t="n">
@@ -45308,7 +45308,7 @@
       <c r="D784" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E784" s="8" t="n">
+      <c r="E784" s="9" t="n">
         <v>82226.95451254556</v>
       </c>
       <c r="F784" s="9" t="n">
@@ -45365,7 +45365,7 @@
       <c r="D785" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E785" s="8" t="n">
+      <c r="E785" s="9" t="n">
         <v>82620.3849169118</v>
       </c>
       <c r="F785" s="9" t="n">
@@ -45422,7 +45422,7 @@
       <c r="D786" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E786" s="8" t="n">
+      <c r="E786" s="9" t="n">
         <v>82817.10011909493</v>
       </c>
       <c r="F786" s="9" t="n">
@@ -45479,7 +45479,7 @@
       <c r="D787" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E787" s="8" t="n">
+      <c r="E787" s="9" t="n">
         <v>79768.01448525651</v>
       </c>
       <c r="F787" s="9" t="n">
@@ -45536,7 +45536,7 @@
       <c r="D788" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E788" s="8" t="n">
+      <c r="E788" s="9" t="n">
         <v>79177.86887870714</v>
       </c>
       <c r="F788" s="9" t="n">
@@ -45593,7 +45593,7 @@
       <c r="D789" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E789" s="8" t="n">
+      <c r="E789" s="9" t="n">
         <v>79177.86887870714</v>
       </c>
       <c r="F789" s="9" t="n">
@@ -45652,7 +45652,7 @@
       <c r="D790" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E790" s="8" t="n">
+      <c r="E790" s="9" t="n">
         <v>79374.58408089027</v>
       </c>
       <c r="F790" s="9" t="n">
@@ -45709,7 +45709,7 @@
       <c r="D791" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E791" s="8" t="n">
+      <c r="E791" s="9" t="n">
         <v>79079.51127761559</v>
       </c>
       <c r="F791" s="9" t="n">
@@ -45766,7 +45766,7 @@
       <c r="D792" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E792" s="8" t="n">
+      <c r="E792" s="9" t="n">
         <v>78194.29286779153</v>
       </c>
       <c r="F792" s="9" t="n">
@@ -45823,7 +45823,7 @@
       <c r="D793" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E793" s="8" t="n">
+      <c r="E793" s="9" t="n">
         <v>77014.00165469278</v>
       </c>
       <c r="F793" s="9" t="n">
@@ -45880,7 +45880,7 @@
       <c r="D794" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E794" s="8" t="n">
+      <c r="E794" s="9" t="n">
         <v>76718.9288514181</v>
       </c>
       <c r="F794" s="9" t="n">
@@ -45937,7 +45937,7 @@
       <c r="D795" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E795" s="8" t="n">
+      <c r="E795" s="9" t="n">
         <v>76227.1408459603</v>
       </c>
       <c r="F795" s="9" t="n">
@@ -45994,7 +45994,7 @@
       <c r="D796" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E796" s="8" t="n">
+      <c r="E796" s="9" t="n">
         <v>77210.71685687591</v>
       </c>
       <c r="F796" s="9" t="n">
@@ -46051,7 +46051,7 @@
       <c r="D797" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E797" s="8" t="n">
+      <c r="E797" s="9" t="n">
         <v>77702.50486233372</v>
       </c>
       <c r="F797" s="9" t="n">
@@ -46108,7 +46108,7 @@
       <c r="D798" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E798" s="8" t="n">
+      <c r="E798" s="9" t="n">
         <v>77210.71685687591</v>
       </c>
       <c r="F798" s="9" t="n">
@@ -46165,7 +46165,7 @@
       <c r="D799" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E799" s="8" t="n">
+      <c r="E799" s="9" t="n">
         <v>78882.79607543246</v>
       </c>
       <c r="F799" s="9" t="n">
@@ -46222,7 +46222,7 @@
       <c r="D800" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E800" s="8" t="n">
+      <c r="E800" s="9" t="n">
         <v>78882.79607543246</v>
       </c>
       <c r="F800" s="9" t="n">
@@ -46279,7 +46279,7 @@
       <c r="D801" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E801" s="8" t="n">
+      <c r="E801" s="9" t="n">
         <v>77702.50486233372</v>
       </c>
       <c r="F801" s="9" t="n">
@@ -46336,7 +46336,7 @@
       <c r="D802" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E802" s="8" t="n">
+      <c r="E802" s="9" t="n">
         <v>78095.93526669996</v>
       </c>
       <c r="F802" s="9" t="n">
@@ -46393,7 +46393,7 @@
       <c r="D803" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E803" s="8" t="n">
+      <c r="E803" s="9" t="n">
         <v>78095.93526669996</v>
       </c>
       <c r="F803" s="9" t="n">
@@ -46450,7 +46450,7 @@
       <c r="D804" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E804" s="8" t="n">
+      <c r="E804" s="9" t="n">
         <v>77702.50486233372</v>
       </c>
       <c r="F804" s="9" t="n">
@@ -46507,7 +46507,7 @@
       <c r="D805" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E805" s="8" t="n">
+      <c r="E805" s="9" t="n">
         <v>78981.15367652402</v>
       </c>
       <c r="F805" s="9" t="n">
@@ -46564,7 +46564,7 @@
       <c r="D806" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E806" s="8" t="n">
+      <c r="E806" s="9" t="n">
         <v>80063.0872885312</v>
       </c>
       <c r="F806" s="9" t="n">
@@ -46621,7 +46621,7 @@
       <c r="D807" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E807" s="8" t="n">
+      <c r="E807" s="9" t="n">
         <v>80849.9480972637</v>
       </c>
       <c r="F807" s="9" t="n">
@@ -46678,7 +46678,7 @@
       <c r="D808" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E808" s="8" t="n">
+      <c r="E808" s="9" t="n">
         <v>79472.94168198183</v>
       </c>
       <c r="F808" s="9" t="n">
@@ -46735,7 +46735,7 @@
       <c r="D809" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E809" s="8" t="n">
+      <c r="E809" s="9" t="n">
         <v>79964.72968743964</v>
       </c>
       <c r="F809" s="9" t="n">
@@ -46792,7 +46792,7 @@
       <c r="D810" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E810" s="8" t="n">
+      <c r="E810" s="9" t="n">
         <v>80161.44488962275</v>
       </c>
       <c r="F810" s="9" t="n">
@@ -46849,7 +46849,7 @@
       <c r="D811" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E811" s="8" t="n">
+      <c r="E811" s="9" t="n">
         <v>79669.65688416496</v>
       </c>
       <c r="F811" s="9" t="n">
@@ -46906,7 +46906,7 @@
       <c r="D812" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E812" s="8" t="n">
+      <c r="E812" s="9" t="n">
         <v>81636.80890599618</v>
       </c>
       <c r="F812" s="9" t="n">
@@ -46965,7 +46965,7 @@
       <c r="D813" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E813" s="8" t="n">
+      <c r="E813" s="9" t="n">
         <v>81243.37850162994</v>
       </c>
       <c r="F813" s="9" t="n">
@@ -47022,7 +47022,7 @@
       <c r="D814" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E814" s="8" t="n">
+      <c r="E814" s="9" t="n">
         <v>79571.29928307339</v>
       </c>
       <c r="F814" s="9" t="n">
@@ -47079,7 +47079,7 @@
       <c r="D815" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E815" s="8" t="n">
+      <c r="E815" s="9" t="n">
         <v>80456.51769289744</v>
       </c>
       <c r="F815" s="9" t="n">
@@ -47136,7 +47136,7 @@
       <c r="D816" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E816" s="8" t="n">
+      <c r="E816" s="9" t="n">
         <v>79177.86887870714</v>
       </c>
       <c r="F816" s="9" t="n">
@@ -47193,7 +47193,7 @@
       <c r="D817" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E817" s="8" t="n">
+      <c r="E817" s="9" t="n">
         <v>77997.57766560841</v>
       </c>
       <c r="F817" s="9" t="n">
@@ -47250,7 +47250,7 @@
       <c r="D818" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E818" s="8" t="n">
+      <c r="E818" s="9" t="n">
         <v>78686.08087324933</v>
       </c>
       <c r="F818" s="9" t="n">
@@ -47307,7 +47307,7 @@
       <c r="D819" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E819" s="8" t="n">
+      <c r="E819" s="9" t="n">
         <v>77604.14726124216</v>
       </c>
       <c r="F819" s="9" t="n">
@@ -47364,7 +47364,7 @@
       <c r="D820" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E820" s="8" t="n">
+      <c r="E820" s="9" t="n">
         <v>77309.07445796746</v>
       </c>
       <c r="F820" s="9" t="n">
@@ -47421,7 +47421,7 @@
       <c r="D821" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E821" s="8" t="n">
+      <c r="E821" s="9" t="n">
         <v>78391.00806997465</v>
       </c>
       <c r="F821" s="9" t="n">
@@ -47478,7 +47478,7 @@
       <c r="D822" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E822" s="8" t="n">
+      <c r="E822" s="9" t="n">
         <v>78981.15367652402</v>
       </c>
       <c r="F822" s="9" t="n">
@@ -47535,7 +47535,7 @@
       <c r="D823" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E823" s="8" t="n">
+      <c r="E823" s="9" t="n">
         <v>77210.71685687591</v>
       </c>
       <c r="F823" s="9" t="n">
@@ -47592,7 +47592,7 @@
       <c r="D824" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E824" s="8" t="n">
+      <c r="E824" s="9" t="n">
         <v>76718.9288514181</v>
       </c>
       <c r="F824" s="9" t="n">
@@ -47649,7 +47649,7 @@
       <c r="D825" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E825" s="8" t="n">
+      <c r="E825" s="9" t="n">
         <v>72587.90960557251</v>
       </c>
       <c r="F825" s="9" t="n">
@@ -47706,7 +47706,7 @@
       <c r="D826" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E826" s="8" t="n">
+      <c r="E826" s="9" t="n">
         <v>73276.41281321345</v>
       </c>
       <c r="F826" s="9" t="n">
@@ -47763,7 +47763,7 @@
       <c r="D827" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E827" s="8" t="n">
+      <c r="E827" s="9" t="n">
         <v>72489.55200448095</v>
       </c>
       <c r="F827" s="9" t="n">
@@ -47820,7 +47820,7 @@
       <c r="D828" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E828" s="8" t="n">
+      <c r="E828" s="9" t="n">
         <v>70620.75758374127</v>
       </c>
       <c r="F828" s="9" t="n">
@@ -47877,7 +47877,7 @@
       <c r="D829" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E829" s="8" t="n">
+      <c r="E829" s="9" t="n">
         <v>71407.61839247377</v>
       </c>
       <c r="F829" s="9" t="n">
@@ -47934,7 +47934,7 @@
       <c r="D830" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E830" s="8" t="n">
+      <c r="E830" s="9" t="n">
         <v>72489.55200448095</v>
       </c>
       <c r="F830" s="9" t="n">
@@ -47991,7 +47991,7 @@
       <c r="D831" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E831" s="8" t="n">
+      <c r="E831" s="9" t="n">
         <v>72784.62480775564</v>
       </c>
       <c r="F831" s="9" t="n">
@@ -48048,7 +48048,7 @@
       <c r="D832" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E832" s="8" t="n">
+      <c r="E832" s="9" t="n">
         <v>72784.62480775564</v>
       </c>
       <c r="F832" s="9" t="n">
@@ -48105,7 +48105,7 @@
       <c r="D833" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E833" s="8" t="n">
+      <c r="E833" s="9" t="n">
         <v>73768.20081867125</v>
       </c>
       <c r="F833" s="9" t="n">
@@ -48164,7 +48164,7 @@
       <c r="D834" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E834" s="8" t="n">
+      <c r="E834" s="9" t="n">
         <v>73768.20081867125</v>
       </c>
       <c r="F834" s="9" t="n">
@@ -48221,7 +48221,7 @@
       <c r="D835" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E835" s="8" t="n">
+      <c r="E835" s="9" t="n">
         <v>73571.48561648813</v>
       </c>
       <c r="F835" s="9" t="n">
@@ -48278,7 +48278,7 @@
       <c r="D836" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E836" s="8" t="n">
+      <c r="E836" s="9" t="n">
         <v>74259.98882412906</v>
       </c>
       <c r="F836" s="9" t="n">
@@ -48335,7 +48335,7 @@
       <c r="D837" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E837" s="8" t="n">
+      <c r="E837" s="9" t="n">
         <v>75145.20723395312</v>
       </c>
       <c r="F837" s="9" t="n">
@@ -48392,7 +48392,7 @@
       <c r="D838" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E838" s="8" t="n">
+      <c r="E838" s="9" t="n">
         <v>74555.06162740375</v>
       </c>
       <c r="F838" s="9" t="n">
@@ -48449,7 +48449,7 @@
       <c r="D839" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E839" s="8" t="n">
+      <c r="E839" s="9" t="n">
         <v>73276.41281321345</v>
       </c>
       <c r="F839" s="9" t="n">
@@ -48506,7 +48506,7 @@
       <c r="D840" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E840" s="8" t="n">
+      <c r="E840" s="9" t="n">
         <v>71604.3335946569</v>
       </c>
       <c r="F840" s="9" t="n">
@@ -48563,7 +48563,7 @@
       <c r="D841" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E841" s="8" t="n">
+      <c r="E841" s="9" t="n">
         <v>71112.54558919909</v>
       </c>
       <c r="F841" s="9" t="n">
@@ -48620,7 +48620,7 @@
       <c r="D842" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E842" s="8" t="n">
+      <c r="E842" s="9" t="n">
         <v>71112.54558919909</v>
       </c>
       <c r="F842" s="9" t="n">
@@ -48677,7 +48677,7 @@
       <c r="D843" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E843" s="8" t="n">
+      <c r="E843" s="9" t="n">
         <v>71604.3335946569</v>
       </c>
       <c r="F843" s="9" t="n">
@@ -48734,7 +48734,7 @@
       <c r="D844" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E844" s="8" t="n">
+      <c r="E844" s="9" t="n">
         <v>72096.1216001147</v>
       </c>
       <c r="F844" s="9" t="n">
@@ -48791,7 +48791,7 @@
       <c r="D845" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E845" s="8" t="n">
+      <c r="E845" s="9" t="n">
         <v>71604.3335946569</v>
       </c>
       <c r="F845" s="9" t="n">
@@ -48848,7 +48848,7 @@
       <c r="D846" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E846" s="8" t="n">
+      <c r="E846" s="9" t="n">
         <v>72096.1216001147</v>
       </c>
       <c r="F846" s="9" t="n">
@@ -48905,7 +48905,7 @@
       <c r="D847" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E847" s="8" t="n">
+      <c r="E847" s="9" t="n">
         <v>71309.26079138221</v>
       </c>
       <c r="F847" s="9" t="n">
@@ -48962,7 +48962,7 @@
       <c r="D848" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E848" s="8" t="n">
+      <c r="E848" s="9" t="n">
         <v>70817.4727859244</v>
       </c>
       <c r="F848" s="9" t="n">
@@ -49019,7 +49019,7 @@
       <c r="D849" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E849" s="8" t="n">
+      <c r="E849" s="9" t="n">
         <v>70424.04237933426</v>
       </c>
       <c r="F849" s="9" t="n">
@@ -49076,7 +49076,7 @@
       <c r="D850" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E850" s="8" t="n">
+      <c r="E850" s="9" t="n">
         <v>70814.20327894276</v>
       </c>
       <c r="F850" s="9" t="n">
@@ -49133,7 +49133,7 @@
       <c r="D851" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E851" s="8" t="n">
+      <c r="E851" s="9" t="n">
         <v>71009.283728747</v>
       </c>
       <c r="F851" s="9" t="n">
@@ -49190,7 +49190,7 @@
       <c r="D852" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E852" s="8" t="n">
+      <c r="E852" s="9" t="n">
         <v>71887.14575286613</v>
       </c>
       <c r="F852" s="9" t="n">
@@ -49247,7 +49247,7 @@
       <c r="D853" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E853" s="8" t="n">
+      <c r="E853" s="9" t="n">
         <v>71204.36417855126</v>
       </c>
       <c r="F853" s="9" t="n">
@@ -49304,7 +49304,7 @@
       <c r="D854" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E854" s="8" t="n">
+      <c r="E854" s="9" t="n">
         <v>68570.77810619389</v>
       </c>
       <c r="F854" s="9" t="n">
@@ -49361,7 +49361,7 @@
       <c r="D855" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E855" s="8" t="n">
+      <c r="E855" s="9" t="n">
         <v>69156.01945560663</v>
       </c>
       <c r="F855" s="9" t="n">
@@ -49420,7 +49420,7 @@
       <c r="D856" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E856" s="8" t="n">
+      <c r="E856" s="9" t="n">
         <v>69351.09990541088</v>
       </c>
       <c r="F856" s="9" t="n">
@@ -49477,7 +49477,7 @@
       <c r="D857" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E857" s="8" t="n">
+      <c r="E857" s="9" t="n">
         <v>69643.72058011725</v>
       </c>
       <c r="F857" s="9" t="n">
@@ -49534,7 +49534,7 @@
       <c r="D858" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E858" s="8" t="n">
+      <c r="E858" s="9" t="n">
         <v>70228.96192953001</v>
       </c>
       <c r="F858" s="9" t="n">
@@ -49591,7 +49591,7 @@
       <c r="D859" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E859" s="8" t="n">
+      <c r="E859" s="9" t="n">
         <v>69448.64013031301</v>
       </c>
       <c r="F859" s="9" t="n">
@@ -49648,7 +49648,7 @@
       <c r="D860" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E860" s="8" t="n">
+      <c r="E860" s="9" t="n">
         <v>69741.26080501938</v>
       </c>
       <c r="F860" s="9" t="n">
@@ -49705,7 +49705,7 @@
       <c r="D861" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E861" s="8" t="n">
+      <c r="E861" s="9" t="n">
         <v>70424.04237933426</v>
       </c>
       <c r="F861" s="9" t="n">
@@ -49762,7 +49762,7 @@
       <c r="D862" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E862" s="8" t="n">
+      <c r="E862" s="9" t="n">
         <v>70326.50215443214</v>
       </c>
       <c r="F862" s="9" t="n">
@@ -49819,7 +49819,7 @@
       <c r="D863" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E863" s="8" t="n">
+      <c r="E863" s="9" t="n">
         <v>70716.66305404063</v>
       </c>
       <c r="F863" s="9" t="n">
@@ -49876,7 +49876,7 @@
       <c r="D864" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E864" s="8" t="n">
+      <c r="E864" s="9" t="n">
         <v>71692.06530306189</v>
       </c>
       <c r="F864" s="9" t="n">
@@ -49933,7 +49933,7 @@
       <c r="D865" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E865" s="8" t="n">
+      <c r="E865" s="9" t="n">
         <v>72765.00777698527</v>
       </c>
       <c r="F865" s="9" t="n">
@@ -49990,7 +49990,7 @@
       <c r="D866" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E866" s="8" t="n">
+      <c r="E866" s="9" t="n">
         <v>72667.46755208314</v>
       </c>
       <c r="F866" s="9" t="n">
@@ -50047,7 +50047,7 @@
       <c r="D867" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E867" s="8" t="n">
+      <c r="E867" s="9" t="n">
         <v>73350.249126398</v>
       </c>
       <c r="F867" s="9" t="n">
@@ -50104,7 +50104,7 @@
       <c r="D868" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E868" s="8" t="n">
+      <c r="E868" s="9" t="n">
         <v>73155.16867659376</v>
       </c>
       <c r="F868" s="9" t="n">
@@ -50161,7 +50161,7 @@
       <c r="D869" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E869" s="8" t="n">
+      <c r="E869" s="9" t="n">
         <v>73155.16867659376</v>
       </c>
       <c r="F869" s="9" t="n">
@@ -50218,7 +50218,7 @@
       <c r="D870" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E870" s="8" t="n">
+      <c r="E870" s="9" t="n">
         <v>73350.249126398</v>
       </c>
       <c r="F870" s="9" t="n">
@@ -50275,7 +50275,7 @@
       <c r="D871" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E871" s="8" t="n">
+      <c r="E871" s="9" t="n">
         <v>73740.4100260065</v>
       </c>
       <c r="F871" s="9" t="n">
@@ -50332,7 +50332,7 @@
       <c r="D872" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E872" s="8" t="n">
+      <c r="E872" s="9" t="n">
         <v>74033.03070071289</v>
       </c>
       <c r="F872" s="9" t="n">
@@ -50389,7 +50389,7 @@
       <c r="D873" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E873" s="8" t="n">
+      <c r="E873" s="9" t="n">
         <v>74325.65137541926</v>
       </c>
       <c r="F873" s="9" t="n">
@@ -50446,7 +50446,7 @@
       <c r="D874" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E874" s="8" t="n">
+      <c r="E874" s="9" t="n">
         <v>74228.11115051713</v>
       </c>
       <c r="F874" s="9" t="n">
@@ -50503,7 +50503,7 @@
       <c r="D875" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E875" s="8" t="n">
+      <c r="E875" s="9" t="n">
         <v>75105.97317463625</v>
       </c>
       <c r="F875" s="9" t="n">
@@ -50562,7 +50562,7 @@
       <c r="D876" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E876" s="8" t="n">
+      <c r="E876" s="9" t="n">
         <v>73837.95025090863</v>
       </c>
       <c r="F876" s="9" t="n">
@@ -50619,7 +50619,7 @@
       <c r="D877" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E877" s="8" t="n">
+      <c r="E877" s="9" t="n">
         <v>73740.4100260065</v>
       </c>
       <c r="F877" s="9" t="n">
@@ -50676,7 +50676,7 @@
       <c r="D878" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E878" s="8" t="n">
+      <c r="E878" s="9" t="n">
         <v>73642.86980110439</v>
       </c>
       <c r="F878" s="9" t="n">
@@ -50733,7 +50733,7 @@
       <c r="D879" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E879" s="8" t="n">
+      <c r="E879" s="9" t="n">
         <v>74618.27205012564</v>
       </c>
       <c r="F879" s="9" t="n">
@@ -50790,7 +50790,7 @@
       <c r="D880" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E880" s="8" t="n">
+      <c r="E880" s="9" t="n">
         <v>75105.97317463625</v>
       </c>
       <c r="F880" s="9" t="n">
@@ -50847,7 +50847,7 @@
       <c r="D881" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E881" s="8" t="n">
+      <c r="E881" s="9" t="n">
         <v>75398.59384934264</v>
       </c>
       <c r="F881" s="9" t="n">
@@ -50904,7 +50904,7 @@
       <c r="D882" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E882" s="8" t="n">
+      <c r="E882" s="9" t="n">
         <v>76081.3754236575</v>
       </c>
       <c r="F882" s="9" t="n">
@@ -50961,7 +50961,7 @@
       <c r="D883" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E883" s="8" t="n">
+      <c r="E883" s="9" t="n">
         <v>76276.45587346176</v>
       </c>
       <c r="F883" s="9" t="n">
@@ -51018,7 +51018,7 @@
       <c r="D884" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E884" s="8" t="n">
+      <c r="E884" s="9" t="n">
         <v>76178.91564855963</v>
       </c>
       <c r="F884" s="9" t="n">
@@ -51075,7 +51075,7 @@
       <c r="D885" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E885" s="8" t="n">
+      <c r="E885" s="9" t="n">
         <v>75691.21452404901</v>
       </c>
       <c r="F885" s="9" t="n">
@@ -51132,7 +51132,7 @@
       <c r="D886" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E886" s="8" t="n">
+      <c r="E886" s="9" t="n">
         <v>75105.97317463625</v>
       </c>
       <c r="F886" s="9" t="n">
@@ -51189,7 +51189,7 @@
       <c r="D887" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E887" s="8" t="n">
+      <c r="E887" s="9" t="n">
         <v>75983.83519875539</v>
       </c>
       <c r="F887" s="9" t="n">
@@ -51246,7 +51246,7 @@
       <c r="D888" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E888" s="8" t="n">
+      <c r="E888" s="9" t="n">
         <v>76666.61677307026</v>
       </c>
       <c r="F888" s="9" t="n">
@@ -51303,7 +51303,7 @@
       <c r="D889" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E889" s="8" t="n">
+      <c r="E889" s="9" t="n">
         <v>75301.05362444051</v>
       </c>
       <c r="F889" s="9" t="n">
@@ -51360,7 +51360,7 @@
       <c r="D890" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E890" s="8" t="n">
+      <c r="E890" s="9" t="n">
         <v>74618.27205012564</v>
       </c>
       <c r="F890" s="9" t="n">
@@ -51417,7 +51417,7 @@
       <c r="D891" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E891" s="8" t="n">
+      <c r="E891" s="9" t="n">
         <v>74910.89272483201</v>
       </c>
       <c r="F891" s="9" t="n">
@@ -51474,7 +51474,7 @@
       <c r="D892" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E892" s="8" t="n">
+      <c r="E892" s="9" t="n">
         <v>75398.59384934264</v>
       </c>
       <c r="F892" s="9" t="n">
@@ -51531,7 +51531,7 @@
       <c r="D893" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E893" s="8" t="n">
+      <c r="E893" s="9" t="n">
         <v>74715.81227502775</v>
       </c>
       <c r="F893" s="9" t="n">
@@ -51588,7 +51588,7 @@
       <c r="D894" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E894" s="8" t="n">
+      <c r="E894" s="9" t="n">
         <v>74910.89272483201</v>
       </c>
       <c r="F894" s="9" t="n">
@@ -51645,7 +51645,7 @@
       <c r="D895" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E895" s="8" t="n">
+      <c r="E895" s="9" t="n">
         <v>75788.75474895113</v>
       </c>
       <c r="F895" s="9" t="n">
@@ -51704,7 +51704,7 @@
       <c r="D896" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E896" s="8" t="n">
+      <c r="E896" s="9" t="n">
         <v>75788.75474895113</v>
       </c>
       <c r="F896" s="9" t="n">
@@ -51761,7 +51761,7 @@
       <c r="D897" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E897" s="8" t="n">
+      <c r="E897" s="9" t="n">
         <v>75105.97317463625</v>
       </c>
       <c r="F897" s="9" t="n">
@@ -51818,7 +51818,7 @@
       <c r="D898" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E898" s="8" t="n">
+      <c r="E898" s="9" t="n">
         <v>75886.29497385326</v>
       </c>
       <c r="F898" s="9" t="n">
@@ -51875,7 +51875,7 @@
       <c r="D899" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E899" s="8" t="n">
+      <c r="E899" s="9" t="n">
         <v>76276.45587346176</v>
       </c>
       <c r="F899" s="9" t="n">
@@ -51932,7 +51932,7 @@
       <c r="D900" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E900" s="8" t="n">
+      <c r="E900" s="9" t="n">
         <v>77056.77767267876</v>
       </c>
       <c r="F900" s="9" t="n">
@@ -51989,7 +51989,7 @@
       <c r="D901" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E901" s="8" t="n">
+      <c r="E901" s="9" t="n">
         <v>76569.07654816813</v>
       </c>
       <c r="F901" s="9" t="n">
@@ -52046,7 +52046,7 @@
       <c r="D902" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E902" s="8" t="n">
+      <c r="E902" s="9" t="n">
         <v>76959.23744777663</v>
       </c>
       <c r="F902" s="9" t="n">
@@ -52103,7 +52103,7 @@
       <c r="D903" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E903" s="8" t="n">
+      <c r="E903" s="9" t="n">
         <v>77056.77767267876</v>
       </c>
       <c r="F903" s="9" t="n">
@@ -52160,7 +52160,7 @@
       <c r="D904" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E904" s="8" t="n">
+      <c r="E904" s="9" t="n">
         <v>78032.17992170001</v>
       </c>
       <c r="F904" s="9" t="n">
@@ -52217,7 +52217,7 @@
       <c r="D905" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E905" s="8" t="n">
+      <c r="E905" s="9" t="n">
         <v>77056.77767267876</v>
       </c>
       <c r="F905" s="9" t="n">
@@ -52274,7 +52274,7 @@
       <c r="D906" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E906" s="8" t="n">
+      <c r="E906" s="9" t="n">
         <v>78519.88104621063</v>
       </c>
       <c r="F906" s="9" t="n">
@@ -52331,7 +52331,7 @@
       <c r="D907" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E907" s="8" t="n">
+      <c r="E907" s="9" t="n">
         <v>78812.501720917</v>
       </c>
       <c r="F907" s="9" t="n">
@@ -52388,7 +52388,7 @@
       <c r="D908" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E908" s="8" t="n">
+      <c r="E908" s="9" t="n">
         <v>78714.96149601489</v>
       </c>
       <c r="F908" s="9" t="n">
@@ -52445,7 +52445,7 @@
       <c r="D909" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E909" s="8" t="n">
+      <c r="E909" s="9" t="n">
         <v>78227.26037150426</v>
       </c>
       <c r="F909" s="9" t="n">
@@ -52502,7 +52502,7 @@
       <c r="D910" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E910" s="8" t="n">
+      <c r="E910" s="9" t="n">
         <v>77056.77767267876</v>
       </c>
       <c r="F910" s="9" t="n">
@@ -52559,7 +52559,7 @@
       <c r="D911" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E911" s="8" t="n">
+      <c r="E911" s="9" t="n">
         <v>77934.63969679788</v>
       </c>
       <c r="F911" s="9" t="n">
@@ -52616,7 +52616,7 @@
       <c r="D912" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E912" s="8" t="n">
+      <c r="E912" s="9" t="n">
         <v>78032.17992170001</v>
       </c>
       <c r="F912" s="9" t="n">
@@ -52673,7 +52673,7 @@
       <c r="D913" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E913" s="8" t="n">
+      <c r="E913" s="9" t="n">
         <v>77349.39834738514</v>
       </c>
       <c r="F913" s="9" t="n">
@@ -52730,7 +52730,7 @@
       <c r="D914" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E914" s="8" t="n">
+      <c r="E914" s="9" t="n">
         <v>76569.07654816813</v>
       </c>
       <c r="F914" s="9" t="n">
@@ -52787,7 +52787,7 @@
       <c r="D915" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E915" s="8" t="n">
+      <c r="E915" s="9" t="n">
         <v>77446.93857228725</v>
       </c>
       <c r="F915" s="9" t="n">
@@ -52844,7 +52844,7 @@
       <c r="D916" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E916" s="8" t="n">
+      <c r="E916" s="9" t="n">
         <v>78324.80059640638</v>
       </c>
       <c r="F916" s="9" t="n">
@@ -52901,7 +52901,7 @@
       <c r="D917" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E917" s="8" t="n">
+      <c r="E917" s="9" t="n">
         <v>75691.21452404901</v>
       </c>
       <c r="F917" s="9" t="n">
@@ -52958,7 +52958,7 @@
       <c r="D918" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E918" s="8" t="n">
+      <c r="E918" s="9" t="n">
         <v>75008.43294973414</v>
       </c>
       <c r="F918" s="9" t="n">
@@ -53017,7 +53017,7 @@
       <c r="D919" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E919" s="8" t="n">
+      <c r="E919" s="9" t="n">
         <v>74228.11115051713</v>
       </c>
       <c r="F919" s="9" t="n">
@@ -53074,7 +53074,7 @@
       <c r="D920" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E920" s="8" t="n">
+      <c r="E920" s="9" t="n">
         <v>79007.58217072126</v>
       </c>
       <c r="F920" s="9" t="n">
@@ -53131,7 +53131,7 @@
       <c r="D921" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E921" s="8" t="n">
+      <c r="E921" s="9" t="n">
         <v>80080.52464464464</v>
       </c>
       <c r="F921" s="9" t="n">
@@ -53188,7 +53188,7 @@
       <c r="D922" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E922" s="8" t="n">
+      <c r="E922" s="9" t="n">
         <v>80958.38666876376</v>
       </c>
       <c r="F922" s="9" t="n">
@@ -53245,7 +53245,7 @@
       <c r="D923" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E923" s="8" t="n">
+      <c r="E923" s="9" t="n">
         <v>82421.49004229564</v>
       </c>
       <c r="F923" s="9" t="n">
@@ -53302,7 +53302,7 @@
       <c r="D924" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E924" s="8" t="n">
+      <c r="E924" s="9" t="n">
         <v>82421.49004229564</v>
       </c>
       <c r="F924" s="9" t="n">
@@ -53359,7 +53359,7 @@
       <c r="D925" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E925" s="8" t="n">
+      <c r="E925" s="9" t="n">
         <v>80958.38666876376</v>
       </c>
       <c r="F925" s="9" t="n">
@@ -53416,7 +53416,7 @@
       <c r="D926" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E926" s="8" t="n">
+      <c r="E926" s="9" t="n">
         <v>80568.22576915527</v>
       </c>
       <c r="F926" s="9" t="n">
@@ -53473,7 +53473,7 @@
       <c r="D927" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E927" s="8" t="n">
+      <c r="E927" s="9" t="n">
         <v>79982.98441974251</v>
       </c>
       <c r="F927" s="9" t="n">
@@ -53530,7 +53530,7 @@
       <c r="D928" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E928" s="8" t="n">
+      <c r="E928" s="9" t="n">
         <v>80080.52464464464</v>
       </c>
       <c r="F928" s="9" t="n">
@@ -53587,7 +53587,7 @@
       <c r="D929" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E929" s="8" t="n">
+      <c r="E929" s="9" t="n">
         <v>81446.08779327439</v>
       </c>
       <c r="F929" s="9" t="n">
@@ -53644,7 +53644,7 @@
       <c r="D930" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E930" s="8" t="n">
+      <c r="E930" s="9" t="n">
         <v>81251.00734347013</v>
       </c>
       <c r="F930" s="9" t="n">
@@ -53701,7 +53701,7 @@
       <c r="D931" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E931" s="8" t="n">
+      <c r="E931" s="9" t="n">
         <v>80860.84644386164</v>
       </c>
       <c r="F931" s="9" t="n">
@@ -53758,7 +53758,7 @@
       <c r="D932" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E932" s="8" t="n">
+      <c r="E932" s="9" t="n">
         <v>80860.84644386164</v>
       </c>
       <c r="F932" s="9" t="n">
@@ -53815,7 +53815,7 @@
       <c r="D933" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E933" s="8" t="n">
+      <c r="E933" s="9" t="n">
         <v>81055.92689366588</v>
       </c>
       <c r="F933" s="9" t="n">
@@ -53872,7 +53872,7 @@
       <c r="D934" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E934" s="8" t="n">
+      <c r="E934" s="9" t="n">
         <v>81738.70846798076</v>
       </c>
       <c r="F934" s="9" t="n">
@@ -53929,7 +53929,7 @@
       <c r="D935" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E935" s="8" t="n">
+      <c r="E935" s="9" t="n">
         <v>80080.52464464464</v>
       </c>
       <c r="F935" s="9" t="n">
@@ -53986,7 +53986,7 @@
       <c r="D936" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E936" s="8" t="n">
+      <c r="E936" s="9" t="n">
         <v>83396.89229131688</v>
       </c>
       <c r="F936" s="9" t="n">
@@ -54043,7 +54043,7 @@
       <c r="D937" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E937" s="8" t="n">
+      <c r="E937" s="9" t="n">
         <v>84567.37499014239</v>
       </c>
       <c r="F937" s="9" t="n">
@@ -54100,7 +54100,7 @@
       <c r="D938" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E938" s="8" t="n">
+      <c r="E938" s="9" t="n">
         <v>87981.28286171675</v>
       </c>
       <c r="F938" s="9" t="n">
@@ -54159,7 +54159,7 @@
       <c r="D939" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E939" s="8" t="n">
+      <c r="E939" s="9" t="n">
         <v>89932.08735975926</v>
       </c>
       <c r="F939" s="9" t="n">
@@ -54216,7 +54216,7 @@
       <c r="D940" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E940" s="8" t="n">
+      <c r="E940" s="9" t="n">
         <v>91687.81140799751</v>
       </c>
       <c r="F940" s="9" t="n">
@@ -54273,7 +54273,7 @@
       <c r="D941" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E941" s="8" t="n">
+      <c r="E941" s="9" t="n">
         <v>86713.25993798913</v>
       </c>
       <c r="F941" s="9" t="n">
@@ -54330,7 +54330,7 @@
       <c r="D942" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E942" s="8" t="n">
+      <c r="E942" s="9" t="n">
         <v>86323.09903838063</v>
       </c>
       <c r="F942" s="9" t="n">
@@ -54387,7 +54387,7 @@
       <c r="D943" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E943" s="8" t="n">
+      <c r="E943" s="9" t="n">
         <v>85835.39791387001</v>
       </c>
       <c r="F943" s="9" t="n">
@@ -54444,7 +54444,7 @@
       <c r="D944" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E944" s="8" t="n">
+      <c r="E944" s="9" t="n">
         <v>85347.69678935938</v>
       </c>
       <c r="F944" s="9" t="n">
@@ -54501,7 +54501,7 @@
       <c r="D945" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E945" s="8" t="n">
+      <c r="E945" s="9" t="n">
         <v>84177.21409053389</v>
       </c>
       <c r="F945" s="9" t="n">
@@ -54558,7 +54558,7 @@
       <c r="D946" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E946" s="8" t="n">
+      <c r="E946" s="9" t="n">
         <v>83884.5934158275</v>
       </c>
       <c r="F946" s="9" t="n">
@@ -54615,7 +54615,7 @@
       <c r="D947" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E947" s="8" t="n">
+      <c r="E947" s="9" t="n">
         <v>84664.91521504452</v>
       </c>
       <c r="F947" s="9" t="n">
@@ -54672,7 +54672,7 @@
       <c r="D948" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E948" s="8" t="n">
+      <c r="E948" s="9" t="n">
         <v>85835.39791387001</v>
       </c>
       <c r="F948" s="9" t="n">
@@ -54729,7 +54729,7 @@
       <c r="D949" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E949" s="8" t="n">
+      <c r="E949" s="9" t="n">
         <v>86030.47836367426</v>
       </c>
       <c r="F949" s="9" t="n">
@@ -54786,7 +54786,7 @@
       <c r="D950" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E950" s="8" t="n">
+      <c r="E950" s="9" t="n">
         <v>86030.47836367426</v>
       </c>
       <c r="F950" s="9" t="n">
@@ -54843,7 +54843,7 @@
       <c r="D951" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E951" s="8" t="n">
+      <c r="E951" s="9" t="n">
         <v>86713.25993415243</v>
       </c>
       <c r="F951" s="9" t="n">
@@ -54900,7 +54900,7 @@
       <c r="D952" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E952" s="8" t="n">
+      <c r="E952" s="9" t="n">
         <v>86228.82831440856</v>
       </c>
       <c r="F952" s="9" t="n">
@@ -54957,7 +54957,7 @@
       <c r="D953" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E953" s="8" t="n">
+      <c r="E953" s="9" t="n">
         <v>86713.25993415243</v>
       </c>
       <c r="F953" s="9" t="n">
@@ -55014,7 +55014,7 @@
       <c r="D954" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E954" s="8" t="n">
+      <c r="E954" s="9" t="n">
         <v>87100.80522994752</v>
       </c>
       <c r="F954" s="9" t="n">
@@ -55082,7 +55082,7 @@
       <c r="D955" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E955" s="8" t="n">
+      <c r="E955" s="9" t="n">
         <v>83322.23859594535</v>
       </c>
       <c r="F955" s="9" t="n">
@@ -55139,7 +55139,7 @@
       <c r="D956" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E956" s="8" t="n">
+      <c r="E956" s="9" t="n">
         <v>79931.21725973656</v>
       </c>
       <c r="F956" s="9" t="n">
@@ -55196,7 +55196,7 @@
       <c r="D957" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E957" s="8" t="n">
+      <c r="E957" s="9" t="n">
         <v>78477.92240046861</v>
       </c>
       <c r="F957" s="9" t="n">
@@ -55253,7 +55253,7 @@
       <c r="D958" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E958" s="8" t="n">
+      <c r="E958" s="9" t="n">
         <v>78477.92240046861</v>
       </c>
       <c r="F958" s="9" t="n">
@@ -55310,7 +55310,7 @@
       <c r="D959" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E959" s="8" t="n">
+      <c r="E959" s="9" t="n">
         <v>78913.910858249</v>
       </c>
       <c r="F959" s="9" t="n">
@@ -55367,7 +55367,7 @@
       <c r="D960" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E960" s="8" t="n">
+      <c r="E960" s="9" t="n">
         <v>79204.56983010258</v>
       </c>
       <c r="F960" s="9" t="n">
@@ -55424,7 +55424,7 @@
       <c r="D961" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E961" s="8" t="n">
+      <c r="E961" s="9" t="n">
         <v>79640.55828788297</v>
       </c>
       <c r="F961" s="9" t="n">
@@ -55481,7 +55481,7 @@
       <c r="D962" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E962" s="8" t="n">
+      <c r="E962" s="9" t="n">
         <v>80294.54097455354</v>
       </c>
       <c r="F962" s="9" t="n">
@@ -55538,7 +55538,7 @@
       <c r="D963" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E963" s="8" t="n">
+      <c r="E963" s="9" t="n">
         <v>81384.51211900449</v>
       </c>
       <c r="F963" s="9" t="n">
@@ -55595,7 +55595,7 @@
       <c r="D964" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E964" s="8" t="n">
+      <c r="E964" s="9" t="n">
         <v>82038.49480567506</v>
       </c>
       <c r="F964" s="9" t="n">
@@ -55652,7 +55652,7 @@
       <c r="D965" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E965" s="8" t="n">
+      <c r="E965" s="9" t="n">
         <v>82111.15954863846</v>
       </c>
       <c r="F965" s="9" t="n">
@@ -55709,7 +55709,7 @@
       <c r="D966" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E966" s="8" t="n">
+      <c r="E966" s="9" t="n">
         <v>82111.15954863846</v>
       </c>
       <c r="F966" s="9" t="n">
@@ -55766,7 +55766,7 @@
       <c r="D967" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E967" s="8" t="n">
+      <c r="E967" s="9" t="n">
         <v>81747.83583382147</v>
       </c>
       <c r="F967" s="9" t="n">
@@ -55823,7 +55823,7 @@
       <c r="D968" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E968" s="8" t="n">
+      <c r="E968" s="9" t="n">
         <v>81239.1826330777</v>
       </c>
       <c r="F968" s="9" t="n">
@@ -55880,7 +55880,7 @@
       <c r="D969" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E969" s="8" t="n">
+      <c r="E969" s="9" t="n">
         <v>81311.8473760411</v>
       </c>
       <c r="F969" s="9" t="n">
@@ -55937,7 +55937,7 @@
       <c r="D970" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E970" s="8" t="n">
+      <c r="E970" s="9" t="n">
         <v>80657.86468937053</v>
       </c>
       <c r="F970" s="9" t="n">
@@ -55994,7 +55994,7 @@
       <c r="D971" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E971" s="8" t="n">
+      <c r="E971" s="9" t="n">
         <v>78986.57560121239</v>
       </c>
       <c r="F971" s="9" t="n">
@@ -56051,7 +56051,7 @@
       <c r="D972" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E972" s="8" t="n">
+      <c r="E972" s="9" t="n">
         <v>80730.52943233392</v>
       </c>
       <c r="F972" s="9" t="n">
@@ -56108,7 +56108,7 @@
       <c r="D973" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E973" s="8" t="n">
+      <c r="E973" s="9" t="n">
         <v>83491.789664943</v>
       </c>
       <c r="F973" s="9" t="n">
@@ -56165,7 +56165,7 @@
       <c r="D974" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E974" s="8" t="n">
+      <c r="E974" s="9" t="n">
         <v>83564.45440790639</v>
       </c>
       <c r="F974" s="9" t="n">
@@ -56222,7 +56222,7 @@
       <c r="D975" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E975" s="8" t="n">
+      <c r="E975" s="9" t="n">
         <v>81384.51211900449</v>
       </c>
       <c r="F975" s="9" t="n">
@@ -56279,7 +56279,7 @@
       <c r="D976" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E976" s="8" t="n">
+      <c r="E976" s="9" t="n">
         <v>82474.48326345545</v>
       </c>
       <c r="F976" s="9" t="n">
@@ -56338,7 +56338,7 @@
       <c r="D977" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E977" s="8" t="n">
+      <c r="E977" s="9" t="n">
         <v>81965.83006271167</v>
       </c>
       <c r="F977" s="9" t="n">
@@ -56395,7 +56395,7 @@
       <c r="D978" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E978" s="8" t="n">
+      <c r="E978" s="9" t="n">
         <v>79204.56983010258</v>
       </c>
       <c r="F978" s="9" t="n">
@@ -56452,7 +56452,7 @@
       <c r="D979" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E979" s="8" t="n">
+      <c r="E979" s="9" t="n">
         <v>77169.95702712747</v>
       </c>
       <c r="F979" s="9" t="n">
@@ -56509,7 +56509,7 @@
       <c r="D980" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E980" s="8" t="n">
+      <c r="E980" s="9" t="n">
         <v>77024.62754120068</v>
       </c>
       <c r="F980" s="9" t="n">
@@ -56566,7 +56566,7 @@
       <c r="D981" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E981" s="8" t="n">
+      <c r="E981" s="9" t="n">
         <v>76806.63331231049</v>
       </c>
       <c r="F981" s="9" t="n">
@@ -56623,7 +56623,7 @@
       <c r="D982" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E982" s="8" t="n">
+      <c r="E982" s="9" t="n">
         <v>74844.68525229878</v>
       </c>
       <c r="F982" s="9" t="n">
@@ -56680,7 +56680,7 @@
       <c r="D983" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E983" s="8" t="n">
+      <c r="E983" s="9" t="n">
         <v>74190.70256562821</v>
       </c>
       <c r="F983" s="9" t="n">
@@ -56737,7 +56737,7 @@
       <c r="D984" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E984" s="8" t="n">
+      <c r="E984" s="9" t="n">
         <v>72737.40770636026</v>
       </c>
       <c r="F984" s="9" t="n">
@@ -56794,7 +56794,7 @@
       <c r="D985" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E985" s="8" t="n">
+      <c r="E985" s="9" t="n">
         <v>72664.74296339687</v>
       </c>
       <c r="F985" s="9" t="n">
@@ -56851,7 +56851,7 @@
       <c r="D986" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E986" s="8" t="n">
+      <c r="E986" s="9" t="n">
         <v>70484.80067449497</v>
       </c>
       <c r="F986" s="9" t="n">
@@ -56908,7 +56908,7 @@
       <c r="D987" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E987" s="8" t="n">
+      <c r="E987" s="9" t="n">
         <v>68377.52312855645</v>
       </c>
       <c r="F987" s="9" t="n">
@@ -56965,7 +56965,7 @@
       <c r="D988" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E988" s="8" t="n">
+      <c r="E988" s="9" t="n">
         <v>70194.14170264137</v>
       </c>
       <c r="F988" s="9" t="n">
@@ -57022,7 +57022,7 @@
       <c r="D989" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E989" s="8" t="n">
+      <c r="E989" s="9" t="n">
         <v>70630.13016042176</v>
       </c>
       <c r="F989" s="9" t="n">
@@ -57079,7 +57079,7 @@
       <c r="D990" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E990" s="8" t="n">
+      <c r="E990" s="9" t="n">
         <v>70484.80067449497</v>
       </c>
       <c r="F990" s="9" t="n">
@@ -57136,7 +57136,7 @@
       <c r="D991" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E991" s="8" t="n">
+      <c r="E991" s="9" t="n">
         <v>70702.79490338515</v>
       </c>
       <c r="F991" s="9" t="n">
@@ -57193,7 +57193,7 @@
       <c r="D992" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E992" s="8" t="n">
+      <c r="E992" s="9" t="n">
         <v>70412.13593153156</v>
       </c>
       <c r="F992" s="9" t="n">
@@ -57250,7 +57250,7 @@
       <c r="D993" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E993" s="8" t="n">
+      <c r="E993" s="9" t="n">
         <v>69394.82953004401</v>
       </c>
       <c r="F993" s="9" t="n">
@@ -57307,7 +57307,7 @@
       <c r="D994" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E994" s="8" t="n">
+      <c r="E994" s="9" t="n">
         <v>68958.84107226363</v>
       </c>
       <c r="F994" s="9" t="n">
@@ -57364,7 +57364,7 @@
       <c r="D995" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E995" s="8" t="n">
+      <c r="E995" s="9" t="n">
         <v>74118.0378226648</v>
       </c>
       <c r="F995" s="9" t="n">
@@ -57421,7 +57421,7 @@
       <c r="D996" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E996" s="8" t="n">
+      <c r="E996" s="9" t="n">
         <v>73464.05513599423</v>
       </c>
       <c r="F996" s="9" t="n">
@@ -57478,7 +57478,7 @@
       <c r="D997" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E997" s="8" t="n">
+      <c r="E997" s="9" t="n">
         <v>73827.37885081122</v>
       </c>
       <c r="F997" s="9" t="n">
@@ -57535,7 +57535,7 @@
       <c r="D998" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E998" s="8" t="n">
+      <c r="E998" s="9" t="n">
         <v>75062.67948118897</v>
       </c>
       <c r="F998" s="9" t="n">
@@ -57594,7 +57594,7 @@
       <c r="D999" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E999" s="8" t="n">
+      <c r="E999" s="9" t="n">
         <v>75353.33845304255</v>
       </c>
       <c r="F999" s="9" t="n">
@@ -57651,7 +57651,7 @@
       <c r="D1000" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E1000" s="8" t="n">
+      <c r="E1000" s="9" t="n">
         <v>74699.35576394931</v>
       </c>
       <c r="F1000" s="9" t="n">
@@ -57708,7 +57708,7 @@
       <c r="D1001" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E1001" s="8" t="n">
+      <c r="E1001" s="9" t="n">
         <v>74555.14851343975</v>
       </c>
       <c r="F1001" s="9" t="n">
@@ -57765,7 +57765,7 @@
       <c r="D1002" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E1002" s="8" t="n">
+      <c r="E1002" s="9" t="n">
         <v>73257.28325885377</v>
       </c>
       <c r="F1002" s="9" t="n">
@@ -57822,7 +57822,7 @@
       <c r="D1003" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E1003" s="8" t="n">
+      <c r="E1003" s="9" t="n">
         <v>73185.17963359899</v>
       </c>
       <c r="F1003" s="9" t="n">
@@ -57879,7 +57879,7 @@
       <c r="D1004" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E1004" s="8" t="n">
+      <c r="E1004" s="9" t="n">
         <v>75492.49564175186</v>
       </c>
       <c r="F1004" s="9" t="n">
@@ -57936,7 +57936,7 @@
       <c r="D1005" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E1005" s="8" t="n">
+      <c r="E1005" s="9" t="n">
         <v>77583.5007741404</v>
       </c>
       <c r="F1005" s="9" t="n">
@@ -57993,7 +57993,7 @@
       <c r="D1006" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E1006" s="8" t="n">
+      <c r="E1006" s="9" t="n">
         <v>77511.39714888563</v>
       </c>
       <c r="F1006" s="9" t="n">
@@ -58050,7 +58050,7 @@
       <c r="D1007" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E1007" s="8" t="n">
+      <c r="E1007" s="9" t="n">
         <v>76429.84277006397</v>
       </c>
       <c r="F1007" s="9" t="n">
@@ -58107,7 +58107,7 @@
       <c r="D1008" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E1008" s="8" t="n">
+      <c r="E1008" s="9" t="n">
         <v>75708.80651751619</v>
       </c>
       <c r="F1008" s="9" t="n">
@@ -58164,7 +58164,7 @@
       <c r="D1009" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E1009" s="8" t="n">
+      <c r="E1009" s="9" t="n">
         <v>75780.91014277097</v>
       </c>
       <c r="F1009" s="9" t="n">
@@ -58221,7 +58221,7 @@
       <c r="D1010" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E1010" s="8" t="n">
+      <c r="E1010" s="9" t="n">
         <v>75348.28839124231</v>
       </c>
       <c r="F1010" s="9" t="n">
@@ -58278,7 +58278,7 @@
       <c r="D1011" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E1011" s="8" t="n">
+      <c r="E1011" s="9" t="n">
         <v>75708.80651751619</v>
       </c>
       <c r="F1011" s="9" t="n">
@@ -58335,7 +58335,7 @@
       <c r="D1012" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E1012" s="8" t="n">
+      <c r="E1012" s="9" t="n">
         <v>75420.39201649708</v>
       </c>
       <c r="F1012" s="9" t="n">
@@ -58392,7 +58392,7 @@
       <c r="D1013" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E1013" s="8" t="n">
+      <c r="E1013" s="9" t="n">
         <v>75708.80651751619</v>
       </c>
       <c r="F1013" s="9" t="n">
@@ -58449,7 +58449,7 @@
       <c r="D1014" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E1014" s="8" t="n">
+      <c r="E1014" s="9" t="n">
         <v>74266.73401242065</v>
       </c>
       <c r="F1014" s="9" t="n">
@@ -58506,7 +58506,7 @@
       <c r="D1015" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E1015" s="8" t="n">
+      <c r="E1015" s="9" t="n">
         <v>74122.5267619111</v>
       </c>
       <c r="F1015" s="9" t="n">
@@ -58563,7 +58563,7 @@
       <c r="D1016" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E1016" s="8" t="n">
+      <c r="E1016" s="9" t="n">
         <v>73834.11226089198</v>
       </c>
       <c r="F1016" s="9" t="n">
@@ -58620,7 +58620,7 @@
       <c r="D1017" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E1017" s="8" t="n">
+      <c r="E1017" s="9" t="n">
         <v>71022.07087595567</v>
       </c>
       <c r="F1017" s="9" t="n">
@@ -58677,7 +58677,7 @@
       <c r="D1018" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E1018" s="8" t="n">
+      <c r="E1018" s="9" t="n">
         <v>71815.21075375822</v>
       </c>
       <c r="F1018" s="9" t="n">
@@ -58734,7 +58734,7 @@
       <c r="D1019" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E1019" s="8" t="n">
+      <c r="E1019" s="9" t="n">
         <v>77150.87902261174</v>
       </c>
       <c r="F1019" s="9" t="n">
@@ -58793,7 +58793,7 @@
       <c r="D1020" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E1020" s="8" t="n">
+      <c r="E1020" s="9" t="n">
         <v>80035.02403280283</v>
       </c>
       <c r="F1020" s="9" t="n">
@@ -58850,7 +58850,7 @@
       <c r="D1021" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E1021" s="8" t="n">
+      <c r="E1021" s="9" t="n">
         <v>80035.02403280283</v>
       </c>
       <c r="F1021" s="9" t="n">
@@ -58907,7 +58907,7 @@
       <c r="D1022" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E1022" s="8" t="n">
+      <c r="E1022" s="9" t="n">
         <v>80107.12765805761</v>
       </c>
       <c r="F1022" s="9" t="n">
@@ -58964,7 +58964,7 @@
       <c r="D1023" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E1023" s="8" t="n">
+      <c r="E1023" s="9" t="n">
         <v>80107.12765805761</v>
       </c>
       <c r="F1023" s="9" t="n">
@@ -59021,7 +59021,7 @@
       <c r="D1024" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E1024" s="8" t="n">
+      <c r="E1024" s="9" t="n">
         <v>82126.02916519137</v>
       </c>
       <c r="F1024" s="9" t="n">
@@ -59078,7 +59078,7 @@
       <c r="D1025" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E1025" s="8" t="n">
+      <c r="E1025" s="9" t="n">
         <v>82198.13279044615</v>
       </c>
       <c r="F1025" s="9" t="n">
@@ -59135,7 +59135,7 @@
       <c r="D1026" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E1026" s="8" t="n">
+      <c r="E1026" s="9" t="n">
         <v>82126.02916519137</v>
       </c>
       <c r="F1026" s="9" t="n">
@@ -59192,7 +59192,7 @@
       <c r="D1027" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E1027" s="8" t="n">
+      <c r="E1027" s="9" t="n">
         <v>81477.09653789838</v>
       </c>
       <c r="F1027" s="9" t="n">
@@ -59249,7 +59249,7 @@
       <c r="D1028" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E1028" s="8" t="n">
+      <c r="E1028" s="9" t="n">
         <v>80756.06028535061</v>
       </c>
       <c r="F1028" s="9" t="n">
@@ -59306,7 +59306,7 @@
       <c r="D1029" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E1029" s="8" t="n">
+      <c r="E1029" s="9" t="n">
         <v>81621.30378840794</v>
       </c>
       <c r="F1029" s="9" t="n">
@@ -59363,7 +59363,7 @@
       <c r="D1030" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E1030" s="8" t="n">
+      <c r="E1030" s="9" t="n">
         <v>81166.61242963339</v>
       </c>
       <c r="F1030" s="9" t="n">
